--- a/slots/resources/sample/BaseLine.xlsx
+++ b/slots/resources/sample/BaseLine.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3CFFAE6-692B-449D-9AAD-2F442017EFEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8113424-3207-4FF5-B400-65C1A4DA5C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaseLine" sheetId="1" r:id="rId1"/>
@@ -236,7 +236,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="79">
   <si>
     <t>id</t>
   </si>
@@ -310,9 +310,6 @@
     <t>gamePlayCalc</t>
   </si>
   <si>
-    <t>1,0</t>
-  </si>
-  <si>
     <t>0:4,8,12,16,20</t>
   </si>
   <si>
@@ -467,10 +464,6 @@
   </si>
   <si>
     <t>0:1,6,11,16,20</t>
-  </si>
-  <si>
-    <t>1,0</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Map&lt;int{:}List&lt;int&gt;{,}&gt;{;}</t>
@@ -478,6 +471,10 @@
   </si>
   <si>
     <t>gameType</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,1</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -1295,7 +1292,7 @@
         <v>12</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>13</v>
@@ -1321,7 +1318,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>16</v>
@@ -1372,22 +1369,22 @@
         <v>1</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J5" s="5">
         <v>5</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.15">
@@ -1401,19 +1398,19 @@
         <v>2</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J6" s="5">
         <v>5</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.15">
@@ -1427,19 +1424,19 @@
         <v>3</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J7" s="5">
         <v>5</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.15">
@@ -1453,19 +1450,19 @@
         <v>4</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J8" s="5">
         <v>5</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.15">
@@ -1479,19 +1476,19 @@
         <v>5</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J9" s="5">
         <v>5</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.15">
@@ -1505,19 +1502,19 @@
         <v>6</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J10" s="5">
         <v>5</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.15">
@@ -1531,19 +1528,19 @@
         <v>7</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J11" s="5">
         <v>5</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.15">
@@ -1557,19 +1554,19 @@
         <v>8</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J12" s="5">
         <v>5</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.15">
@@ -1583,19 +1580,19 @@
         <v>9</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J13" s="5">
         <v>5</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.15">
@@ -1609,19 +1606,19 @@
         <v>10</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J14" s="5">
         <v>5</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.15">
@@ -1635,19 +1632,19 @@
         <v>11</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J15" s="5">
         <v>5</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.15">
@@ -1661,19 +1658,19 @@
         <v>12</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J16" s="5">
         <v>5</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.15">
@@ -1687,19 +1684,19 @@
         <v>13</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J17" s="5">
         <v>5</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.15">
@@ -1713,19 +1710,19 @@
         <v>14</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J18" s="5">
         <v>5</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.15">
@@ -1739,19 +1736,19 @@
         <v>15</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J19" s="5">
         <v>5</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.15">
@@ -1765,19 +1762,19 @@
         <v>16</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J20" s="5">
         <v>5</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.15">
@@ -1791,19 +1788,19 @@
         <v>17</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J21" s="5">
         <v>5</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.15">
@@ -1817,19 +1814,19 @@
         <v>18</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J22" s="5">
         <v>5</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.15">
@@ -1843,19 +1840,19 @@
         <v>19</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J23" s="5">
         <v>5</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.15">
@@ -1869,19 +1866,19 @@
         <v>20</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J24" s="5">
         <v>5</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.15">
@@ -1895,19 +1892,19 @@
         <v>21</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J25" s="5">
         <v>5</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.15">
@@ -1921,19 +1918,19 @@
         <v>22</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J26" s="5">
         <v>5</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.15">
@@ -1947,19 +1944,19 @@
         <v>23</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J27" s="5">
         <v>5</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.15">
@@ -1973,19 +1970,19 @@
         <v>24</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J28" s="5">
         <v>5</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.15">
@@ -1999,19 +1996,19 @@
         <v>25</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J29" s="5">
         <v>5</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.15">
@@ -2025,19 +2022,19 @@
         <v>26</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J30" s="5">
         <v>5</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.15">
@@ -2051,19 +2048,19 @@
         <v>27</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J31" s="5">
         <v>5</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.15">
@@ -2077,19 +2074,19 @@
         <v>28</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J32" s="5">
         <v>5</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.15">
@@ -2103,19 +2100,19 @@
         <v>29</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J33" s="5">
         <v>5</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.15">
@@ -2129,19 +2126,19 @@
         <v>30</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J34" s="5">
         <v>5</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.15">
@@ -2155,19 +2152,19 @@
         <v>31</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J35" s="5">
         <v>5</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.15">
@@ -2181,19 +2178,19 @@
         <v>32</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J36" s="5">
         <v>5</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.15">
@@ -2207,19 +2204,19 @@
         <v>33</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J37" s="5">
         <v>5</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.15">
@@ -2233,19 +2230,19 @@
         <v>34</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J38" s="5">
         <v>5</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.15">
@@ -2259,19 +2256,19 @@
         <v>35</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J39" s="5">
         <v>5</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.15">
@@ -2285,19 +2282,19 @@
         <v>36</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J40" s="5">
         <v>5</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.15">
@@ -2311,19 +2308,19 @@
         <v>37</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J41" s="5">
         <v>5</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.15">
@@ -2337,19 +2334,19 @@
         <v>38</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J42" s="5">
         <v>5</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.15">
@@ -2363,19 +2360,19 @@
         <v>39</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J43" s="5">
         <v>5</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.15">
@@ -2389,19 +2386,19 @@
         <v>40</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J44" s="5">
         <v>5</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.15">
@@ -2415,19 +2412,19 @@
         <v>41</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J45" s="5">
         <v>5</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.15">
@@ -2441,19 +2438,19 @@
         <v>42</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J46" s="5">
         <v>5</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.15">
@@ -2467,19 +2464,19 @@
         <v>43</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J47" s="5">
         <v>5</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.15">
@@ -2493,19 +2490,19 @@
         <v>44</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J48" s="5">
         <v>5</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.15">
@@ -2519,19 +2516,19 @@
         <v>45</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J49" s="5">
         <v>5</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.15">
@@ -2545,19 +2542,19 @@
         <v>46</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J50" s="5">
         <v>5</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.15">
@@ -2571,19 +2568,19 @@
         <v>47</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J51" s="5">
         <v>5</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.15">
@@ -2597,19 +2594,19 @@
         <v>48</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J52" s="5">
         <v>5</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.15">
@@ -2623,19 +2620,19 @@
         <v>49</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J53" s="5">
         <v>5</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.15">
@@ -2649,19 +2646,19 @@
         <v>50</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J54" s="5">
         <v>5</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseLine.xlsx
+++ b/slots/resources/sample/BaseLine.xlsx
@@ -306,7 +306,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="112">
   <si>
     <t>id</t>
   </si>
@@ -498,6 +498,60 @@
   </si>
   <si>
     <t>1,6,11,16,20</t>
+  </si>
+  <si>
+    <t>2,5,8</t>
+  </si>
+  <si>
+    <t>2,5,8,11,14</t>
+  </si>
+  <si>
+    <t>从左向右</t>
+  </si>
+  <si>
+    <t>1,4,7,10,13</t>
+  </si>
+  <si>
+    <t>3,6,9,12,15</t>
+  </si>
+  <si>
+    <t>1,5,9,11,13</t>
+  </si>
+  <si>
+    <t>3,5,7,11,15</t>
+  </si>
+  <si>
+    <t>1,4,8,10,13</t>
+  </si>
+  <si>
+    <t>3,6,8,12,15</t>
+  </si>
+  <si>
+    <t>2,6,9,12,14</t>
+  </si>
+  <si>
+    <t>2,4,7,10,14</t>
+  </si>
+  <si>
+    <t>1,5,8,11,13</t>
+  </si>
+  <si>
+    <t>3,5,8,11,15</t>
+  </si>
+  <si>
+    <t>2,5,7,11,14</t>
+  </si>
+  <si>
+    <t>2,5,9,11,14</t>
+  </si>
+  <si>
+    <t>1,6,9,12,13</t>
+  </si>
+  <si>
+    <t>3,4,7,10,15</t>
+  </si>
+  <si>
+    <t>从右向左</t>
   </si>
   <si>
     <t>线路类型</t>
@@ -787,7 +841,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -803,6 +857,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1140,7 +1206,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1164,16 +1230,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1182,89 +1248,89 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1296,6 +1362,24 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1914,7 +1998,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z54"/>
+  <dimension ref="A1:Z85"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.375"/>
@@ -2854,7 +2938,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="5">
-        <f t="shared" ref="A38:A54" si="1">(B38+500000)*100+C38</f>
+        <f t="shared" ref="A38:A56" si="1">(B38+500000)*100+C38</f>
         <v>60010034</v>
       </c>
       <c r="B38" s="6">
@@ -3225,6 +3309,793 @@
         <v>5</v>
       </c>
       <c r="G54" s="5"/>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="11">
+        <f t="shared" si="1"/>
+        <v>60030001</v>
+      </c>
+      <c r="B55" s="12">
+        <v>100300</v>
+      </c>
+      <c r="C55" s="13">
+        <v>1</v>
+      </c>
+      <c r="D55" s="13">
+        <v>1</v>
+      </c>
+      <c r="E55" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="F55" s="13">
+        <v>5</v>
+      </c>
+      <c r="G55" s="5"/>
+    </row>
+    <row r="56" spans="1:15">
+      <c r="A56" s="14">
+        <f t="shared" si="1"/>
+        <v>60120001</v>
+      </c>
+      <c r="B56" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C56" s="16">
+        <v>1</v>
+      </c>
+      <c r="D56" s="16">
+        <v>1</v>
+      </c>
+      <c r="E56" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="F56" s="16">
+        <v>5</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="K56" s="9">
+        <v>1</v>
+      </c>
+      <c r="L56" s="9">
+        <v>4</v>
+      </c>
+      <c r="M56" s="9">
+        <v>7</v>
+      </c>
+      <c r="N56" s="9">
+        <v>10</v>
+      </c>
+      <c r="O56" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15">
+      <c r="A57" s="14">
+        <f t="shared" ref="A57:A85" si="2">(B57+500000)*100+C57</f>
+        <v>60120002</v>
+      </c>
+      <c r="B57" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C57" s="16">
+        <v>2</v>
+      </c>
+      <c r="D57" s="16">
+        <v>1</v>
+      </c>
+      <c r="E57" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="F57" s="16">
+        <v>5</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="K57" s="9">
+        <v>2</v>
+      </c>
+      <c r="L57" s="9">
+        <v>5</v>
+      </c>
+      <c r="M57" s="9">
+        <v>8</v>
+      </c>
+      <c r="N57" s="9">
+        <v>11</v>
+      </c>
+      <c r="O57" s="9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15">
+      <c r="A58" s="14">
+        <f t="shared" si="2"/>
+        <v>60120003</v>
+      </c>
+      <c r="B58" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C58" s="16">
+        <v>3</v>
+      </c>
+      <c r="D58" s="16">
+        <v>1</v>
+      </c>
+      <c r="E58" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="F58" s="16">
+        <v>5</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="K58" s="9">
+        <v>3</v>
+      </c>
+      <c r="L58" s="9">
+        <v>6</v>
+      </c>
+      <c r="M58" s="9">
+        <v>9</v>
+      </c>
+      <c r="N58" s="9">
+        <v>12</v>
+      </c>
+      <c r="O58" s="9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="14">
+        <f t="shared" si="2"/>
+        <v>60120004</v>
+      </c>
+      <c r="B59" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C59" s="16">
+        <v>4</v>
+      </c>
+      <c r="D59" s="16">
+        <v>1</v>
+      </c>
+      <c r="E59" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="F59" s="16">
+        <v>5</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" s="14">
+        <f t="shared" si="2"/>
+        <v>60120005</v>
+      </c>
+      <c r="B60" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C60" s="16">
+        <v>5</v>
+      </c>
+      <c r="D60" s="16">
+        <v>1</v>
+      </c>
+      <c r="E60" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="F60" s="16">
+        <v>5</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" s="14">
+        <f t="shared" si="2"/>
+        <v>60120006</v>
+      </c>
+      <c r="B61" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C61" s="16">
+        <v>6</v>
+      </c>
+      <c r="D61" s="16">
+        <v>1</v>
+      </c>
+      <c r="E61" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="F61" s="16">
+        <v>5</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="14">
+        <f t="shared" si="2"/>
+        <v>60120007</v>
+      </c>
+      <c r="B62" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C62" s="16">
+        <v>7</v>
+      </c>
+      <c r="D62" s="16">
+        <v>1</v>
+      </c>
+      <c r="E62" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="F62" s="16">
+        <v>5</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" s="14">
+        <f t="shared" si="2"/>
+        <v>60120008</v>
+      </c>
+      <c r="B63" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C63" s="16">
+        <v>8</v>
+      </c>
+      <c r="D63" s="16">
+        <v>1</v>
+      </c>
+      <c r="E63" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="F63" s="16">
+        <v>5</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" s="14">
+        <f t="shared" si="2"/>
+        <v>60120009</v>
+      </c>
+      <c r="B64" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C64" s="16">
+        <v>9</v>
+      </c>
+      <c r="D64" s="16">
+        <v>1</v>
+      </c>
+      <c r="E64" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="F64" s="16">
+        <v>5</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" s="14">
+        <f t="shared" si="2"/>
+        <v>60120010</v>
+      </c>
+      <c r="B65" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C65" s="16">
+        <v>10</v>
+      </c>
+      <c r="D65" s="16">
+        <v>1</v>
+      </c>
+      <c r="E65" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="F65" s="16">
+        <v>5</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" s="14">
+        <f t="shared" si="2"/>
+        <v>60120011</v>
+      </c>
+      <c r="B66" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C66" s="16">
+        <v>11</v>
+      </c>
+      <c r="D66" s="16">
+        <v>1</v>
+      </c>
+      <c r="E66" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="F66" s="16">
+        <v>5</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" s="14">
+        <f t="shared" si="2"/>
+        <v>60120012</v>
+      </c>
+      <c r="B67" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C67" s="16">
+        <v>12</v>
+      </c>
+      <c r="D67" s="16">
+        <v>1</v>
+      </c>
+      <c r="E67" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="F67" s="16">
+        <v>5</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" s="14">
+        <f t="shared" si="2"/>
+        <v>60120013</v>
+      </c>
+      <c r="B68" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C68" s="16">
+        <v>13</v>
+      </c>
+      <c r="D68" s="16">
+        <v>1</v>
+      </c>
+      <c r="E68" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="F68" s="16">
+        <v>5</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" s="14">
+        <f t="shared" si="2"/>
+        <v>60120014</v>
+      </c>
+      <c r="B69" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C69" s="16">
+        <v>14</v>
+      </c>
+      <c r="D69" s="16">
+        <v>1</v>
+      </c>
+      <c r="E69" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="F69" s="16">
+        <v>5</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" s="14">
+        <f t="shared" si="2"/>
+        <v>60120015</v>
+      </c>
+      <c r="B70" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C70" s="16">
+        <v>15</v>
+      </c>
+      <c r="D70" s="16">
+        <v>1</v>
+      </c>
+      <c r="E70" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="F70" s="16">
+        <v>5</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" s="14">
+        <f t="shared" si="2"/>
+        <v>60120016</v>
+      </c>
+      <c r="B71" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C71" s="16">
+        <v>16</v>
+      </c>
+      <c r="D71" s="16">
+        <v>2</v>
+      </c>
+      <c r="E71" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="F71" s="16">
+        <v>5</v>
+      </c>
+      <c r="G71" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" s="14">
+        <f t="shared" si="2"/>
+        <v>60120017</v>
+      </c>
+      <c r="B72" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C72" s="16">
+        <v>17</v>
+      </c>
+      <c r="D72" s="16">
+        <v>2</v>
+      </c>
+      <c r="E72" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="F72" s="16">
+        <v>5</v>
+      </c>
+      <c r="G72" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" s="14">
+        <f t="shared" si="2"/>
+        <v>60120018</v>
+      </c>
+      <c r="B73" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C73" s="16">
+        <v>18</v>
+      </c>
+      <c r="D73" s="16">
+        <v>2</v>
+      </c>
+      <c r="E73" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="F73" s="16">
+        <v>5</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" s="14">
+        <f t="shared" si="2"/>
+        <v>60120019</v>
+      </c>
+      <c r="B74" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C74" s="16">
+        <v>19</v>
+      </c>
+      <c r="D74" s="16">
+        <v>2</v>
+      </c>
+      <c r="E74" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="F74" s="16">
+        <v>5</v>
+      </c>
+      <c r="G74" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" s="14">
+        <f t="shared" si="2"/>
+        <v>60120020</v>
+      </c>
+      <c r="B75" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C75" s="16">
+        <v>20</v>
+      </c>
+      <c r="D75" s="16">
+        <v>2</v>
+      </c>
+      <c r="E75" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="F75" s="16">
+        <v>5</v>
+      </c>
+      <c r="G75" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" s="14">
+        <f t="shared" si="2"/>
+        <v>60120021</v>
+      </c>
+      <c r="B76" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C76" s="16">
+        <v>21</v>
+      </c>
+      <c r="D76" s="16">
+        <v>2</v>
+      </c>
+      <c r="E76" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="F76" s="16">
+        <v>5</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" s="14">
+        <f t="shared" si="2"/>
+        <v>60120022</v>
+      </c>
+      <c r="B77" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C77" s="16">
+        <v>22</v>
+      </c>
+      <c r="D77" s="16">
+        <v>2</v>
+      </c>
+      <c r="E77" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="F77" s="16">
+        <v>5</v>
+      </c>
+      <c r="G77" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" s="14">
+        <f t="shared" si="2"/>
+        <v>60120023</v>
+      </c>
+      <c r="B78" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C78" s="16">
+        <v>23</v>
+      </c>
+      <c r="D78" s="16">
+        <v>2</v>
+      </c>
+      <c r="E78" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="F78" s="16">
+        <v>5</v>
+      </c>
+      <c r="G78" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" s="14">
+        <f t="shared" si="2"/>
+        <v>60120024</v>
+      </c>
+      <c r="B79" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C79" s="16">
+        <v>24</v>
+      </c>
+      <c r="D79" s="16">
+        <v>2</v>
+      </c>
+      <c r="E79" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="F79" s="16">
+        <v>5</v>
+      </c>
+      <c r="G79" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" s="14">
+        <f t="shared" si="2"/>
+        <v>60120025</v>
+      </c>
+      <c r="B80" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C80" s="16">
+        <v>25</v>
+      </c>
+      <c r="D80" s="16">
+        <v>2</v>
+      </c>
+      <c r="E80" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="F80" s="16">
+        <v>5</v>
+      </c>
+      <c r="G80" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" s="14">
+        <f t="shared" si="2"/>
+        <v>60120026</v>
+      </c>
+      <c r="B81" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C81" s="16">
+        <v>26</v>
+      </c>
+      <c r="D81" s="16">
+        <v>2</v>
+      </c>
+      <c r="E81" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="F81" s="16">
+        <v>5</v>
+      </c>
+      <c r="G81" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" s="14">
+        <f t="shared" si="2"/>
+        <v>60120027</v>
+      </c>
+      <c r="B82" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C82" s="16">
+        <v>27</v>
+      </c>
+      <c r="D82" s="16">
+        <v>2</v>
+      </c>
+      <c r="E82" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="F82" s="16">
+        <v>5</v>
+      </c>
+      <c r="G82" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" s="14">
+        <f t="shared" si="2"/>
+        <v>60120028</v>
+      </c>
+      <c r="B83" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C83" s="16">
+        <v>28</v>
+      </c>
+      <c r="D83" s="16">
+        <v>2</v>
+      </c>
+      <c r="E83" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="F83" s="16">
+        <v>5</v>
+      </c>
+      <c r="G83" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" s="14">
+        <f t="shared" si="2"/>
+        <v>60120029</v>
+      </c>
+      <c r="B84" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C84" s="16">
+        <v>29</v>
+      </c>
+      <c r="D84" s="16">
+        <v>2</v>
+      </c>
+      <c r="E84" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="F84" s="16">
+        <v>5</v>
+      </c>
+      <c r="G84" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" s="14">
+        <f t="shared" si="2"/>
+        <v>60120030</v>
+      </c>
+      <c r="B85" s="15">
+        <v>101200</v>
+      </c>
+      <c r="C85" s="16">
+        <v>30</v>
+      </c>
+      <c r="D85" s="16">
+        <v>2</v>
+      </c>
+      <c r="E85" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="F85" s="16">
+        <v>5</v>
+      </c>
+      <c r="G85" s="9" t="s">
+        <v>81</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3249,30 +4120,30 @@
         <v>1</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>2</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>4</v>
       </c>
       <c r="L20" s="4"/>
       <c r="M20" s="4" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="Q20" s="4" t="s">
         <v>5</v>
@@ -3281,7 +4152,7 @@
         <v>3</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="5:19">
@@ -3299,29 +4170,29 @@
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="7" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="L21" s="7"/>
       <c r="M21" s="7" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="Q21" s="7" t="s">
         <v>6</v>
       </c>
       <c r="R21" s="7" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="S21" s="7"/>
     </row>
@@ -3333,30 +4204,30 @@
         <v>9</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>10</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="K22" s="7" t="s">
         <v>12</v>
       </c>
       <c r="L22" s="7"/>
       <c r="M22" s="7" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="Q22" s="7" t="s">
         <v>13</v>
@@ -3396,28 +4267,28 @@
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="7" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
       <c r="M24" s="7" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="O24" s="7"/>
       <c r="P24" s="7" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="Q24" s="7">
         <v>5</v>
       </c>
       <c r="R24" s="7" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="S24" s="7" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="5:19">
@@ -3435,28 +4306,28 @@
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
       <c r="M25" s="8" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="O25" s="7"/>
       <c r="P25" s="7" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="Q25" s="7">
         <v>5</v>
       </c>
       <c r="R25" s="7" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="S25" s="7" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="5:19">
@@ -3524,7 +4395,7 @@
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
       <c r="L28" s="7" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="M28" s="5"/>
       <c r="N28" s="7">
@@ -3532,16 +4403,16 @@
       </c>
       <c r="O28" s="7"/>
       <c r="P28" s="7" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="Q28" s="7">
         <v>5</v>
       </c>
       <c r="R28" s="7" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="S28" s="7" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseLine.xlsx
+++ b/slots/resources/sample/BaseLine.xlsx
@@ -332,7 +332,7 @@
     <t>List&lt;int&gt;{|}</t>
   </si>
   <si>
-    <t>List&lt;int&gt;{,}</t>
+    <t>List&lt;int&gt;{_}</t>
   </si>
   <si>
     <t>gameType</t>
@@ -350,205 +350,205 @@
     <t>gamePlayCalc</t>
   </si>
   <si>
-    <t>4,8,12,16,20</t>
-  </si>
-  <si>
-    <t>1,5,9,13,17</t>
-  </si>
-  <si>
-    <t>3,7,11,15,19</t>
-  </si>
-  <si>
-    <t>2,6,10,14,18</t>
-  </si>
-  <si>
-    <t>4,7,10,15,20</t>
-  </si>
-  <si>
-    <t>1,6,11,14,17</t>
-  </si>
-  <si>
-    <t>3,6,9,14,19</t>
-  </si>
-  <si>
-    <t>2,7,12,15,18</t>
-  </si>
-  <si>
-    <t>4,7,12,15,20</t>
-  </si>
-  <si>
-    <t>1,6,9,14,17</t>
-  </si>
-  <si>
-    <t>3,8,11,16,19</t>
-  </si>
-  <si>
-    <t>2,5,10,13,18</t>
-  </si>
-  <si>
-    <t>3,6,11,14,19</t>
-  </si>
-  <si>
-    <t>2,7,10,15,18</t>
-  </si>
-  <si>
-    <t>4,7,11,15,20</t>
-  </si>
-  <si>
-    <t>1,6,10,14,17</t>
-  </si>
-  <si>
-    <t>3,8,12,16,19</t>
-  </si>
-  <si>
-    <t>2,5,9,13,18</t>
-  </si>
-  <si>
-    <t>3,6,10,14,19</t>
-  </si>
-  <si>
-    <t>2,7,11,15,18</t>
-  </si>
-  <si>
-    <t>4,8,11,16,20</t>
-  </si>
-  <si>
-    <t>1,5,10,13,17</t>
-  </si>
-  <si>
-    <t>3,7,12,15,19</t>
-  </si>
-  <si>
-    <t>2,6,9,14,18</t>
-  </si>
-  <si>
-    <t>3,7,10,15,19</t>
-  </si>
-  <si>
-    <t>2,6,11,14,18</t>
-  </si>
-  <si>
-    <t>4,8,10,16,20</t>
-  </si>
-  <si>
-    <t>1,5,11,13,17</t>
-  </si>
-  <si>
-    <t>3,7,9,15,19</t>
-  </si>
-  <si>
-    <t>2,6,12,14,18</t>
-  </si>
-  <si>
-    <t>4,6,10,14,20</t>
-  </si>
-  <si>
-    <t>1,7,11,15,17</t>
-  </si>
-  <si>
-    <t>3,5,9,13,19</t>
-  </si>
-  <si>
-    <t>2,8,12,16,18</t>
-  </si>
-  <si>
-    <t>3,8,10,16,19</t>
-  </si>
-  <si>
-    <t>2,5,11,13,18</t>
-  </si>
-  <si>
-    <t>3,6,12,14,19</t>
-  </si>
-  <si>
-    <t>2,7,9,15,18</t>
-  </si>
-  <si>
-    <t>4,6,12,14,20</t>
-  </si>
-  <si>
-    <t>1,7,9,15,17</t>
-  </si>
-  <si>
-    <t>3,5,11,13,19</t>
-  </si>
-  <si>
-    <t>2,8,10,16,18</t>
-  </si>
-  <si>
-    <t>4,6,11,14,20</t>
-  </si>
-  <si>
-    <t>1,7,10,15,17</t>
-  </si>
-  <si>
-    <t>3,5,10,13,19</t>
-  </si>
-  <si>
-    <t>2,8,11,16,18</t>
-  </si>
-  <si>
-    <t>4,8,11,14,17</t>
-  </si>
-  <si>
-    <t>1,5,10,15,20</t>
-  </si>
-  <si>
-    <t>4,7,10,13,17</t>
-  </si>
-  <si>
-    <t>1,6,11,16,20</t>
-  </si>
-  <si>
-    <t>2,5,8</t>
-  </si>
-  <si>
-    <t>2,5,8,11,14</t>
+    <t>4_8_12_16_20</t>
+  </si>
+  <si>
+    <t>1_5_9_13_17</t>
+  </si>
+  <si>
+    <t>3_7_11_15_19</t>
+  </si>
+  <si>
+    <t>2_6_10_14_18</t>
+  </si>
+  <si>
+    <t>4_7_10_15_20</t>
+  </si>
+  <si>
+    <t>1_6_11_14_17</t>
+  </si>
+  <si>
+    <t>3_6_9_14_19</t>
+  </si>
+  <si>
+    <t>2_7_12_15_18</t>
+  </si>
+  <si>
+    <t>4_7_12_15_20</t>
+  </si>
+  <si>
+    <t>1_6_9_14_17</t>
+  </si>
+  <si>
+    <t>3_8_11_16_19</t>
+  </si>
+  <si>
+    <t>2_5_10_13_18</t>
+  </si>
+  <si>
+    <t>3_6_11_14_19</t>
+  </si>
+  <si>
+    <t>2_7_10_15_18</t>
+  </si>
+  <si>
+    <t>4_7_11_15_20</t>
+  </si>
+  <si>
+    <t>1_6_10_14_17</t>
+  </si>
+  <si>
+    <t>3_8_12_16_19</t>
+  </si>
+  <si>
+    <t>2_5_9_13_18</t>
+  </si>
+  <si>
+    <t>3_6_10_14_19</t>
+  </si>
+  <si>
+    <t>2_7_11_15_18</t>
+  </si>
+  <si>
+    <t>4_8_11_16_20</t>
+  </si>
+  <si>
+    <t>1_5_10_13_17</t>
+  </si>
+  <si>
+    <t>3_7_12_15_19</t>
+  </si>
+  <si>
+    <t>2_6_9_14_18</t>
+  </si>
+  <si>
+    <t>3_7_10_15_19</t>
+  </si>
+  <si>
+    <t>2_6_11_14_18</t>
+  </si>
+  <si>
+    <t>4_8_10_16_20</t>
+  </si>
+  <si>
+    <t>1_5_11_13_17</t>
+  </si>
+  <si>
+    <t>3_7_9_15_19</t>
+  </si>
+  <si>
+    <t>2_6_12_14_18</t>
+  </si>
+  <si>
+    <t>4_6_10_14_20</t>
+  </si>
+  <si>
+    <t>1_7_11_15_17</t>
+  </si>
+  <si>
+    <t>3_5_9_13_19</t>
+  </si>
+  <si>
+    <t>2_8_12_16_18</t>
+  </si>
+  <si>
+    <t>3_8_10_16_19</t>
+  </si>
+  <si>
+    <t>2_5_11_13_18</t>
+  </si>
+  <si>
+    <t>3_6_12_14_19</t>
+  </si>
+  <si>
+    <t>2_7_9_15_18</t>
+  </si>
+  <si>
+    <t>4_6_12_14_20</t>
+  </si>
+  <si>
+    <t>1_7_9_15_17</t>
+  </si>
+  <si>
+    <t>3_5_11_13_19</t>
+  </si>
+  <si>
+    <t>2_8_10_16_18</t>
+  </si>
+  <si>
+    <t>4_6_11_14_20</t>
+  </si>
+  <si>
+    <t>1_7_10_15_17</t>
+  </si>
+  <si>
+    <t>3_5_10_13_19</t>
+  </si>
+  <si>
+    <t>2_8_11_16_18</t>
+  </si>
+  <si>
+    <t>4_8_11_14_17</t>
+  </si>
+  <si>
+    <t>1_5_10_15_20</t>
+  </si>
+  <si>
+    <t>4_7_10_13_17</t>
+  </si>
+  <si>
+    <t>1_6_11_16_20</t>
+  </si>
+  <si>
+    <t>2_5_8</t>
+  </si>
+  <si>
+    <t>2_5_8_11_14</t>
   </si>
   <si>
     <t>从左向右</t>
   </si>
   <si>
-    <t>1,4,7,10,13</t>
-  </si>
-  <si>
-    <t>3,6,9,12,15</t>
-  </si>
-  <si>
-    <t>1,5,9,11,13</t>
-  </si>
-  <si>
-    <t>3,5,7,11,15</t>
-  </si>
-  <si>
-    <t>1,4,8,10,13</t>
-  </si>
-  <si>
-    <t>3,6,8,12,15</t>
-  </si>
-  <si>
-    <t>2,6,9,12,14</t>
-  </si>
-  <si>
-    <t>2,4,7,10,14</t>
-  </si>
-  <si>
-    <t>1,5,8,11,13</t>
-  </si>
-  <si>
-    <t>3,5,8,11,15</t>
-  </si>
-  <si>
-    <t>2,5,7,11,14</t>
-  </si>
-  <si>
-    <t>2,5,9,11,14</t>
-  </si>
-  <si>
-    <t>1,6,9,12,13</t>
-  </si>
-  <si>
-    <t>3,4,7,10,15</t>
+    <t>1_4_7_10_13</t>
+  </si>
+  <si>
+    <t>3_6_9_12_15</t>
+  </si>
+  <si>
+    <t>1_5_9_11_13</t>
+  </si>
+  <si>
+    <t>3_5_7_11_15</t>
+  </si>
+  <si>
+    <t>1_4_8_10_13</t>
+  </si>
+  <si>
+    <t>3_6_8_12_15</t>
+  </si>
+  <si>
+    <t>2_6_9_12_14</t>
+  </si>
+  <si>
+    <t>2_4_7_10_14</t>
+  </si>
+  <si>
+    <t>1_5_8_11_13</t>
+  </si>
+  <si>
+    <t>3_5_8_11_15</t>
+  </si>
+  <si>
+    <t>2_5_7_11_14</t>
+  </si>
+  <si>
+    <t>2_5_9_11_14</t>
+  </si>
+  <si>
+    <t>1_6_9_12_13</t>
+  </si>
+  <si>
+    <t>3_4_7_10_15</t>
   </si>
   <si>
     <t>从右向左</t>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="G55" s="5"/>
     </row>
-    <row r="56" spans="1:15">
+    <row r="56" spans="1:7">
       <c r="A56" s="14">
         <f t="shared" si="1"/>
         <v>60120001</v>
@@ -3355,23 +3355,8 @@
       <c r="G56" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="K56" s="9">
-        <v>1</v>
-      </c>
-      <c r="L56" s="9">
-        <v>4</v>
-      </c>
-      <c r="M56" s="9">
-        <v>7</v>
-      </c>
-      <c r="N56" s="9">
-        <v>10</v>
-      </c>
-      <c r="O56" s="9">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15">
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57" s="14">
         <f t="shared" ref="A57:A85" si="2">(B57+500000)*100+C57</f>
         <v>60120002</v>
@@ -3394,23 +3379,8 @@
       <c r="G57" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="K57" s="9">
-        <v>2</v>
-      </c>
-      <c r="L57" s="9">
-        <v>5</v>
-      </c>
-      <c r="M57" s="9">
-        <v>8</v>
-      </c>
-      <c r="N57" s="9">
-        <v>11</v>
-      </c>
-      <c r="O57" s="9">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15">
+    </row>
+    <row r="58" spans="1:7">
       <c r="A58" s="14">
         <f t="shared" si="2"/>
         <v>60120003</v>
@@ -3432,21 +3402,6 @@
       </c>
       <c r="G58" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="K58" s="9">
-        <v>3</v>
-      </c>
-      <c r="L58" s="9">
-        <v>6</v>
-      </c>
-      <c r="M58" s="9">
-        <v>9</v>
-      </c>
-      <c r="N58" s="9">
-        <v>12</v>
-      </c>
-      <c r="O58" s="9">
-        <v>15</v>
       </c>
     </row>
     <row r="59" spans="1:7">

--- a/slots/resources/sample/BaseLine.xlsx
+++ b/slots/resources/sample/BaseLine.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="BaseLine" sheetId="1" r:id="rId1"/>

--- a/slots/resources/sample/BaseLine.xlsx
+++ b/slots/resources/sample/BaseLine.xlsx
@@ -306,7 +306,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="112">
   <si>
     <t>id</t>
   </si>
@@ -1745,6 +1745,266 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9505567" cy="9816255"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="790575" y="18230850"/>
+          <a:ext cx="9505315" cy="9815830"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>660400</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>176530</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="790575" y="18230850"/>
+          <a:ext cx="9509125" cy="9815830"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9505567" cy="9816255"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="790575" y="18230850"/>
+          <a:ext cx="9505315" cy="9815830"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>660400</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>176530</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="790575" y="18230850"/>
+          <a:ext cx="9509125" cy="9815830"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9505567" cy="9816255"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="790575" y="18230850"/>
+          <a:ext cx="9505315" cy="9815830"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>660400</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>176530</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="790575" y="18230850"/>
+          <a:ext cx="9509125" cy="9815830"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9505567" cy="9816255"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="790575" y="18230850"/>
+          <a:ext cx="9505315" cy="9815830"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9360">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1998,7 +2258,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z85"/>
+  <dimension ref="A1:Z135"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.375"/>
@@ -3358,7 +3618,7 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="14">
-        <f t="shared" ref="A57:A85" si="2">(B57+500000)*100+C57</f>
+        <f t="shared" ref="A57:A120" si="2">(B57+500000)*100+C57</f>
         <v>60120002</v>
       </c>
       <c r="B57" s="15">
@@ -4051,6 +4311,1240 @@
       <c r="G85" s="9" t="s">
         <v>81</v>
       </c>
+    </row>
+    <row r="86" s="5" customFormat="1" spans="1:6">
+      <c r="A86" s="5">
+        <f t="shared" si="2"/>
+        <v>60240001</v>
+      </c>
+      <c r="B86" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C86" s="7">
+        <v>1</v>
+      </c>
+      <c r="D86" s="7">
+        <v>1</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F86" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" s="5">
+        <f t="shared" si="2"/>
+        <v>60240002</v>
+      </c>
+      <c r="B87" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C87" s="7">
+        <v>2</v>
+      </c>
+      <c r="D87" s="7">
+        <v>1</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F87" s="7">
+        <v>5</v>
+      </c>
+      <c r="G87" s="5"/>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" s="5">
+        <f t="shared" si="2"/>
+        <v>60240003</v>
+      </c>
+      <c r="B88" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C88" s="7">
+        <v>3</v>
+      </c>
+      <c r="D88" s="7">
+        <v>1</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F88" s="7">
+        <v>5</v>
+      </c>
+      <c r="G88" s="5"/>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" s="5">
+        <f t="shared" si="2"/>
+        <v>60240004</v>
+      </c>
+      <c r="B89" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C89" s="7">
+        <v>4</v>
+      </c>
+      <c r="D89" s="7">
+        <v>1</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F89" s="7">
+        <v>5</v>
+      </c>
+      <c r="G89" s="5"/>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" s="5">
+        <f t="shared" si="2"/>
+        <v>60240005</v>
+      </c>
+      <c r="B90" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C90" s="7">
+        <v>5</v>
+      </c>
+      <c r="D90" s="7">
+        <v>1</v>
+      </c>
+      <c r="E90" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F90" s="7">
+        <v>5</v>
+      </c>
+      <c r="G90" s="5"/>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" s="5">
+        <f t="shared" si="2"/>
+        <v>60240006</v>
+      </c>
+      <c r="B91" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C91" s="7">
+        <v>6</v>
+      </c>
+      <c r="D91" s="7">
+        <v>1</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F91" s="7">
+        <v>5</v>
+      </c>
+      <c r="G91" s="5"/>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" s="5">
+        <f t="shared" si="2"/>
+        <v>60240007</v>
+      </c>
+      <c r="B92" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C92" s="7">
+        <v>7</v>
+      </c>
+      <c r="D92" s="7">
+        <v>1</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F92" s="7">
+        <v>5</v>
+      </c>
+      <c r="G92" s="5"/>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" s="5">
+        <f t="shared" si="2"/>
+        <v>60240008</v>
+      </c>
+      <c r="B93" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C93" s="7">
+        <v>8</v>
+      </c>
+      <c r="D93" s="7">
+        <v>1</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F93" s="7">
+        <v>5</v>
+      </c>
+      <c r="G93" s="5"/>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" s="5">
+        <f t="shared" si="2"/>
+        <v>60240009</v>
+      </c>
+      <c r="B94" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C94" s="7">
+        <v>9</v>
+      </c>
+      <c r="D94" s="7">
+        <v>1</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F94" s="7">
+        <v>5</v>
+      </c>
+      <c r="G94" s="5"/>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" s="5">
+        <f t="shared" si="2"/>
+        <v>60240010</v>
+      </c>
+      <c r="B95" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C95" s="7">
+        <v>10</v>
+      </c>
+      <c r="D95" s="7">
+        <v>1</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F95" s="7">
+        <v>5</v>
+      </c>
+      <c r="G95" s="5"/>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" s="5">
+        <f t="shared" si="2"/>
+        <v>60240011</v>
+      </c>
+      <c r="B96" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C96" s="7">
+        <v>11</v>
+      </c>
+      <c r="D96" s="7">
+        <v>1</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F96" s="7">
+        <v>5</v>
+      </c>
+      <c r="G96" s="5"/>
+    </row>
+    <row r="97" spans="1:26">
+      <c r="A97" s="5">
+        <f t="shared" si="2"/>
+        <v>60240012</v>
+      </c>
+      <c r="B97" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C97" s="7">
+        <v>12</v>
+      </c>
+      <c r="D97" s="7">
+        <v>1</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F97" s="7">
+        <v>5</v>
+      </c>
+      <c r="G97" s="5"/>
+      <c r="L97"/>
+      <c r="M97"/>
+      <c r="N97"/>
+      <c r="O97"/>
+      <c r="P97"/>
+      <c r="Q97"/>
+      <c r="R97"/>
+      <c r="S97"/>
+      <c r="T97"/>
+      <c r="U97"/>
+      <c r="V97"/>
+      <c r="W97"/>
+      <c r="X97"/>
+      <c r="Y97"/>
+      <c r="Z97"/>
+    </row>
+    <row r="98" spans="1:26">
+      <c r="A98" s="5">
+        <f t="shared" si="2"/>
+        <v>60240013</v>
+      </c>
+      <c r="B98" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C98" s="7">
+        <v>13</v>
+      </c>
+      <c r="D98" s="7">
+        <v>1</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F98" s="7">
+        <v>5</v>
+      </c>
+      <c r="G98" s="5"/>
+      <c r="L98"/>
+      <c r="M98"/>
+      <c r="N98"/>
+      <c r="O98"/>
+      <c r="P98"/>
+      <c r="Q98"/>
+      <c r="R98"/>
+      <c r="S98"/>
+      <c r="T98"/>
+      <c r="U98"/>
+      <c r="V98"/>
+      <c r="W98"/>
+      <c r="X98"/>
+      <c r="Y98"/>
+      <c r="Z98"/>
+    </row>
+    <row r="99" spans="1:26">
+      <c r="A99" s="5">
+        <f t="shared" si="2"/>
+        <v>60240014</v>
+      </c>
+      <c r="B99" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C99" s="7">
+        <v>14</v>
+      </c>
+      <c r="D99" s="7">
+        <v>1</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F99" s="7">
+        <v>5</v>
+      </c>
+      <c r="G99" s="5"/>
+      <c r="L99"/>
+      <c r="M99"/>
+      <c r="N99"/>
+      <c r="O99"/>
+      <c r="P99"/>
+      <c r="Q99"/>
+      <c r="R99"/>
+      <c r="S99"/>
+      <c r="T99"/>
+      <c r="U99"/>
+      <c r="V99"/>
+      <c r="W99"/>
+      <c r="X99"/>
+      <c r="Y99"/>
+      <c r="Z99"/>
+    </row>
+    <row r="100" spans="1:26">
+      <c r="A100" s="5">
+        <f t="shared" si="2"/>
+        <v>60240015</v>
+      </c>
+      <c r="B100" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C100" s="7">
+        <v>15</v>
+      </c>
+      <c r="D100" s="7">
+        <v>1</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F100" s="7">
+        <v>5</v>
+      </c>
+      <c r="G100" s="5"/>
+      <c r="L100"/>
+      <c r="M100"/>
+      <c r="N100"/>
+      <c r="O100"/>
+      <c r="P100"/>
+      <c r="Q100"/>
+      <c r="R100"/>
+      <c r="S100"/>
+      <c r="T100"/>
+      <c r="U100"/>
+      <c r="V100"/>
+      <c r="W100"/>
+      <c r="X100"/>
+      <c r="Y100"/>
+      <c r="Z100"/>
+    </row>
+    <row r="101" spans="1:26">
+      <c r="A101" s="5">
+        <f t="shared" si="2"/>
+        <v>60240016</v>
+      </c>
+      <c r="B101" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C101" s="7">
+        <v>16</v>
+      </c>
+      <c r="D101" s="7">
+        <v>1</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F101" s="7">
+        <v>5</v>
+      </c>
+      <c r="G101" s="5"/>
+      <c r="L101"/>
+      <c r="M101"/>
+      <c r="N101"/>
+      <c r="O101"/>
+      <c r="P101"/>
+      <c r="Q101"/>
+      <c r="R101"/>
+      <c r="S101"/>
+      <c r="T101"/>
+      <c r="U101"/>
+      <c r="V101"/>
+      <c r="W101"/>
+      <c r="X101"/>
+      <c r="Y101"/>
+      <c r="Z101"/>
+    </row>
+    <row r="102" spans="1:26">
+      <c r="A102" s="5">
+        <f t="shared" si="2"/>
+        <v>60240017</v>
+      </c>
+      <c r="B102" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C102" s="7">
+        <v>17</v>
+      </c>
+      <c r="D102" s="7">
+        <v>1</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F102" s="7">
+        <v>5</v>
+      </c>
+      <c r="G102" s="5"/>
+      <c r="L102"/>
+      <c r="M102"/>
+      <c r="N102"/>
+      <c r="O102"/>
+      <c r="P102"/>
+      <c r="Q102"/>
+      <c r="R102"/>
+      <c r="S102"/>
+      <c r="T102"/>
+      <c r="U102"/>
+      <c r="V102"/>
+      <c r="W102"/>
+      <c r="X102"/>
+      <c r="Y102"/>
+      <c r="Z102"/>
+    </row>
+    <row r="103" spans="1:26">
+      <c r="A103" s="5">
+        <f t="shared" si="2"/>
+        <v>60240018</v>
+      </c>
+      <c r="B103" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C103" s="7">
+        <v>18</v>
+      </c>
+      <c r="D103" s="7">
+        <v>1</v>
+      </c>
+      <c r="E103" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F103" s="7">
+        <v>5</v>
+      </c>
+      <c r="G103" s="5"/>
+      <c r="L103"/>
+      <c r="M103"/>
+      <c r="N103"/>
+      <c r="O103"/>
+      <c r="P103"/>
+      <c r="Q103"/>
+      <c r="R103"/>
+      <c r="S103"/>
+      <c r="T103"/>
+      <c r="U103"/>
+      <c r="V103"/>
+      <c r="W103"/>
+      <c r="X103"/>
+      <c r="Y103"/>
+      <c r="Z103"/>
+    </row>
+    <row r="104" spans="1:26">
+      <c r="A104" s="5">
+        <f t="shared" si="2"/>
+        <v>60240019</v>
+      </c>
+      <c r="B104" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C104" s="7">
+        <v>19</v>
+      </c>
+      <c r="D104" s="7">
+        <v>1</v>
+      </c>
+      <c r="E104" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F104" s="7">
+        <v>5</v>
+      </c>
+      <c r="G104" s="5"/>
+      <c r="L104"/>
+      <c r="M104"/>
+      <c r="N104"/>
+      <c r="O104"/>
+      <c r="P104"/>
+      <c r="Q104"/>
+      <c r="R104"/>
+      <c r="S104"/>
+      <c r="T104"/>
+      <c r="U104"/>
+      <c r="V104"/>
+      <c r="W104"/>
+      <c r="X104"/>
+      <c r="Y104"/>
+      <c r="Z104"/>
+    </row>
+    <row r="105" spans="1:26">
+      <c r="A105" s="5">
+        <f t="shared" si="2"/>
+        <v>60240020</v>
+      </c>
+      <c r="B105" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C105" s="7">
+        <v>20</v>
+      </c>
+      <c r="D105" s="7">
+        <v>1</v>
+      </c>
+      <c r="E105" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F105" s="7">
+        <v>5</v>
+      </c>
+      <c r="G105" s="5"/>
+      <c r="L105"/>
+      <c r="M105"/>
+      <c r="N105"/>
+      <c r="O105"/>
+      <c r="P105"/>
+      <c r="Q105"/>
+      <c r="R105"/>
+      <c r="S105"/>
+      <c r="T105"/>
+      <c r="U105"/>
+      <c r="V105"/>
+      <c r="W105"/>
+      <c r="X105"/>
+      <c r="Y105"/>
+      <c r="Z105"/>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106" s="5">
+        <f t="shared" si="2"/>
+        <v>60240021</v>
+      </c>
+      <c r="B106" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C106" s="7">
+        <v>21</v>
+      </c>
+      <c r="D106" s="7">
+        <v>1</v>
+      </c>
+      <c r="E106" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F106" s="7">
+        <v>5</v>
+      </c>
+      <c r="G106" s="5"/>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107" s="5">
+        <f t="shared" si="2"/>
+        <v>60240022</v>
+      </c>
+      <c r="B107" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C107" s="7">
+        <v>22</v>
+      </c>
+      <c r="D107" s="7">
+        <v>1</v>
+      </c>
+      <c r="E107" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F107" s="7">
+        <v>5</v>
+      </c>
+      <c r="G107" s="5"/>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" s="5">
+        <f t="shared" si="2"/>
+        <v>60240023</v>
+      </c>
+      <c r="B108" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C108" s="7">
+        <v>23</v>
+      </c>
+      <c r="D108" s="7">
+        <v>1</v>
+      </c>
+      <c r="E108" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F108" s="7">
+        <v>5</v>
+      </c>
+      <c r="G108" s="5"/>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109" s="5">
+        <f t="shared" si="2"/>
+        <v>60240024</v>
+      </c>
+      <c r="B109" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C109" s="7">
+        <v>24</v>
+      </c>
+      <c r="D109" s="7">
+        <v>1</v>
+      </c>
+      <c r="E109" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F109" s="7">
+        <v>5</v>
+      </c>
+      <c r="G109" s="5"/>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110" s="5">
+        <f t="shared" si="2"/>
+        <v>60240025</v>
+      </c>
+      <c r="B110" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C110" s="7">
+        <v>25</v>
+      </c>
+      <c r="D110" s="7">
+        <v>1</v>
+      </c>
+      <c r="E110" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F110" s="7">
+        <v>5</v>
+      </c>
+      <c r="G110" s="5"/>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111" s="5">
+        <f t="shared" si="2"/>
+        <v>60240026</v>
+      </c>
+      <c r="B111" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C111" s="7">
+        <v>26</v>
+      </c>
+      <c r="D111" s="7">
+        <v>1</v>
+      </c>
+      <c r="E111" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F111" s="7">
+        <v>5</v>
+      </c>
+      <c r="G111" s="5"/>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112" s="5">
+        <f t="shared" si="2"/>
+        <v>60240027</v>
+      </c>
+      <c r="B112" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C112" s="7">
+        <v>27</v>
+      </c>
+      <c r="D112" s="7">
+        <v>1</v>
+      </c>
+      <c r="E112" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F112" s="7">
+        <v>5</v>
+      </c>
+      <c r="G112" s="5"/>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113" s="5">
+        <f t="shared" si="2"/>
+        <v>60240028</v>
+      </c>
+      <c r="B113" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C113" s="7">
+        <v>28</v>
+      </c>
+      <c r="D113" s="7">
+        <v>1</v>
+      </c>
+      <c r="E113" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F113" s="7">
+        <v>5</v>
+      </c>
+      <c r="G113" s="5"/>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114" s="5">
+        <f t="shared" si="2"/>
+        <v>60240029</v>
+      </c>
+      <c r="B114" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C114" s="7">
+        <v>29</v>
+      </c>
+      <c r="D114" s="7">
+        <v>1</v>
+      </c>
+      <c r="E114" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F114" s="7">
+        <v>5</v>
+      </c>
+      <c r="G114" s="5"/>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" s="5">
+        <f t="shared" si="2"/>
+        <v>60240030</v>
+      </c>
+      <c r="B115" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C115" s="7">
+        <v>30</v>
+      </c>
+      <c r="D115" s="7">
+        <v>1</v>
+      </c>
+      <c r="E115" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F115" s="7">
+        <v>5</v>
+      </c>
+      <c r="G115" s="5"/>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" s="5">
+        <f t="shared" si="2"/>
+        <v>60240031</v>
+      </c>
+      <c r="B116" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C116" s="7">
+        <v>31</v>
+      </c>
+      <c r="D116" s="7">
+        <v>1</v>
+      </c>
+      <c r="E116" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F116" s="7">
+        <v>5</v>
+      </c>
+      <c r="G116" s="5"/>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" s="5">
+        <f t="shared" si="2"/>
+        <v>60240032</v>
+      </c>
+      <c r="B117" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C117" s="7">
+        <v>32</v>
+      </c>
+      <c r="D117" s="7">
+        <v>1</v>
+      </c>
+      <c r="E117" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F117" s="7">
+        <v>5</v>
+      </c>
+      <c r="G117" s="5"/>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" s="5">
+        <f t="shared" si="2"/>
+        <v>60240033</v>
+      </c>
+      <c r="B118" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C118" s="7">
+        <v>33</v>
+      </c>
+      <c r="D118" s="7">
+        <v>1</v>
+      </c>
+      <c r="E118" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F118" s="7">
+        <v>5</v>
+      </c>
+      <c r="G118" s="5"/>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" s="5">
+        <f t="shared" si="2"/>
+        <v>60240034</v>
+      </c>
+      <c r="B119" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C119" s="7">
+        <v>34</v>
+      </c>
+      <c r="D119" s="7">
+        <v>1</v>
+      </c>
+      <c r="E119" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F119" s="7">
+        <v>5</v>
+      </c>
+      <c r="G119" s="5"/>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120" s="5">
+        <f t="shared" si="2"/>
+        <v>60240035</v>
+      </c>
+      <c r="B120" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C120" s="7">
+        <v>35</v>
+      </c>
+      <c r="D120" s="7">
+        <v>1</v>
+      </c>
+      <c r="E120" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F120" s="7">
+        <v>5</v>
+      </c>
+      <c r="G120" s="5"/>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" s="5">
+        <f t="shared" ref="A121:A135" si="3">(B121+500000)*100+C121</f>
+        <v>60240036</v>
+      </c>
+      <c r="B121" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C121" s="7">
+        <v>36</v>
+      </c>
+      <c r="D121" s="7">
+        <v>1</v>
+      </c>
+      <c r="E121" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F121" s="7">
+        <v>5</v>
+      </c>
+      <c r="G121" s="5"/>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122" s="5">
+        <f t="shared" si="3"/>
+        <v>60240037</v>
+      </c>
+      <c r="B122" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C122" s="7">
+        <v>37</v>
+      </c>
+      <c r="D122" s="7">
+        <v>1</v>
+      </c>
+      <c r="E122" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F122" s="7">
+        <v>5</v>
+      </c>
+      <c r="G122" s="5"/>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" s="5">
+        <f t="shared" si="3"/>
+        <v>60240038</v>
+      </c>
+      <c r="B123" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C123" s="7">
+        <v>38</v>
+      </c>
+      <c r="D123" s="7">
+        <v>1</v>
+      </c>
+      <c r="E123" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F123" s="7">
+        <v>5</v>
+      </c>
+      <c r="G123" s="5"/>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124" s="5">
+        <f t="shared" si="3"/>
+        <v>60240039</v>
+      </c>
+      <c r="B124" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C124" s="7">
+        <v>39</v>
+      </c>
+      <c r="D124" s="7">
+        <v>1</v>
+      </c>
+      <c r="E124" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F124" s="7">
+        <v>5</v>
+      </c>
+      <c r="G124" s="5"/>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" s="5">
+        <f t="shared" si="3"/>
+        <v>60240040</v>
+      </c>
+      <c r="B125" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C125" s="7">
+        <v>40</v>
+      </c>
+      <c r="D125" s="7">
+        <v>1</v>
+      </c>
+      <c r="E125" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F125" s="7">
+        <v>5</v>
+      </c>
+      <c r="G125" s="5"/>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126" s="5">
+        <f t="shared" si="3"/>
+        <v>60240041</v>
+      </c>
+      <c r="B126" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C126" s="7">
+        <v>41</v>
+      </c>
+      <c r="D126" s="7">
+        <v>1</v>
+      </c>
+      <c r="E126" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F126" s="7">
+        <v>5</v>
+      </c>
+      <c r="G126" s="5"/>
+    </row>
+    <row r="127" spans="1:7">
+      <c r="A127" s="5">
+        <f t="shared" si="3"/>
+        <v>60240042</v>
+      </c>
+      <c r="B127" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C127" s="7">
+        <v>42</v>
+      </c>
+      <c r="D127" s="7">
+        <v>1</v>
+      </c>
+      <c r="E127" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F127" s="7">
+        <v>5</v>
+      </c>
+      <c r="G127" s="5"/>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="A128" s="5">
+        <f t="shared" si="3"/>
+        <v>60240043</v>
+      </c>
+      <c r="B128" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C128" s="7">
+        <v>43</v>
+      </c>
+      <c r="D128" s="7">
+        <v>1</v>
+      </c>
+      <c r="E128" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F128" s="7">
+        <v>5</v>
+      </c>
+      <c r="G128" s="5"/>
+    </row>
+    <row r="129" spans="1:7">
+      <c r="A129" s="5">
+        <f t="shared" si="3"/>
+        <v>60240044</v>
+      </c>
+      <c r="B129" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C129" s="7">
+        <v>44</v>
+      </c>
+      <c r="D129" s="7">
+        <v>1</v>
+      </c>
+      <c r="E129" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F129" s="7">
+        <v>5</v>
+      </c>
+      <c r="G129" s="5"/>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="A130" s="5">
+        <f t="shared" si="3"/>
+        <v>60240045</v>
+      </c>
+      <c r="B130" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C130" s="7">
+        <v>45</v>
+      </c>
+      <c r="D130" s="7">
+        <v>1</v>
+      </c>
+      <c r="E130" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F130" s="7">
+        <v>5</v>
+      </c>
+      <c r="G130" s="5"/>
+    </row>
+    <row r="131" spans="1:7">
+      <c r="A131" s="5">
+        <f t="shared" si="3"/>
+        <v>60240046</v>
+      </c>
+      <c r="B131" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C131" s="7">
+        <v>46</v>
+      </c>
+      <c r="D131" s="7">
+        <v>1</v>
+      </c>
+      <c r="E131" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F131" s="7">
+        <v>5</v>
+      </c>
+      <c r="G131" s="5"/>
+    </row>
+    <row r="132" spans="1:7">
+      <c r="A132" s="5">
+        <f t="shared" si="3"/>
+        <v>60240047</v>
+      </c>
+      <c r="B132" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C132" s="7">
+        <v>47</v>
+      </c>
+      <c r="D132" s="7">
+        <v>1</v>
+      </c>
+      <c r="E132" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F132" s="7">
+        <v>5</v>
+      </c>
+      <c r="G132" s="5"/>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133" s="5">
+        <f t="shared" si="3"/>
+        <v>60240048</v>
+      </c>
+      <c r="B133" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C133" s="7">
+        <v>48</v>
+      </c>
+      <c r="D133" s="7">
+        <v>1</v>
+      </c>
+      <c r="E133" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F133" s="7">
+        <v>5</v>
+      </c>
+      <c r="G133" s="5"/>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="A134" s="5">
+        <f t="shared" si="3"/>
+        <v>60240049</v>
+      </c>
+      <c r="B134" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C134" s="7">
+        <v>49</v>
+      </c>
+      <c r="D134" s="7">
+        <v>1</v>
+      </c>
+      <c r="E134" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F134" s="7">
+        <v>5</v>
+      </c>
+      <c r="G134" s="5"/>
+    </row>
+    <row r="135" spans="1:7">
+      <c r="A135" s="5">
+        <f t="shared" si="3"/>
+        <v>60240050</v>
+      </c>
+      <c r="B135" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C135" s="7">
+        <v>50</v>
+      </c>
+      <c r="D135" s="7">
+        <v>1</v>
+      </c>
+      <c r="E135" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F135" s="7">
+        <v>5</v>
+      </c>
+      <c r="G135" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseLine.xlsx
+++ b/slots/resources/sample/BaseLine.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseLine" sheetId="1" r:id="rId1"/>
@@ -88,6 +88,18 @@
 最小:6
 全局:7
 未被覆盖加:8</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>默认为0，若主游戏和免费游戏不一样时用1、2分别</t>
         </r>
       </text>
     </comment>
@@ -306,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="139">
   <si>
     <t>id</t>
   </si>
@@ -326,6 +338,9 @@
     <t>玩法算法</t>
   </si>
   <si>
+    <t>指定适用模式</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -350,6 +365,9 @@
     <t>gamePlayCalc</t>
   </si>
   <si>
+    <t>gameMode</t>
+  </si>
+  <si>
     <t>4_8_12_16_20</t>
   </si>
   <si>
@@ -552,6 +570,81 @@
   </si>
   <si>
     <t>从右向左</t>
+  </si>
+  <si>
+    <t>1_4_8_12_15</t>
+  </si>
+  <si>
+    <t>3_6_8_10_13</t>
+  </si>
+  <si>
+    <t>2_6_8_10_14</t>
+  </si>
+  <si>
+    <t>2_4_8_12_14</t>
+  </si>
+  <si>
+    <t>1_5_7_11_13</t>
+  </si>
+  <si>
+    <t>3_5_9_11_15</t>
+  </si>
+  <si>
+    <t>1_4_9_10_13</t>
+  </si>
+  <si>
+    <t>3_6_7_12_15</t>
+  </si>
+  <si>
+    <t>2_6_7_12_14</t>
+  </si>
+  <si>
+    <t>2_4_9_10_14</t>
+  </si>
+  <si>
+    <t>1_6_7_12_13</t>
+  </si>
+  <si>
+    <t>3_4_9_10_15</t>
+  </si>
+  <si>
+    <t>1_4_7_11_15</t>
+  </si>
+  <si>
+    <t>1_4_7_10_15</t>
+  </si>
+  <si>
+    <t>3_6_9_12_13</t>
+  </si>
+  <si>
+    <t>1_4_9_12_15</t>
+  </si>
+  <si>
+    <t>3_6_7_10_13</t>
+  </si>
+  <si>
+    <t>1_5_9_12_15</t>
+  </si>
+  <si>
+    <t>3_5_7_10_13</t>
+  </si>
+  <si>
+    <t>1_6_9_11_13</t>
+  </si>
+  <si>
+    <t>3_4_7_11_15</t>
+  </si>
+  <si>
+    <t>1_5_9_12_13</t>
+  </si>
+  <si>
+    <t>3_5_7_10_15</t>
+  </si>
+  <si>
+    <t>1_6_9_12_15</t>
+  </si>
+  <si>
+    <t>3_4_7_10_13</t>
   </si>
   <si>
     <t>线路类型</t>
@@ -1330,7 +1423,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1364,22 +1457,19 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1454,7 +1544,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>660400</xdr:colOff>
+      <xdr:colOff>360045</xdr:colOff>
       <xdr:row>45</xdr:row>
       <xdr:rowOff>176530</xdr:rowOff>
     </xdr:to>
@@ -1529,7 +1619,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>660400</xdr:colOff>
+      <xdr:colOff>360045</xdr:colOff>
       <xdr:row>51</xdr:row>
       <xdr:rowOff>176530</xdr:rowOff>
     </xdr:to>
@@ -1604,7 +1694,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>660400</xdr:colOff>
+      <xdr:colOff>360045</xdr:colOff>
       <xdr:row>51</xdr:row>
       <xdr:rowOff>176530</xdr:rowOff>
     </xdr:to>
@@ -1679,7 +1769,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>660400</xdr:colOff>
+      <xdr:colOff>360045</xdr:colOff>
       <xdr:row>51</xdr:row>
       <xdr:rowOff>176530</xdr:rowOff>
     </xdr:to>
@@ -1789,7 +1879,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>660400</xdr:colOff>
+      <xdr:colOff>360045</xdr:colOff>
       <xdr:row>132</xdr:row>
       <xdr:rowOff>176530</xdr:rowOff>
     </xdr:to>
@@ -1864,7 +1954,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>660400</xdr:colOff>
+      <xdr:colOff>360045</xdr:colOff>
       <xdr:row>132</xdr:row>
       <xdr:rowOff>176530</xdr:rowOff>
     </xdr:to>
@@ -1939,7 +2029,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>660400</xdr:colOff>
+      <xdr:colOff>360045</xdr:colOff>
       <xdr:row>132</xdr:row>
       <xdr:rowOff>176530</xdr:rowOff>
     </xdr:to>
@@ -2258,7 +2348,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z135"/>
+  <dimension ref="A1:Z185"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.375"/>
@@ -2267,10 +2357,11 @@
     <col min="4" max="4" width="14.5" style="9" customWidth="1"/>
     <col min="5" max="5" width="16.375" style="7" customWidth="1"/>
     <col min="6" max="6" width="12.25" style="7" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="9"/>
+    <col min="7" max="7" width="12.9416666666667" style="9" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="33" customHeight="1" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="33" customHeight="1" spans="1:26">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2289,56 +2380,65 @@
       <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" s="5" customFormat="1" spans="1:6">
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" s="5" customFormat="1" spans="1:26">
       <c r="A2" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" s="5" customFormat="1" spans="1:6">
+      <c r="G2" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" s="5" customFormat="1" spans="1:26">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" s="5" customFormat="1" spans="2:6">
+        <v>14</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" s="5" customFormat="1" spans="1:26">
       <c r="B4" s="6"/>
       <c r="C4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
     </row>
-    <row r="5" s="5" customFormat="1" spans="1:6">
+    <row r="5" s="5" customFormat="1" spans="1:26">
       <c r="A5" s="5">
-        <f>(B5+500000)*100+C5</f>
+        <f t="shared" ref="A5:A36" si="0">(B5+500000)*100+C5+G5*1000</f>
         <v>60010001</v>
       </c>
       <c r="B5" s="6">
@@ -2351,15 +2451,18 @@
         <v>1</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F5" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26">
       <c r="A6" s="5">
-        <f t="shared" ref="A6:A37" si="0">(B6+500000)*100+C6</f>
+        <f t="shared" si="0"/>
         <v>60010002</v>
       </c>
       <c r="B6" s="6">
@@ -2372,14 +2475,16 @@
         <v>1</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F6" s="7">
         <v>5</v>
       </c>
-      <c r="G6" s="5"/>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26">
       <c r="A7" s="5">
         <f t="shared" si="0"/>
         <v>60010003</v>
@@ -2394,14 +2499,16 @@
         <v>1</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F7" s="7">
         <v>5</v>
       </c>
-      <c r="G7" s="5"/>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26">
       <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>60010004</v>
@@ -2416,14 +2523,16 @@
         <v>1</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F8" s="7">
         <v>5</v>
       </c>
-      <c r="G8" s="5"/>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26">
       <c r="A9" s="5">
         <f t="shared" si="0"/>
         <v>60010005</v>
@@ -2438,14 +2547,16 @@
         <v>1</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F9" s="7">
         <v>5</v>
       </c>
-      <c r="G9" s="5"/>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26">
       <c r="A10" s="5">
         <f t="shared" si="0"/>
         <v>60010006</v>
@@ -2460,14 +2571,16 @@
         <v>1</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F10" s="7">
         <v>5</v>
       </c>
-      <c r="G10" s="5"/>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26">
       <c r="A11" s="5">
         <f t="shared" si="0"/>
         <v>60010007</v>
@@ -2482,14 +2595,16 @@
         <v>1</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F11" s="7">
         <v>5</v>
       </c>
-      <c r="G11" s="5"/>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26">
       <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>60010008</v>
@@ -2504,14 +2619,16 @@
         <v>1</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F12" s="7">
         <v>5</v>
       </c>
-      <c r="G12" s="5"/>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26">
       <c r="A13" s="5">
         <f t="shared" si="0"/>
         <v>60010009</v>
@@ -2526,14 +2643,16 @@
         <v>1</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F13" s="7">
         <v>5</v>
       </c>
-      <c r="G13" s="5"/>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26">
       <c r="A14" s="5">
         <f t="shared" si="0"/>
         <v>60010010</v>
@@ -2548,14 +2667,16 @@
         <v>1</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F14" s="7">
         <v>5</v>
       </c>
-      <c r="G14" s="5"/>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26">
       <c r="A15" s="5">
         <f t="shared" si="0"/>
         <v>60010011</v>
@@ -2570,12 +2691,14 @@
         <v>1</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F15" s="7">
         <v>5</v>
       </c>
-      <c r="G15" s="5"/>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:26">
       <c r="A16" s="5">
@@ -2592,12 +2715,14 @@
         <v>1</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F16" s="7">
         <v>5</v>
       </c>
-      <c r="G16" s="5"/>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
       <c r="L16"/>
       <c r="M16"/>
       <c r="N16"/>
@@ -2629,12 +2754,14 @@
         <v>1</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F17" s="7">
         <v>5</v>
       </c>
-      <c r="G17" s="5"/>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
       <c r="L17"/>
       <c r="M17"/>
       <c r="N17"/>
@@ -2666,12 +2793,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F18" s="7">
         <v>5</v>
       </c>
-      <c r="G18" s="5"/>
+      <c r="G18" s="5">
+        <v>0</v>
+      </c>
       <c r="L18"/>
       <c r="M18"/>
       <c r="N18"/>
@@ -2703,12 +2832,14 @@
         <v>1</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F19" s="7">
         <v>5</v>
       </c>
-      <c r="G19" s="5"/>
+      <c r="G19" s="5">
+        <v>0</v>
+      </c>
       <c r="L19"/>
       <c r="M19"/>
       <c r="N19"/>
@@ -2740,12 +2871,14 @@
         <v>1</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F20" s="7">
         <v>5</v>
       </c>
-      <c r="G20" s="5"/>
+      <c r="G20" s="5">
+        <v>0</v>
+      </c>
       <c r="L20"/>
       <c r="M20"/>
       <c r="N20"/>
@@ -2777,12 +2910,14 @@
         <v>1</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F21" s="7">
         <v>5</v>
       </c>
-      <c r="G21" s="5"/>
+      <c r="G21" s="5">
+        <v>0</v>
+      </c>
       <c r="L21"/>
       <c r="M21"/>
       <c r="N21"/>
@@ -2814,12 +2949,14 @@
         <v>1</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F22" s="7">
         <v>5</v>
       </c>
-      <c r="G22" s="5"/>
+      <c r="G22" s="5">
+        <v>0</v>
+      </c>
       <c r="L22"/>
       <c r="M22"/>
       <c r="N22"/>
@@ -2851,12 +2988,14 @@
         <v>1</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F23" s="7">
         <v>5</v>
       </c>
-      <c r="G23" s="5"/>
+      <c r="G23" s="5">
+        <v>0</v>
+      </c>
       <c r="L23"/>
       <c r="M23"/>
       <c r="N23"/>
@@ -2888,12 +3027,14 @@
         <v>1</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F24" s="7">
         <v>5</v>
       </c>
-      <c r="G24" s="5"/>
+      <c r="G24" s="5">
+        <v>0</v>
+      </c>
       <c r="L24"/>
       <c r="M24"/>
       <c r="N24"/>
@@ -2910,7 +3051,7 @@
       <c r="Y24"/>
       <c r="Z24"/>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:26">
       <c r="A25" s="5">
         <f t="shared" si="0"/>
         <v>60010021</v>
@@ -2925,14 +3066,16 @@
         <v>1</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F25" s="7">
         <v>5</v>
       </c>
-      <c r="G25" s="5"/>
-    </row>
-    <row r="26" spans="1:7">
+      <c r="G25" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26">
       <c r="A26" s="5">
         <f t="shared" si="0"/>
         <v>60010022</v>
@@ -2947,14 +3090,16 @@
         <v>1</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F26" s="7">
         <v>5</v>
       </c>
-      <c r="G26" s="5"/>
-    </row>
-    <row r="27" spans="1:7">
+      <c r="G26" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26">
       <c r="A27" s="5">
         <f t="shared" si="0"/>
         <v>60010023</v>
@@ -2969,14 +3114,16 @@
         <v>1</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F27" s="7">
         <v>5</v>
       </c>
-      <c r="G27" s="5"/>
-    </row>
-    <row r="28" spans="1:7">
+      <c r="G27" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26">
       <c r="A28" s="5">
         <f t="shared" si="0"/>
         <v>60010024</v>
@@ -2991,14 +3138,16 @@
         <v>1</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F28" s="7">
         <v>5</v>
       </c>
-      <c r="G28" s="5"/>
-    </row>
-    <row r="29" spans="1:7">
+      <c r="G28" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26">
       <c r="A29" s="5">
         <f t="shared" si="0"/>
         <v>60010025</v>
@@ -3013,14 +3162,16 @@
         <v>1</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F29" s="7">
         <v>5</v>
       </c>
-      <c r="G29" s="5"/>
-    </row>
-    <row r="30" spans="1:7">
+      <c r="G29" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:26">
       <c r="A30" s="5">
         <f t="shared" si="0"/>
         <v>60010026</v>
@@ -3035,14 +3186,16 @@
         <v>1</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F30" s="7">
         <v>5</v>
       </c>
-      <c r="G30" s="5"/>
-    </row>
-    <row r="31" spans="1:7">
+      <c r="G30" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:26">
       <c r="A31" s="5">
         <f t="shared" si="0"/>
         <v>60010027</v>
@@ -3057,14 +3210,16 @@
         <v>1</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F31" s="7">
         <v>5</v>
       </c>
-      <c r="G31" s="5"/>
-    </row>
-    <row r="32" spans="1:7">
+      <c r="G31" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26">
       <c r="A32" s="5">
         <f t="shared" si="0"/>
         <v>60010028</v>
@@ -3079,12 +3234,14 @@
         <v>1</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F32" s="7">
         <v>5</v>
       </c>
-      <c r="G32" s="5"/>
+      <c r="G32" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="5">
@@ -3101,12 +3258,14 @@
         <v>1</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F33" s="7">
         <v>5</v>
       </c>
-      <c r="G33" s="5"/>
+      <c r="G33" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="5">
@@ -3123,12 +3282,14 @@
         <v>1</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F34" s="7">
         <v>5</v>
       </c>
-      <c r="G34" s="5"/>
+      <c r="G34" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="5">
@@ -3145,12 +3306,14 @@
         <v>1</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F35" s="7">
         <v>5</v>
       </c>
-      <c r="G35" s="5"/>
+      <c r="G35" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="5">
@@ -3167,16 +3330,18 @@
         <v>1</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F36" s="7">
         <v>5</v>
       </c>
-      <c r="G36" s="5"/>
+      <c r="G36" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A37:A68" si="1">(B37+500000)*100+C37+G37*1000</f>
         <v>60010033</v>
       </c>
       <c r="B37" s="6">
@@ -3189,16 +3354,18 @@
         <v>1</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F37" s="7">
         <v>5</v>
       </c>
-      <c r="G37" s="5"/>
+      <c r="G37" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="5">
-        <f t="shared" ref="A38:A56" si="1">(B38+500000)*100+C38</f>
+        <f t="shared" si="1"/>
         <v>60010034</v>
       </c>
       <c r="B38" s="6">
@@ -3211,12 +3378,14 @@
         <v>1</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F38" s="7">
         <v>5</v>
       </c>
-      <c r="G38" s="5"/>
+      <c r="G38" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="5">
@@ -3233,12 +3402,14 @@
         <v>1</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F39" s="7">
         <v>5</v>
       </c>
-      <c r="G39" s="5"/>
+      <c r="G39" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="5">
@@ -3255,12 +3426,14 @@
         <v>1</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F40" s="7">
         <v>5</v>
       </c>
-      <c r="G40" s="5"/>
+      <c r="G40" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="5">
@@ -3277,12 +3450,14 @@
         <v>1</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F41" s="7">
         <v>5</v>
       </c>
-      <c r="G41" s="5"/>
+      <c r="G41" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="5">
@@ -3299,12 +3474,14 @@
         <v>1</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F42" s="7">
         <v>5</v>
       </c>
-      <c r="G42" s="5"/>
+      <c r="G42" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="5">
@@ -3321,12 +3498,14 @@
         <v>1</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F43" s="7">
         <v>5</v>
       </c>
-      <c r="G43" s="5"/>
+      <c r="G43" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="5">
@@ -3343,12 +3522,14 @@
         <v>1</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F44" s="7">
         <v>5</v>
       </c>
-      <c r="G44" s="5"/>
+      <c r="G44" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="5">
@@ -3365,12 +3546,14 @@
         <v>1</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F45" s="7">
         <v>5</v>
       </c>
-      <c r="G45" s="5"/>
+      <c r="G45" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="5">
@@ -3387,12 +3570,14 @@
         <v>1</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F46" s="7">
         <v>5</v>
       </c>
-      <c r="G46" s="5"/>
+      <c r="G46" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="5">
@@ -3409,12 +3594,14 @@
         <v>1</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F47" s="7">
         <v>5</v>
       </c>
-      <c r="G47" s="5"/>
+      <c r="G47" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="5">
@@ -3431,14 +3618,16 @@
         <v>1</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F48" s="7">
         <v>5</v>
       </c>
-      <c r="G48" s="5"/>
-    </row>
-    <row r="49" spans="1:7">
+      <c r="G48" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" s="5">
         <f t="shared" si="1"/>
         <v>60010045</v>
@@ -3453,14 +3642,16 @@
         <v>1</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F49" s="7">
         <v>5</v>
       </c>
-      <c r="G49" s="5"/>
-    </row>
-    <row r="50" spans="1:7">
+      <c r="G49" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50" s="5">
         <f t="shared" si="1"/>
         <v>60010046</v>
@@ -3475,14 +3666,16 @@
         <v>1</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F50" s="7">
         <v>5</v>
       </c>
-      <c r="G50" s="5"/>
-    </row>
-    <row r="51" spans="1:7">
+      <c r="G50" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" s="5">
         <f t="shared" si="1"/>
         <v>60010047</v>
@@ -3497,14 +3690,16 @@
         <v>1</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F51" s="7">
         <v>5</v>
       </c>
-      <c r="G51" s="5"/>
-    </row>
-    <row r="52" spans="1:7">
+      <c r="G51" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
       <c r="A52" s="5">
         <f t="shared" si="1"/>
         <v>60010048</v>
@@ -3519,14 +3714,16 @@
         <v>1</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F52" s="7">
         <v>5</v>
       </c>
-      <c r="G52" s="5"/>
-    </row>
-    <row r="53" spans="1:7">
+      <c r="G52" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
       <c r="A53" s="5">
         <f t="shared" si="1"/>
         <v>60010049</v>
@@ -3541,14 +3738,16 @@
         <v>1</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F53" s="7">
         <v>5</v>
       </c>
-      <c r="G53" s="5"/>
-    </row>
-    <row r="54" spans="1:7">
+      <c r="G53" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
       <c r="A54" s="5">
         <f t="shared" si="1"/>
         <v>60010050</v>
@@ -3563,756 +3762,850 @@
         <v>1</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F54" s="7">
         <v>5</v>
       </c>
-      <c r="G54" s="5"/>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55" s="11">
+      <c r="G54" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="5">
         <f t="shared" si="1"/>
         <v>60030001</v>
       </c>
-      <c r="B55" s="12">
+      <c r="B55" s="11">
         <v>100300</v>
       </c>
-      <c r="C55" s="13">
-        <v>1</v>
-      </c>
-      <c r="D55" s="13">
-        <v>1</v>
-      </c>
-      <c r="E55" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="F55" s="13">
-        <v>5</v>
-      </c>
-      <c r="G55" s="5"/>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56" s="14">
+      <c r="C55" s="12">
+        <v>1</v>
+      </c>
+      <c r="D55" s="12">
+        <v>1</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="F55" s="12">
+        <v>5</v>
+      </c>
+      <c r="G55" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="5">
         <f t="shared" si="1"/>
         <v>60120001</v>
       </c>
-      <c r="B56" s="15">
+      <c r="B56" s="13">
         <v>101200</v>
       </c>
-      <c r="C56" s="16">
-        <v>1</v>
-      </c>
-      <c r="D56" s="16">
-        <v>1</v>
-      </c>
-      <c r="E56" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="F56" s="16">
-        <v>5</v>
-      </c>
-      <c r="G56" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57" s="14">
-        <f t="shared" ref="A57:A120" si="2">(B57+500000)*100+C57</f>
+      <c r="C56" s="14">
+        <v>1</v>
+      </c>
+      <c r="D56" s="14">
+        <v>1</v>
+      </c>
+      <c r="E56" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="F56" s="14">
+        <v>5</v>
+      </c>
+      <c r="G56" s="5">
+        <v>0</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="5">
+        <f t="shared" si="1"/>
         <v>60120002</v>
       </c>
-      <c r="B57" s="15">
+      <c r="B57" s="13">
         <v>101200</v>
       </c>
-      <c r="C57" s="16">
+      <c r="C57" s="14">
         <v>2</v>
       </c>
-      <c r="D57" s="16">
-        <v>1</v>
-      </c>
-      <c r="E57" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="F57" s="16">
-        <v>5</v>
-      </c>
-      <c r="G57" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58" s="14">
-        <f t="shared" si="2"/>
+      <c r="D57" s="14">
+        <v>1</v>
+      </c>
+      <c r="E57" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="F57" s="14">
+        <v>5</v>
+      </c>
+      <c r="G57" s="5">
+        <v>0</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="5">
+        <f t="shared" si="1"/>
         <v>60120003</v>
       </c>
-      <c r="B58" s="15">
+      <c r="B58" s="13">
         <v>101200</v>
       </c>
-      <c r="C58" s="16">
+      <c r="C58" s="14">
         <v>3</v>
       </c>
-      <c r="D58" s="16">
-        <v>1</v>
-      </c>
-      <c r="E58" s="16" t="s">
+      <c r="D58" s="14">
+        <v>1</v>
+      </c>
+      <c r="E58" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F58" s="14">
+        <v>5</v>
+      </c>
+      <c r="G58" s="5">
+        <v>0</v>
+      </c>
+      <c r="H58" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="F58" s="16">
-        <v>5</v>
-      </c>
-      <c r="G58" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59" s="14">
-        <f t="shared" si="2"/>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="5">
+        <f t="shared" si="1"/>
         <v>60120004</v>
       </c>
-      <c r="B59" s="15">
+      <c r="B59" s="13">
         <v>101200</v>
       </c>
-      <c r="C59" s="16">
+      <c r="C59" s="14">
         <v>4</v>
       </c>
-      <c r="D59" s="16">
-        <v>1</v>
-      </c>
-      <c r="E59" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="F59" s="16">
-        <v>5</v>
-      </c>
-      <c r="G59" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60" s="14">
-        <f t="shared" si="2"/>
+      <c r="D59" s="14">
+        <v>1</v>
+      </c>
+      <c r="E59" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="F59" s="14">
+        <v>5</v>
+      </c>
+      <c r="G59" s="5">
+        <v>0</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="5">
+        <f t="shared" si="1"/>
         <v>60120005</v>
       </c>
-      <c r="B60" s="15">
+      <c r="B60" s="13">
         <v>101200</v>
       </c>
-      <c r="C60" s="16">
-        <v>5</v>
-      </c>
-      <c r="D60" s="16">
-        <v>1</v>
-      </c>
-      <c r="E60" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="F60" s="16">
-        <v>5</v>
-      </c>
-      <c r="G60" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="A61" s="14">
-        <f t="shared" si="2"/>
+      <c r="C60" s="14">
+        <v>5</v>
+      </c>
+      <c r="D60" s="14">
+        <v>1</v>
+      </c>
+      <c r="E60" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="F60" s="14">
+        <v>5</v>
+      </c>
+      <c r="G60" s="5">
+        <v>0</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="5">
+        <f t="shared" si="1"/>
         <v>60120006</v>
       </c>
-      <c r="B61" s="15">
+      <c r="B61" s="13">
         <v>101200</v>
       </c>
-      <c r="C61" s="16">
+      <c r="C61" s="14">
         <v>6</v>
       </c>
-      <c r="D61" s="16">
-        <v>1</v>
-      </c>
-      <c r="E61" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="F61" s="16">
-        <v>5</v>
-      </c>
-      <c r="G61" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
-      <c r="A62" s="14">
-        <f t="shared" si="2"/>
+      <c r="D61" s="14">
+        <v>1</v>
+      </c>
+      <c r="E61" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="F61" s="14">
+        <v>5</v>
+      </c>
+      <c r="G61" s="5">
+        <v>0</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="5">
+        <f t="shared" si="1"/>
         <v>60120007</v>
       </c>
-      <c r="B62" s="15">
+      <c r="B62" s="13">
         <v>101200</v>
       </c>
-      <c r="C62" s="16">
+      <c r="C62" s="14">
         <v>7</v>
       </c>
-      <c r="D62" s="16">
-        <v>1</v>
-      </c>
-      <c r="E62" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="F62" s="16">
-        <v>5</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
-      <c r="A63" s="14">
-        <f t="shared" si="2"/>
+      <c r="D62" s="14">
+        <v>1</v>
+      </c>
+      <c r="E62" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F62" s="14">
+        <v>5</v>
+      </c>
+      <c r="G62" s="5">
+        <v>0</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="5">
+        <f t="shared" si="1"/>
         <v>60120008</v>
       </c>
-      <c r="B63" s="15">
+      <c r="B63" s="13">
         <v>101200</v>
       </c>
-      <c r="C63" s="16">
+      <c r="C63" s="14">
         <v>8</v>
       </c>
-      <c r="D63" s="16">
-        <v>1</v>
-      </c>
-      <c r="E63" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="F63" s="16">
-        <v>5</v>
-      </c>
-      <c r="G63" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64" s="14">
-        <f t="shared" si="2"/>
+      <c r="D63" s="14">
+        <v>1</v>
+      </c>
+      <c r="E63" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="F63" s="14">
+        <v>5</v>
+      </c>
+      <c r="G63" s="5">
+        <v>0</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="5">
+        <f t="shared" si="1"/>
         <v>60120009</v>
       </c>
-      <c r="B64" s="15">
+      <c r="B64" s="13">
         <v>101200</v>
       </c>
-      <c r="C64" s="16">
+      <c r="C64" s="14">
         <v>9</v>
       </c>
-      <c r="D64" s="16">
-        <v>1</v>
-      </c>
-      <c r="E64" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="F64" s="16">
-        <v>5</v>
-      </c>
-      <c r="G64" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
-      <c r="A65" s="14">
-        <f t="shared" si="2"/>
+      <c r="D64" s="14">
+        <v>1</v>
+      </c>
+      <c r="E64" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F64" s="14">
+        <v>5</v>
+      </c>
+      <c r="G64" s="5">
+        <v>0</v>
+      </c>
+      <c r="H64" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="5">
+        <f t="shared" si="1"/>
         <v>60120010</v>
       </c>
-      <c r="B65" s="15">
+      <c r="B65" s="13">
         <v>101200</v>
       </c>
-      <c r="C65" s="16">
+      <c r="C65" s="14">
         <v>10</v>
       </c>
-      <c r="D65" s="16">
-        <v>1</v>
-      </c>
-      <c r="E65" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="F65" s="16">
-        <v>5</v>
-      </c>
-      <c r="G65" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
-      <c r="A66" s="14">
-        <f t="shared" si="2"/>
+      <c r="D65" s="14">
+        <v>1</v>
+      </c>
+      <c r="E65" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="F65" s="14">
+        <v>5</v>
+      </c>
+      <c r="G65" s="5">
+        <v>0</v>
+      </c>
+      <c r="H65" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="5">
+        <f t="shared" si="1"/>
         <v>60120011</v>
       </c>
-      <c r="B66" s="15">
+      <c r="B66" s="13">
         <v>101200</v>
       </c>
-      <c r="C66" s="16">
+      <c r="C66" s="14">
         <v>11</v>
       </c>
-      <c r="D66" s="16">
-        <v>1</v>
-      </c>
-      <c r="E66" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="F66" s="16">
-        <v>5</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
-      <c r="A67" s="14">
-        <f t="shared" si="2"/>
+      <c r="D66" s="14">
+        <v>1</v>
+      </c>
+      <c r="E66" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F66" s="14">
+        <v>5</v>
+      </c>
+      <c r="G66" s="5">
+        <v>0</v>
+      </c>
+      <c r="H66" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="5">
+        <f t="shared" si="1"/>
         <v>60120012</v>
       </c>
-      <c r="B67" s="15">
+      <c r="B67" s="13">
         <v>101200</v>
       </c>
-      <c r="C67" s="16">
+      <c r="C67" s="14">
         <v>12</v>
       </c>
-      <c r="D67" s="16">
-        <v>1</v>
-      </c>
-      <c r="E67" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="F67" s="16">
-        <v>5</v>
-      </c>
-      <c r="G67" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
-      <c r="A68" s="14">
-        <f t="shared" si="2"/>
+      <c r="D67" s="14">
+        <v>1</v>
+      </c>
+      <c r="E67" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F67" s="14">
+        <v>5</v>
+      </c>
+      <c r="G67" s="5">
+        <v>0</v>
+      </c>
+      <c r="H67" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="5">
+        <f t="shared" si="1"/>
         <v>60120013</v>
       </c>
-      <c r="B68" s="15">
+      <c r="B68" s="13">
         <v>101200</v>
       </c>
-      <c r="C68" s="16">
+      <c r="C68" s="14">
         <v>13</v>
       </c>
-      <c r="D68" s="16">
-        <v>1</v>
-      </c>
-      <c r="E68" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="F68" s="16">
-        <v>5</v>
-      </c>
-      <c r="G68" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
-      <c r="A69" s="14">
-        <f t="shared" si="2"/>
+      <c r="D68" s="14">
+        <v>1</v>
+      </c>
+      <c r="E68" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="F68" s="14">
+        <v>5</v>
+      </c>
+      <c r="G68" s="5">
+        <v>0</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="5">
+        <f t="shared" ref="A69:A86" si="2">(B69+500000)*100+C69+G69*1000</f>
         <v>60120014</v>
       </c>
-      <c r="B69" s="15">
+      <c r="B69" s="13">
         <v>101200</v>
       </c>
-      <c r="C69" s="16">
+      <c r="C69" s="14">
         <v>14</v>
       </c>
-      <c r="D69" s="16">
-        <v>1</v>
-      </c>
-      <c r="E69" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="F69" s="16">
-        <v>5</v>
-      </c>
-      <c r="G69" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="A70" s="14">
+      <c r="D69" s="14">
+        <v>1</v>
+      </c>
+      <c r="E69" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F69" s="14">
+        <v>5</v>
+      </c>
+      <c r="G69" s="5">
+        <v>0</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="5">
         <f t="shared" si="2"/>
         <v>60120015</v>
       </c>
-      <c r="B70" s="15">
+      <c r="B70" s="13">
         <v>101200</v>
       </c>
-      <c r="C70" s="16">
+      <c r="C70" s="14">
         <v>15</v>
       </c>
-      <c r="D70" s="16">
-        <v>1</v>
-      </c>
-      <c r="E70" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="F70" s="16">
-        <v>5</v>
-      </c>
-      <c r="G70" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7">
-      <c r="A71" s="14">
+      <c r="D70" s="14">
+        <v>1</v>
+      </c>
+      <c r="E70" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F70" s="14">
+        <v>5</v>
+      </c>
+      <c r="G70" s="5">
+        <v>0</v>
+      </c>
+      <c r="H70" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="5">
         <f t="shared" si="2"/>
         <v>60120016</v>
       </c>
-      <c r="B71" s="15">
+      <c r="B71" s="13">
         <v>101200</v>
       </c>
-      <c r="C71" s="16">
+      <c r="C71" s="14">
         <v>16</v>
       </c>
-      <c r="D71" s="16">
+      <c r="D71" s="14">
         <v>2</v>
       </c>
-      <c r="E71" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="F71" s="16">
-        <v>5</v>
-      </c>
-      <c r="G71" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7">
-      <c r="A72" s="14">
+      <c r="E71" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="F71" s="14">
+        <v>5</v>
+      </c>
+      <c r="G71" s="5">
+        <v>0</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="5">
         <f t="shared" si="2"/>
         <v>60120017</v>
       </c>
-      <c r="B72" s="15">
+      <c r="B72" s="13">
         <v>101200</v>
       </c>
-      <c r="C72" s="16">
+      <c r="C72" s="14">
         <v>17</v>
       </c>
-      <c r="D72" s="16">
+      <c r="D72" s="14">
         <v>2</v>
       </c>
-      <c r="E72" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="F72" s="16">
-        <v>5</v>
-      </c>
-      <c r="G72" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7">
-      <c r="A73" s="14">
+      <c r="E72" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="F72" s="14">
+        <v>5</v>
+      </c>
+      <c r="G72" s="5">
+        <v>0</v>
+      </c>
+      <c r="H72" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="5">
         <f t="shared" si="2"/>
         <v>60120018</v>
       </c>
-      <c r="B73" s="15">
+      <c r="B73" s="13">
         <v>101200</v>
       </c>
-      <c r="C73" s="16">
+      <c r="C73" s="14">
         <v>18</v>
       </c>
-      <c r="D73" s="16">
+      <c r="D73" s="14">
         <v>2</v>
       </c>
-      <c r="E73" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="F73" s="16">
-        <v>5</v>
-      </c>
-      <c r="G73" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7">
-      <c r="A74" s="14">
+      <c r="E73" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F73" s="14">
+        <v>5</v>
+      </c>
+      <c r="G73" s="5">
+        <v>0</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="5">
         <f t="shared" si="2"/>
         <v>60120019</v>
       </c>
-      <c r="B74" s="15">
+      <c r="B74" s="13">
         <v>101200</v>
       </c>
-      <c r="C74" s="16">
+      <c r="C74" s="14">
         <v>19</v>
       </c>
-      <c r="D74" s="16">
+      <c r="D74" s="14">
         <v>2</v>
       </c>
-      <c r="E74" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="F74" s="16">
-        <v>5</v>
-      </c>
-      <c r="G74" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7">
-      <c r="A75" s="14">
+      <c r="E74" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="F74" s="14">
+        <v>5</v>
+      </c>
+      <c r="G74" s="5">
+        <v>0</v>
+      </c>
+      <c r="H74" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="5">
         <f t="shared" si="2"/>
         <v>60120020</v>
       </c>
-      <c r="B75" s="15">
+      <c r="B75" s="13">
         <v>101200</v>
       </c>
-      <c r="C75" s="16">
+      <c r="C75" s="14">
         <v>20</v>
       </c>
-      <c r="D75" s="16">
+      <c r="D75" s="14">
         <v>2</v>
       </c>
-      <c r="E75" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="F75" s="16">
-        <v>5</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7">
-      <c r="A76" s="14">
+      <c r="E75" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="F75" s="14">
+        <v>5</v>
+      </c>
+      <c r="G75" s="5">
+        <v>0</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="5">
         <f t="shared" si="2"/>
         <v>60120021</v>
       </c>
-      <c r="B76" s="15">
+      <c r="B76" s="13">
         <v>101200</v>
       </c>
-      <c r="C76" s="16">
+      <c r="C76" s="14">
         <v>21</v>
       </c>
-      <c r="D76" s="16">
+      <c r="D76" s="14">
         <v>2</v>
       </c>
-      <c r="E76" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="F76" s="16">
-        <v>5</v>
-      </c>
-      <c r="G76" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7">
-      <c r="A77" s="14">
+      <c r="E76" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="F76" s="14">
+        <v>5</v>
+      </c>
+      <c r="G76" s="5">
+        <v>0</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="5">
         <f t="shared" si="2"/>
         <v>60120022</v>
       </c>
-      <c r="B77" s="15">
+      <c r="B77" s="13">
         <v>101200</v>
       </c>
-      <c r="C77" s="16">
+      <c r="C77" s="14">
         <v>22</v>
       </c>
-      <c r="D77" s="16">
+      <c r="D77" s="14">
         <v>2</v>
       </c>
-      <c r="E77" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="F77" s="16">
-        <v>5</v>
-      </c>
-      <c r="G77" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
-      <c r="A78" s="14">
+      <c r="E77" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F77" s="14">
+        <v>5</v>
+      </c>
+      <c r="G77" s="5">
+        <v>0</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="5">
         <f t="shared" si="2"/>
         <v>60120023</v>
       </c>
-      <c r="B78" s="15">
+      <c r="B78" s="13">
         <v>101200</v>
       </c>
-      <c r="C78" s="16">
+      <c r="C78" s="14">
         <v>23</v>
       </c>
-      <c r="D78" s="16">
+      <c r="D78" s="14">
         <v>2</v>
       </c>
-      <c r="E78" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="F78" s="16">
-        <v>5</v>
-      </c>
-      <c r="G78" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7">
-      <c r="A79" s="14">
+      <c r="E78" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="F78" s="14">
+        <v>5</v>
+      </c>
+      <c r="G78" s="5">
+        <v>0</v>
+      </c>
+      <c r="H78" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="5">
         <f t="shared" si="2"/>
         <v>60120024</v>
       </c>
-      <c r="B79" s="15">
+      <c r="B79" s="13">
         <v>101200</v>
       </c>
-      <c r="C79" s="16">
+      <c r="C79" s="14">
         <v>24</v>
       </c>
-      <c r="D79" s="16">
+      <c r="D79" s="14">
         <v>2</v>
       </c>
-      <c r="E79" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="F79" s="16">
-        <v>5</v>
-      </c>
-      <c r="G79" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7">
-      <c r="A80" s="14">
+      <c r="E79" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F79" s="14">
+        <v>5</v>
+      </c>
+      <c r="G79" s="5">
+        <v>0</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="5">
         <f t="shared" si="2"/>
         <v>60120025</v>
       </c>
-      <c r="B80" s="15">
+      <c r="B80" s="13">
         <v>101200</v>
       </c>
-      <c r="C80" s="16">
+      <c r="C80" s="14">
         <v>25</v>
       </c>
-      <c r="D80" s="16">
+      <c r="D80" s="14">
         <v>2</v>
       </c>
-      <c r="E80" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="F80" s="16">
-        <v>5</v>
-      </c>
-      <c r="G80" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7">
-      <c r="A81" s="14">
+      <c r="E80" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="F80" s="14">
+        <v>5</v>
+      </c>
+      <c r="G80" s="5">
+        <v>0</v>
+      </c>
+      <c r="H80" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" s="5">
         <f t="shared" si="2"/>
         <v>60120026</v>
       </c>
-      <c r="B81" s="15">
+      <c r="B81" s="13">
         <v>101200</v>
       </c>
-      <c r="C81" s="16">
+      <c r="C81" s="14">
         <v>26</v>
       </c>
-      <c r="D81" s="16">
+      <c r="D81" s="14">
         <v>2</v>
       </c>
-      <c r="E81" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="F81" s="16">
-        <v>5</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7">
-      <c r="A82" s="14">
+      <c r="E81" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F81" s="14">
+        <v>5</v>
+      </c>
+      <c r="G81" s="5">
+        <v>0</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" s="5">
         <f t="shared" si="2"/>
         <v>60120027</v>
       </c>
-      <c r="B82" s="15">
+      <c r="B82" s="13">
         <v>101200</v>
       </c>
-      <c r="C82" s="16">
+      <c r="C82" s="14">
         <v>27</v>
       </c>
-      <c r="D82" s="16">
+      <c r="D82" s="14">
         <v>2</v>
       </c>
-      <c r="E82" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="F82" s="16">
-        <v>5</v>
-      </c>
-      <c r="G82" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7">
-      <c r="A83" s="14">
+      <c r="E82" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F82" s="14">
+        <v>5</v>
+      </c>
+      <c r="G82" s="5">
+        <v>0</v>
+      </c>
+      <c r="H82" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" s="5">
         <f t="shared" si="2"/>
         <v>60120028</v>
       </c>
-      <c r="B83" s="15">
+      <c r="B83" s="13">
         <v>101200</v>
       </c>
-      <c r="C83" s="16">
+      <c r="C83" s="14">
         <v>28</v>
       </c>
-      <c r="D83" s="16">
+      <c r="D83" s="14">
         <v>2</v>
       </c>
-      <c r="E83" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="F83" s="16">
-        <v>5</v>
-      </c>
-      <c r="G83" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7">
-      <c r="A84" s="14">
+      <c r="E83" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="F83" s="14">
+        <v>5</v>
+      </c>
+      <c r="G83" s="5">
+        <v>0</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" s="5">
         <f t="shared" si="2"/>
         <v>60120029</v>
       </c>
-      <c r="B84" s="15">
+      <c r="B84" s="13">
         <v>101200</v>
       </c>
-      <c r="C84" s="16">
+      <c r="C84" s="14">
         <v>29</v>
       </c>
-      <c r="D84" s="16">
+      <c r="D84" s="14">
         <v>2</v>
       </c>
-      <c r="E84" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="F84" s="16">
-        <v>5</v>
-      </c>
-      <c r="G84" s="9" t="s">
+      <c r="E84" s="14" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="85" spans="1:7">
-      <c r="A85" s="14">
+      <c r="F84" s="14">
+        <v>5</v>
+      </c>
+      <c r="G84" s="5">
+        <v>0</v>
+      </c>
+      <c r="H84" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" s="5">
         <f t="shared" si="2"/>
         <v>60120030</v>
       </c>
-      <c r="B85" s="15">
+      <c r="B85" s="13">
         <v>101200</v>
       </c>
-      <c r="C85" s="16">
+      <c r="C85" s="14">
         <v>30</v>
       </c>
-      <c r="D85" s="16">
+      <c r="D85" s="14">
         <v>2</v>
       </c>
-      <c r="E85" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="F85" s="16">
-        <v>5</v>
-      </c>
-      <c r="G85" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="86" s="5" customFormat="1" spans="1:6">
+      <c r="E85" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F85" s="14">
+        <v>5</v>
+      </c>
+      <c r="G85" s="5">
+        <v>0</v>
+      </c>
+      <c r="H85" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="86" s="5" customFormat="1" spans="1:8">
       <c r="A86" s="5">
         <f t="shared" si="2"/>
         <v>60240001</v>
@@ -4327,15 +4620,18 @@
         <v>1</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F86" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="87" spans="1:7">
+      <c r="G86" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
       <c r="A87" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A87:A118" si="3">(B87+500000)*100+C87+G87*1000</f>
         <v>60240002</v>
       </c>
       <c r="B87" s="6">
@@ -4348,16 +4644,18 @@
         <v>1</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F87" s="7">
         <v>5</v>
       </c>
-      <c r="G87" s="5"/>
-    </row>
-    <row r="88" spans="1:7">
+      <c r="G87" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
       <c r="A88" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240003</v>
       </c>
       <c r="B88" s="6">
@@ -4370,16 +4668,18 @@
         <v>1</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F88" s="7">
         <v>5</v>
       </c>
-      <c r="G88" s="5"/>
-    </row>
-    <row r="89" spans="1:7">
+      <c r="G88" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
       <c r="A89" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240004</v>
       </c>
       <c r="B89" s="6">
@@ -4392,16 +4692,18 @@
         <v>1</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F89" s="7">
         <v>5</v>
       </c>
-      <c r="G89" s="5"/>
-    </row>
-    <row r="90" spans="1:7">
+      <c r="G89" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
       <c r="A90" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240005</v>
       </c>
       <c r="B90" s="6">
@@ -4414,16 +4716,18 @@
         <v>1</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F90" s="7">
         <v>5</v>
       </c>
-      <c r="G90" s="5"/>
-    </row>
-    <row r="91" spans="1:7">
+      <c r="G90" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
       <c r="A91" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240006</v>
       </c>
       <c r="B91" s="6">
@@ -4436,16 +4740,18 @@
         <v>1</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F91" s="7">
         <v>5</v>
       </c>
-      <c r="G91" s="5"/>
-    </row>
-    <row r="92" spans="1:7">
+      <c r="G91" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
       <c r="A92" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240007</v>
       </c>
       <c r="B92" s="6">
@@ -4458,16 +4764,18 @@
         <v>1</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F92" s="7">
         <v>5</v>
       </c>
-      <c r="G92" s="5"/>
-    </row>
-    <row r="93" spans="1:7">
+      <c r="G92" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
       <c r="A93" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240008</v>
       </c>
       <c r="B93" s="6">
@@ -4480,16 +4788,18 @@
         <v>1</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F93" s="7">
         <v>5</v>
       </c>
-      <c r="G93" s="5"/>
-    </row>
-    <row r="94" spans="1:7">
+      <c r="G93" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
       <c r="A94" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240009</v>
       </c>
       <c r="B94" s="6">
@@ -4502,16 +4812,18 @@
         <v>1</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F94" s="7">
         <v>5</v>
       </c>
-      <c r="G94" s="5"/>
-    </row>
-    <row r="95" spans="1:7">
+      <c r="G94" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
       <c r="A95" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240010</v>
       </c>
       <c r="B95" s="6">
@@ -4524,16 +4836,18 @@
         <v>1</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F95" s="7">
         <v>5</v>
       </c>
-      <c r="G95" s="5"/>
-    </row>
-    <row r="96" spans="1:7">
+      <c r="G95" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
       <c r="A96" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240011</v>
       </c>
       <c r="B96" s="6">
@@ -4546,16 +4860,18 @@
         <v>1</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F96" s="7">
         <v>5</v>
       </c>
-      <c r="G96" s="5"/>
+      <c r="G96" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="97" spans="1:26">
       <c r="A97" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240012</v>
       </c>
       <c r="B97" s="6">
@@ -4568,12 +4884,14 @@
         <v>1</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F97" s="7">
         <v>5</v>
       </c>
-      <c r="G97" s="5"/>
+      <c r="G97" s="5">
+        <v>0</v>
+      </c>
       <c r="L97"/>
       <c r="M97"/>
       <c r="N97"/>
@@ -4592,7 +4910,7 @@
     </row>
     <row r="98" spans="1:26">
       <c r="A98" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240013</v>
       </c>
       <c r="B98" s="6">
@@ -4605,12 +4923,14 @@
         <v>1</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F98" s="7">
         <v>5</v>
       </c>
-      <c r="G98" s="5"/>
+      <c r="G98" s="5">
+        <v>0</v>
+      </c>
       <c r="L98"/>
       <c r="M98"/>
       <c r="N98"/>
@@ -4629,7 +4949,7 @@
     </row>
     <row r="99" spans="1:26">
       <c r="A99" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240014</v>
       </c>
       <c r="B99" s="6">
@@ -4642,12 +4962,14 @@
         <v>1</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F99" s="7">
         <v>5</v>
       </c>
-      <c r="G99" s="5"/>
+      <c r="G99" s="5">
+        <v>0</v>
+      </c>
       <c r="L99"/>
       <c r="M99"/>
       <c r="N99"/>
@@ -4666,7 +4988,7 @@
     </row>
     <row r="100" spans="1:26">
       <c r="A100" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240015</v>
       </c>
       <c r="B100" s="6">
@@ -4679,12 +5001,14 @@
         <v>1</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F100" s="7">
         <v>5</v>
       </c>
-      <c r="G100" s="5"/>
+      <c r="G100" s="5">
+        <v>0</v>
+      </c>
       <c r="L100"/>
       <c r="M100"/>
       <c r="N100"/>
@@ -4703,7 +5027,7 @@
     </row>
     <row r="101" spans="1:26">
       <c r="A101" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240016</v>
       </c>
       <c r="B101" s="6">
@@ -4716,12 +5040,14 @@
         <v>1</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F101" s="7">
         <v>5</v>
       </c>
-      <c r="G101" s="5"/>
+      <c r="G101" s="5">
+        <v>0</v>
+      </c>
       <c r="L101"/>
       <c r="M101"/>
       <c r="N101"/>
@@ -4740,7 +5066,7 @@
     </row>
     <row r="102" spans="1:26">
       <c r="A102" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240017</v>
       </c>
       <c r="B102" s="6">
@@ -4753,12 +5079,14 @@
         <v>1</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F102" s="7">
         <v>5</v>
       </c>
-      <c r="G102" s="5"/>
+      <c r="G102" s="5">
+        <v>0</v>
+      </c>
       <c r="L102"/>
       <c r="M102"/>
       <c r="N102"/>
@@ -4777,7 +5105,7 @@
     </row>
     <row r="103" spans="1:26">
       <c r="A103" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240018</v>
       </c>
       <c r="B103" s="6">
@@ -4790,12 +5118,14 @@
         <v>1</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F103" s="7">
         <v>5</v>
       </c>
-      <c r="G103" s="5"/>
+      <c r="G103" s="5">
+        <v>0</v>
+      </c>
       <c r="L103"/>
       <c r="M103"/>
       <c r="N103"/>
@@ -4814,7 +5144,7 @@
     </row>
     <row r="104" spans="1:26">
       <c r="A104" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240019</v>
       </c>
       <c r="B104" s="6">
@@ -4827,12 +5157,14 @@
         <v>1</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F104" s="7">
         <v>5</v>
       </c>
-      <c r="G104" s="5"/>
+      <c r="G104" s="5">
+        <v>0</v>
+      </c>
       <c r="L104"/>
       <c r="M104"/>
       <c r="N104"/>
@@ -4851,7 +5183,7 @@
     </row>
     <row r="105" spans="1:26">
       <c r="A105" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240020</v>
       </c>
       <c r="B105" s="6">
@@ -4864,12 +5196,14 @@
         <v>1</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F105" s="7">
         <v>5</v>
       </c>
-      <c r="G105" s="5"/>
+      <c r="G105" s="5">
+        <v>0</v>
+      </c>
       <c r="L105"/>
       <c r="M105"/>
       <c r="N105"/>
@@ -4886,9 +5220,9 @@
       <c r="Y105"/>
       <c r="Z105"/>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:26">
       <c r="A106" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240021</v>
       </c>
       <c r="B106" s="6">
@@ -4901,16 +5235,18 @@
         <v>1</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F106" s="7">
         <v>5</v>
       </c>
-      <c r="G106" s="5"/>
-    </row>
-    <row r="107" spans="1:7">
+      <c r="G106" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:26">
       <c r="A107" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240022</v>
       </c>
       <c r="B107" s="6">
@@ -4923,16 +5259,18 @@
         <v>1</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F107" s="7">
         <v>5</v>
       </c>
-      <c r="G107" s="5"/>
-    </row>
-    <row r="108" spans="1:7">
+      <c r="G107" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:26">
       <c r="A108" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240023</v>
       </c>
       <c r="B108" s="6">
@@ -4945,16 +5283,18 @@
         <v>1</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F108" s="7">
         <v>5</v>
       </c>
-      <c r="G108" s="5"/>
-    </row>
-    <row r="109" spans="1:7">
+      <c r="G108" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:26">
       <c r="A109" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240024</v>
       </c>
       <c r="B109" s="6">
@@ -4967,16 +5307,18 @@
         <v>1</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F109" s="7">
         <v>5</v>
       </c>
-      <c r="G109" s="5"/>
-    </row>
-    <row r="110" spans="1:7">
+      <c r="G109" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:26">
       <c r="A110" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240025</v>
       </c>
       <c r="B110" s="6">
@@ -4989,16 +5331,18 @@
         <v>1</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F110" s="7">
         <v>5</v>
       </c>
-      <c r="G110" s="5"/>
-    </row>
-    <row r="111" spans="1:7">
+      <c r="G110" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:26">
       <c r="A111" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240026</v>
       </c>
       <c r="B111" s="6">
@@ -5011,16 +5355,18 @@
         <v>1</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F111" s="7">
         <v>5</v>
       </c>
-      <c r="G111" s="5"/>
-    </row>
-    <row r="112" spans="1:7">
+      <c r="G111" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:26">
       <c r="A112" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240027</v>
       </c>
       <c r="B112" s="6">
@@ -5033,16 +5379,18 @@
         <v>1</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F112" s="7">
         <v>5</v>
       </c>
-      <c r="G112" s="5"/>
+      <c r="G112" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240028</v>
       </c>
       <c r="B113" s="6">
@@ -5055,16 +5403,18 @@
         <v>1</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F113" s="7">
         <v>5</v>
       </c>
-      <c r="G113" s="5"/>
+      <c r="G113" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240029</v>
       </c>
       <c r="B114" s="6">
@@ -5077,16 +5427,18 @@
         <v>1</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F114" s="7">
         <v>5</v>
       </c>
-      <c r="G114" s="5"/>
+      <c r="G114" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240030</v>
       </c>
       <c r="B115" s="6">
@@ -5099,16 +5451,18 @@
         <v>1</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F115" s="7">
         <v>5</v>
       </c>
-      <c r="G115" s="5"/>
+      <c r="G115" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240031</v>
       </c>
       <c r="B116" s="6">
@@ -5121,16 +5475,18 @@
         <v>1</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F116" s="7">
         <v>5</v>
       </c>
-      <c r="G116" s="5"/>
+      <c r="G116" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240032</v>
       </c>
       <c r="B117" s="6">
@@ -5143,16 +5499,18 @@
         <v>1</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F117" s="7">
         <v>5</v>
       </c>
-      <c r="G117" s="5"/>
+      <c r="G117" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60240033</v>
       </c>
       <c r="B118" s="6">
@@ -5165,16 +5523,18 @@
         <v>1</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F118" s="7">
         <v>5</v>
       </c>
-      <c r="G118" s="5"/>
+      <c r="G118" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A119:A150" si="4">(B119+500000)*100+C119+G119*1000</f>
         <v>60240034</v>
       </c>
       <c r="B119" s="6">
@@ -5187,16 +5547,18 @@
         <v>1</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F119" s="7">
         <v>5</v>
       </c>
-      <c r="G119" s="5"/>
+      <c r="G119" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>60240035</v>
       </c>
       <c r="B120" s="6">
@@ -5209,16 +5571,18 @@
         <v>1</v>
       </c>
       <c r="E120" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F120" s="7">
         <v>5</v>
       </c>
-      <c r="G120" s="5"/>
+      <c r="G120" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="5">
-        <f t="shared" ref="A121:A135" si="3">(B121+500000)*100+C121</f>
+        <f t="shared" si="4"/>
         <v>60240036</v>
       </c>
       <c r="B121" s="6">
@@ -5231,16 +5595,18 @@
         <v>1</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F121" s="7">
         <v>5</v>
       </c>
-      <c r="G121" s="5"/>
+      <c r="G121" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>60240037</v>
       </c>
       <c r="B122" s="6">
@@ -5253,16 +5619,18 @@
         <v>1</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F122" s="7">
         <v>5</v>
       </c>
-      <c r="G122" s="5"/>
+      <c r="G122" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>60240038</v>
       </c>
       <c r="B123" s="6">
@@ -5275,16 +5643,18 @@
         <v>1</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F123" s="7">
         <v>5</v>
       </c>
-      <c r="G123" s="5"/>
+      <c r="G123" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>60240039</v>
       </c>
       <c r="B124" s="6">
@@ -5297,16 +5667,18 @@
         <v>1</v>
       </c>
       <c r="E124" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F124" s="7">
         <v>5</v>
       </c>
-      <c r="G124" s="5"/>
+      <c r="G124" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>60240040</v>
       </c>
       <c r="B125" s="6">
@@ -5319,16 +5691,18 @@
         <v>1</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F125" s="7">
         <v>5</v>
       </c>
-      <c r="G125" s="5"/>
+      <c r="G125" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>60240041</v>
       </c>
       <c r="B126" s="6">
@@ -5341,16 +5715,18 @@
         <v>1</v>
       </c>
       <c r="E126" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F126" s="7">
         <v>5</v>
       </c>
-      <c r="G126" s="5"/>
+      <c r="G126" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>60240042</v>
       </c>
       <c r="B127" s="6">
@@ -5363,16 +5739,18 @@
         <v>1</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F127" s="7">
         <v>5</v>
       </c>
-      <c r="G127" s="5"/>
+      <c r="G127" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>60240043</v>
       </c>
       <c r="B128" s="6">
@@ -5385,16 +5763,18 @@
         <v>1</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F128" s="7">
         <v>5</v>
       </c>
-      <c r="G128" s="5"/>
+      <c r="G128" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>60240044</v>
       </c>
       <c r="B129" s="6">
@@ -5407,16 +5787,18 @@
         <v>1</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F129" s="7">
         <v>5</v>
       </c>
-      <c r="G129" s="5"/>
+      <c r="G129" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>60240045</v>
       </c>
       <c r="B130" s="6">
@@ -5429,16 +5811,18 @@
         <v>1</v>
       </c>
       <c r="E130" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F130" s="7">
         <v>5</v>
       </c>
-      <c r="G130" s="5"/>
+      <c r="G130" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>60240046</v>
       </c>
       <c r="B131" s="6">
@@ -5451,16 +5835,18 @@
         <v>1</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F131" s="7">
         <v>5</v>
       </c>
-      <c r="G131" s="5"/>
+      <c r="G131" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>60240047</v>
       </c>
       <c r="B132" s="6">
@@ -5473,16 +5859,18 @@
         <v>1</v>
       </c>
       <c r="E132" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F132" s="7">
         <v>5</v>
       </c>
-      <c r="G132" s="5"/>
+      <c r="G132" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>60240048</v>
       </c>
       <c r="B133" s="6">
@@ -5495,16 +5883,18 @@
         <v>1</v>
       </c>
       <c r="E133" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F133" s="7">
         <v>5</v>
       </c>
-      <c r="G133" s="5"/>
+      <c r="G133" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>60240049</v>
       </c>
       <c r="B134" s="6">
@@ -5517,16 +5907,18 @@
         <v>1</v>
       </c>
       <c r="E134" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F134" s="7">
         <v>5</v>
       </c>
-      <c r="G134" s="5"/>
+      <c r="G134" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>60240050</v>
       </c>
       <c r="B135" s="6">
@@ -5539,12 +5931,1214 @@
         <v>1</v>
       </c>
       <c r="E135" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F135" s="7">
         <v>5</v>
       </c>
-      <c r="G135" s="5"/>
+      <c r="G135" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
+      <c r="A136" s="5">
+        <f t="shared" si="4"/>
+        <v>60221001</v>
+      </c>
+      <c r="B136" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C136" s="7">
+        <v>1</v>
+      </c>
+      <c r="D136" s="9">
+        <v>1</v>
+      </c>
+      <c r="E136" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F136" s="7">
+        <v>5</v>
+      </c>
+      <c r="G136" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
+      <c r="A137" s="5">
+        <f t="shared" si="4"/>
+        <v>60221002</v>
+      </c>
+      <c r="B137" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C137" s="7">
+        <v>2</v>
+      </c>
+      <c r="D137" s="9">
+        <v>1</v>
+      </c>
+      <c r="E137" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F137" s="7">
+        <v>5</v>
+      </c>
+      <c r="G137" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
+      <c r="A138" s="5">
+        <f t="shared" si="4"/>
+        <v>60221003</v>
+      </c>
+      <c r="B138" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C138" s="7">
+        <v>3</v>
+      </c>
+      <c r="D138" s="9">
+        <v>1</v>
+      </c>
+      <c r="E138" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F138" s="7">
+        <v>5</v>
+      </c>
+      <c r="G138" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7">
+      <c r="A139" s="5">
+        <f t="shared" si="4"/>
+        <v>60221004</v>
+      </c>
+      <c r="B139" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C139" s="7">
+        <v>4</v>
+      </c>
+      <c r="D139" s="9">
+        <v>1</v>
+      </c>
+      <c r="E139" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F139" s="7">
+        <v>5</v>
+      </c>
+      <c r="G139" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
+      <c r="A140" s="5">
+        <f t="shared" si="4"/>
+        <v>60221005</v>
+      </c>
+      <c r="B140" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C140" s="7">
+        <v>5</v>
+      </c>
+      <c r="D140" s="9">
+        <v>1</v>
+      </c>
+      <c r="E140" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F140" s="7">
+        <v>5</v>
+      </c>
+      <c r="G140" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
+      <c r="A141" s="5">
+        <f t="shared" si="4"/>
+        <v>60221006</v>
+      </c>
+      <c r="B141" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C141" s="7">
+        <v>6</v>
+      </c>
+      <c r="D141" s="9">
+        <v>1</v>
+      </c>
+      <c r="E141" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F141" s="7">
+        <v>5</v>
+      </c>
+      <c r="G141" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
+      <c r="A142" s="5">
+        <f t="shared" si="4"/>
+        <v>60221007</v>
+      </c>
+      <c r="B142" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C142" s="7">
+        <v>7</v>
+      </c>
+      <c r="D142" s="9">
+        <v>1</v>
+      </c>
+      <c r="E142" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F142" s="7">
+        <v>5</v>
+      </c>
+      <c r="G142" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
+      <c r="A143" s="5">
+        <f t="shared" si="4"/>
+        <v>60221008</v>
+      </c>
+      <c r="B143" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C143" s="7">
+        <v>8</v>
+      </c>
+      <c r="D143" s="9">
+        <v>1</v>
+      </c>
+      <c r="E143" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F143" s="7">
+        <v>5</v>
+      </c>
+      <c r="G143" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="A144" s="5">
+        <f t="shared" si="4"/>
+        <v>60221009</v>
+      </c>
+      <c r="B144" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C144" s="7">
+        <v>9</v>
+      </c>
+      <c r="D144" s="9">
+        <v>1</v>
+      </c>
+      <c r="E144" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F144" s="7">
+        <v>5</v>
+      </c>
+      <c r="G144" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7">
+      <c r="A145" s="5">
+        <f t="shared" si="4"/>
+        <v>60221010</v>
+      </c>
+      <c r="B145" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C145" s="7">
+        <v>10</v>
+      </c>
+      <c r="D145" s="9">
+        <v>1</v>
+      </c>
+      <c r="E145" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F145" s="7">
+        <v>5</v>
+      </c>
+      <c r="G145" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7">
+      <c r="A146" s="5">
+        <f t="shared" si="4"/>
+        <v>60221011</v>
+      </c>
+      <c r="B146" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C146" s="7">
+        <v>11</v>
+      </c>
+      <c r="D146" s="9">
+        <v>1</v>
+      </c>
+      <c r="E146" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F146" s="7">
+        <v>5</v>
+      </c>
+      <c r="G146" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7">
+      <c r="A147" s="5">
+        <f t="shared" si="4"/>
+        <v>60221012</v>
+      </c>
+      <c r="B147" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C147" s="7">
+        <v>12</v>
+      </c>
+      <c r="D147" s="9">
+        <v>1</v>
+      </c>
+      <c r="E147" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F147" s="7">
+        <v>5</v>
+      </c>
+      <c r="G147" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7">
+      <c r="A148" s="5">
+        <f t="shared" si="4"/>
+        <v>60221013</v>
+      </c>
+      <c r="B148" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C148" s="7">
+        <v>13</v>
+      </c>
+      <c r="D148" s="9">
+        <v>1</v>
+      </c>
+      <c r="E148" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F148" s="7">
+        <v>5</v>
+      </c>
+      <c r="G148" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="A149" s="5">
+        <f t="shared" si="4"/>
+        <v>60221014</v>
+      </c>
+      <c r="B149" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C149" s="7">
+        <v>14</v>
+      </c>
+      <c r="D149" s="9">
+        <v>1</v>
+      </c>
+      <c r="E149" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F149" s="7">
+        <v>5</v>
+      </c>
+      <c r="G149" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7">
+      <c r="A150" s="5">
+        <f t="shared" si="4"/>
+        <v>60221015</v>
+      </c>
+      <c r="B150" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C150" s="7">
+        <v>15</v>
+      </c>
+      <c r="D150" s="9">
+        <v>1</v>
+      </c>
+      <c r="E150" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="F150" s="7">
+        <v>5</v>
+      </c>
+      <c r="G150" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7">
+      <c r="A151" s="5">
+        <f t="shared" ref="A151:A185" si="5">(B151+500000)*100+C151+G151*1000</f>
+        <v>60221016</v>
+      </c>
+      <c r="B151" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C151" s="7">
+        <v>16</v>
+      </c>
+      <c r="D151" s="9">
+        <v>1</v>
+      </c>
+      <c r="E151" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F151" s="7">
+        <v>5</v>
+      </c>
+      <c r="G151" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7">
+      <c r="A152" s="5">
+        <f t="shared" si="5"/>
+        <v>60221017</v>
+      </c>
+      <c r="B152" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C152" s="7">
+        <v>17</v>
+      </c>
+      <c r="D152" s="9">
+        <v>1</v>
+      </c>
+      <c r="E152" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F152" s="7">
+        <v>5</v>
+      </c>
+      <c r="G152" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
+      <c r="A153" s="5">
+        <f t="shared" si="5"/>
+        <v>60221018</v>
+      </c>
+      <c r="B153" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C153" s="7">
+        <v>18</v>
+      </c>
+      <c r="D153" s="9">
+        <v>1</v>
+      </c>
+      <c r="E153" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F153" s="7">
+        <v>5</v>
+      </c>
+      <c r="G153" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154" s="5">
+        <f t="shared" si="5"/>
+        <v>60221019</v>
+      </c>
+      <c r="B154" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C154" s="7">
+        <v>19</v>
+      </c>
+      <c r="D154" s="9">
+        <v>1</v>
+      </c>
+      <c r="E154" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F154" s="7">
+        <v>5</v>
+      </c>
+      <c r="G154" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7">
+      <c r="A155" s="5">
+        <f t="shared" si="5"/>
+        <v>60221020</v>
+      </c>
+      <c r="B155" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C155" s="7">
+        <v>20</v>
+      </c>
+      <c r="D155" s="9">
+        <v>1</v>
+      </c>
+      <c r="E155" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F155" s="7">
+        <v>5</v>
+      </c>
+      <c r="G155" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7">
+      <c r="A156" s="5">
+        <f t="shared" si="5"/>
+        <v>60221021</v>
+      </c>
+      <c r="B156" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C156" s="7">
+        <v>21</v>
+      </c>
+      <c r="D156" s="9">
+        <v>1</v>
+      </c>
+      <c r="E156" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F156" s="7">
+        <v>5</v>
+      </c>
+      <c r="G156" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157" s="5">
+        <f t="shared" si="5"/>
+        <v>60221022</v>
+      </c>
+      <c r="B157" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C157" s="7">
+        <v>22</v>
+      </c>
+      <c r="D157" s="9">
+        <v>1</v>
+      </c>
+      <c r="E157" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F157" s="7">
+        <v>5</v>
+      </c>
+      <c r="G157" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7">
+      <c r="A158" s="5">
+        <f t="shared" si="5"/>
+        <v>60221023</v>
+      </c>
+      <c r="B158" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C158" s="7">
+        <v>23</v>
+      </c>
+      <c r="D158" s="9">
+        <v>1</v>
+      </c>
+      <c r="E158" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F158" s="7">
+        <v>5</v>
+      </c>
+      <c r="G158" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7">
+      <c r="A159" s="5">
+        <f t="shared" si="5"/>
+        <v>60221024</v>
+      </c>
+      <c r="B159" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C159" s="7">
+        <v>24</v>
+      </c>
+      <c r="D159" s="9">
+        <v>1</v>
+      </c>
+      <c r="E159" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F159" s="7">
+        <v>5</v>
+      </c>
+      <c r="G159" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7">
+      <c r="A160" s="5">
+        <f t="shared" si="5"/>
+        <v>60221025</v>
+      </c>
+      <c r="B160" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C160" s="7">
+        <v>25</v>
+      </c>
+      <c r="D160" s="9">
+        <v>1</v>
+      </c>
+      <c r="E160" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F160" s="7">
+        <v>5</v>
+      </c>
+      <c r="G160" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7">
+      <c r="A161" s="5">
+        <f t="shared" si="5"/>
+        <v>60222001</v>
+      </c>
+      <c r="B161" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C161" s="7">
+        <v>1</v>
+      </c>
+      <c r="D161" s="9">
+        <v>1</v>
+      </c>
+      <c r="E161" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F161" s="7">
+        <v>5</v>
+      </c>
+      <c r="G161" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7">
+      <c r="A162" s="5">
+        <f t="shared" si="5"/>
+        <v>60222002</v>
+      </c>
+      <c r="B162" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C162" s="7">
+        <v>2</v>
+      </c>
+      <c r="D162" s="9">
+        <v>1</v>
+      </c>
+      <c r="E162" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="F162" s="7">
+        <v>5</v>
+      </c>
+      <c r="G162" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7">
+      <c r="A163" s="5">
+        <f t="shared" si="5"/>
+        <v>60222003</v>
+      </c>
+      <c r="B163" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C163" s="7">
+        <v>3</v>
+      </c>
+      <c r="D163" s="9">
+        <v>1</v>
+      </c>
+      <c r="E163" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F163" s="7">
+        <v>5</v>
+      </c>
+      <c r="G163" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7">
+      <c r="A164" s="5">
+        <f t="shared" si="5"/>
+        <v>60222004</v>
+      </c>
+      <c r="B164" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C164" s="7">
+        <v>4</v>
+      </c>
+      <c r="D164" s="9">
+        <v>1</v>
+      </c>
+      <c r="E164" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F164" s="7">
+        <v>5</v>
+      </c>
+      <c r="G164" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
+      <c r="A165" s="5">
+        <f t="shared" si="5"/>
+        <v>60222005</v>
+      </c>
+      <c r="B165" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C165" s="7">
+        <v>5</v>
+      </c>
+      <c r="D165" s="9">
+        <v>1</v>
+      </c>
+      <c r="E165" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F165" s="7">
+        <v>5</v>
+      </c>
+      <c r="G165" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7">
+      <c r="A166" s="5">
+        <f t="shared" si="5"/>
+        <v>60222006</v>
+      </c>
+      <c r="B166" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C166" s="7">
+        <v>6</v>
+      </c>
+      <c r="D166" s="9">
+        <v>1</v>
+      </c>
+      <c r="E166" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="F166" s="7">
+        <v>5</v>
+      </c>
+      <c r="G166" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7">
+      <c r="A167" s="5">
+        <f t="shared" si="5"/>
+        <v>60222007</v>
+      </c>
+      <c r="B167" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C167" s="7">
+        <v>7</v>
+      </c>
+      <c r="D167" s="9">
+        <v>1</v>
+      </c>
+      <c r="E167" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F167" s="7">
+        <v>5</v>
+      </c>
+      <c r="G167" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7">
+      <c r="A168" s="5">
+        <f t="shared" si="5"/>
+        <v>60222008</v>
+      </c>
+      <c r="B168" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C168" s="7">
+        <v>8</v>
+      </c>
+      <c r="D168" s="9">
+        <v>1</v>
+      </c>
+      <c r="E168" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="F168" s="7">
+        <v>5</v>
+      </c>
+      <c r="G168" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7">
+      <c r="A169" s="5">
+        <f t="shared" si="5"/>
+        <v>60222009</v>
+      </c>
+      <c r="B169" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C169" s="7">
+        <v>9</v>
+      </c>
+      <c r="D169" s="9">
+        <v>1</v>
+      </c>
+      <c r="E169" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="F169" s="7">
+        <v>5</v>
+      </c>
+      <c r="G169" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7">
+      <c r="A170" s="5">
+        <f t="shared" si="5"/>
+        <v>60222010</v>
+      </c>
+      <c r="B170" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C170" s="7">
+        <v>10</v>
+      </c>
+      <c r="D170" s="9">
+        <v>1</v>
+      </c>
+      <c r="E170" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F170" s="7">
+        <v>5</v>
+      </c>
+      <c r="G170" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7">
+      <c r="A171" s="5">
+        <f t="shared" si="5"/>
+        <v>60222011</v>
+      </c>
+      <c r="B171" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C171" s="7">
+        <v>11</v>
+      </c>
+      <c r="D171" s="9">
+        <v>1</v>
+      </c>
+      <c r="E171" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F171" s="7">
+        <v>5</v>
+      </c>
+      <c r="G171" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7">
+      <c r="A172" s="5">
+        <f t="shared" si="5"/>
+        <v>60222012</v>
+      </c>
+      <c r="B172" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C172" s="7">
+        <v>12</v>
+      </c>
+      <c r="D172" s="9">
+        <v>1</v>
+      </c>
+      <c r="E172" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="F172" s="7">
+        <v>5</v>
+      </c>
+      <c r="G172" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7">
+      <c r="A173" s="5">
+        <f t="shared" si="5"/>
+        <v>60222013</v>
+      </c>
+      <c r="B173" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C173" s="7">
+        <v>13</v>
+      </c>
+      <c r="D173" s="9">
+        <v>1</v>
+      </c>
+      <c r="E173" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F173" s="7">
+        <v>5</v>
+      </c>
+      <c r="G173" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7">
+      <c r="A174" s="5">
+        <f t="shared" si="5"/>
+        <v>60222014</v>
+      </c>
+      <c r="B174" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C174" s="7">
+        <v>14</v>
+      </c>
+      <c r="D174" s="9">
+        <v>1</v>
+      </c>
+      <c r="E174" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="F174" s="7">
+        <v>5</v>
+      </c>
+      <c r="G174" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7">
+      <c r="A175" s="5">
+        <f t="shared" si="5"/>
+        <v>60222015</v>
+      </c>
+      <c r="B175" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C175" s="7">
+        <v>15</v>
+      </c>
+      <c r="D175" s="9">
+        <v>1</v>
+      </c>
+      <c r="E175" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="F175" s="7">
+        <v>5</v>
+      </c>
+      <c r="G175" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7">
+      <c r="A176" s="5">
+        <f t="shared" si="5"/>
+        <v>60222016</v>
+      </c>
+      <c r="B176" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C176" s="7">
+        <v>16</v>
+      </c>
+      <c r="D176" s="9">
+        <v>1</v>
+      </c>
+      <c r="E176" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F176" s="7">
+        <v>5</v>
+      </c>
+      <c r="G176" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7">
+      <c r="A177" s="5">
+        <f t="shared" si="5"/>
+        <v>60222017</v>
+      </c>
+      <c r="B177" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C177" s="7">
+        <v>17</v>
+      </c>
+      <c r="D177" s="9">
+        <v>1</v>
+      </c>
+      <c r="E177" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="F177" s="7">
+        <v>5</v>
+      </c>
+      <c r="G177" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7">
+      <c r="A178" s="5">
+        <f t="shared" si="5"/>
+        <v>60222018</v>
+      </c>
+      <c r="B178" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C178" s="7">
+        <v>18</v>
+      </c>
+      <c r="D178" s="9">
+        <v>1</v>
+      </c>
+      <c r="E178" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F178" s="7">
+        <v>5</v>
+      </c>
+      <c r="G178" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7">
+      <c r="A179" s="5">
+        <f t="shared" si="5"/>
+        <v>60222019</v>
+      </c>
+      <c r="B179" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C179" s="7">
+        <v>19</v>
+      </c>
+      <c r="D179" s="9">
+        <v>1</v>
+      </c>
+      <c r="E179" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="F179" s="7">
+        <v>5</v>
+      </c>
+      <c r="G179" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7">
+      <c r="A180" s="5">
+        <f t="shared" si="5"/>
+        <v>60222020</v>
+      </c>
+      <c r="B180" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C180" s="7">
+        <v>20</v>
+      </c>
+      <c r="D180" s="9">
+        <v>1</v>
+      </c>
+      <c r="E180" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F180" s="7">
+        <v>5</v>
+      </c>
+      <c r="G180" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7">
+      <c r="A181" s="5">
+        <f t="shared" si="5"/>
+        <v>60222021</v>
+      </c>
+      <c r="B181" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C181" s="7">
+        <v>21</v>
+      </c>
+      <c r="D181" s="9">
+        <v>1</v>
+      </c>
+      <c r="E181" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F181" s="7">
+        <v>5</v>
+      </c>
+      <c r="G181" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7">
+      <c r="A182" s="5">
+        <f t="shared" si="5"/>
+        <v>60222022</v>
+      </c>
+      <c r="B182" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C182" s="7">
+        <v>22</v>
+      </c>
+      <c r="D182" s="9">
+        <v>1</v>
+      </c>
+      <c r="E182" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F182" s="7">
+        <v>5</v>
+      </c>
+      <c r="G182" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7">
+      <c r="A183" s="5">
+        <f t="shared" si="5"/>
+        <v>60222023</v>
+      </c>
+      <c r="B183" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C183" s="7">
+        <v>23</v>
+      </c>
+      <c r="D183" s="9">
+        <v>1</v>
+      </c>
+      <c r="E183" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F183" s="7">
+        <v>5</v>
+      </c>
+      <c r="G183" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7">
+      <c r="A184" s="5">
+        <f t="shared" si="5"/>
+        <v>60222024</v>
+      </c>
+      <c r="B184" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C184" s="7">
+        <v>24</v>
+      </c>
+      <c r="D184" s="9">
+        <v>1</v>
+      </c>
+      <c r="E184" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="F184" s="7">
+        <v>5</v>
+      </c>
+      <c r="G184" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7">
+      <c r="A185" s="5">
+        <f t="shared" si="5"/>
+        <v>60222025</v>
+      </c>
+      <c r="B185" s="6">
+        <v>102200</v>
+      </c>
+      <c r="C185" s="7">
+        <v>25</v>
+      </c>
+      <c r="D185" s="9">
+        <v>1</v>
+      </c>
+      <c r="E185" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="F185" s="7">
+        <v>5</v>
+      </c>
+      <c r="G185" s="15">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5569,30 +7163,30 @@
         <v>1</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>2</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>4</v>
       </c>
       <c r="L20" s="4"/>
       <c r="M20" s="4" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="Q20" s="4" t="s">
         <v>5</v>
@@ -5601,47 +7195,47 @@
         <v>3</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="5:19">
       <c r="E21" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="7" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="L21" s="7"/>
       <c r="M21" s="7" t="s">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R21" s="7" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="S21" s="7"/>
     </row>
@@ -5650,36 +7244,36 @@
         <v>0</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L22" s="7"/>
       <c r="M22" s="7" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R22" s="7"/>
       <c r="S22" s="7"/>
@@ -5716,28 +7310,28 @@
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="7" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
       <c r="M24" s="7" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="O24" s="7"/>
       <c r="P24" s="7" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="Q24" s="7">
         <v>5</v>
       </c>
       <c r="R24" s="7" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="S24" s="7" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="5:19">
@@ -5755,28 +7349,28 @@
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
       <c r="M25" s="8" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="O25" s="7"/>
       <c r="P25" s="7" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="Q25" s="7">
         <v>5</v>
       </c>
       <c r="R25" s="7" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="S25" s="7" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="5:19">
@@ -5844,7 +7438,7 @@
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
       <c r="L28" s="7" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="M28" s="5"/>
       <c r="N28" s="7">
@@ -5852,16 +7446,16 @@
       </c>
       <c r="O28" s="7"/>
       <c r="P28" s="7" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="Q28" s="7">
         <v>5</v>
       </c>
       <c r="R28" s="7" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="S28" s="7" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseLine.xlsx
+++ b/slots/resources/sample/BaseLine.xlsx
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="142">
   <si>
     <t>id</t>
   </si>
@@ -608,43 +608,52 @@
     <t>3_4_9_10_15</t>
   </si>
   <si>
-    <t>1_4_7_11_15</t>
-  </si>
-  <si>
-    <t>1_4_7_10_15</t>
-  </si>
-  <si>
-    <t>3_6_9_12_13</t>
-  </si>
-  <si>
-    <t>1_4_9_12_15</t>
-  </si>
-  <si>
-    <t>3_6_7_10_13</t>
-  </si>
-  <si>
-    <t>1_5_9_12_15</t>
-  </si>
-  <si>
-    <t>3_5_7_10_13</t>
-  </si>
-  <si>
-    <t>1_6_9_11_13</t>
-  </si>
-  <si>
-    <t>3_4_7_11_15</t>
-  </si>
-  <si>
-    <t>1_5_9_12_13</t>
-  </si>
-  <si>
-    <t>3_5_7_10_15</t>
-  </si>
-  <si>
-    <t>1_6_9_12_15</t>
-  </si>
-  <si>
-    <t>3_4_7_10_13</t>
+    <t>1_4_7_11_14</t>
+  </si>
+  <si>
+    <t>1_4_7_10_14</t>
+  </si>
+  <si>
+    <t>2_5_8_11_13</t>
+  </si>
+  <si>
+    <t>1_4_8_11_14</t>
+  </si>
+  <si>
+    <t>2_5_7_10_13</t>
+  </si>
+  <si>
+    <t>2_4_8_10_14</t>
+  </si>
+  <si>
+    <t>1_5_8_12_14</t>
+  </si>
+  <si>
+    <t>2_6_7_10_13</t>
+  </si>
+  <si>
+    <t>1_5_8_11_14</t>
+  </si>
+  <si>
+    <t>2_4_7_10_13</t>
+  </si>
+  <si>
+    <t>1_5_7_12_13</t>
+  </si>
+  <si>
+    <t>1_5_8_12_13</t>
+  </si>
+  <si>
+    <t>2_5_7_10_14</t>
+  </si>
+  <si>
+    <t>1_6_8_12_13</t>
+  </si>
+  <si>
+    <t>1_6_8_12_14</t>
+  </si>
+  <si>
+    <t>2_4_7_11_13</t>
   </si>
   <si>
     <t>线路类型</t>
@@ -1524,6 +1533,15 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -6603,7 +6621,7 @@
         <v>1</v>
       </c>
       <c r="E163" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F163" s="7">
         <v>5</v>
@@ -6627,7 +6645,7 @@
         <v>1</v>
       </c>
       <c r="E164" s="7" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F164" s="7">
         <v>5</v>
@@ -6651,7 +6669,7 @@
         <v>1</v>
       </c>
       <c r="E165" s="7" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="F165" s="7">
         <v>5</v>
@@ -6771,7 +6789,7 @@
         <v>1</v>
       </c>
       <c r="E170" s="7" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F170" s="7">
         <v>5</v>
@@ -6795,7 +6813,7 @@
         <v>1</v>
       </c>
       <c r="E171" s="7" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F171" s="7">
         <v>5</v>
@@ -6819,7 +6837,7 @@
         <v>1</v>
       </c>
       <c r="E172" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F172" s="7">
         <v>5</v>
@@ -6843,7 +6861,7 @@
         <v>1</v>
       </c>
       <c r="E173" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F173" s="7">
         <v>5</v>
@@ -6867,7 +6885,7 @@
         <v>1</v>
       </c>
       <c r="E174" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F174" s="7">
         <v>5</v>
@@ -6891,7 +6909,7 @@
         <v>1</v>
       </c>
       <c r="E175" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F175" s="7">
         <v>5</v>
@@ -6915,7 +6933,7 @@
         <v>1</v>
       </c>
       <c r="E176" s="7" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="F176" s="7">
         <v>5</v>
@@ -6939,7 +6957,7 @@
         <v>1</v>
       </c>
       <c r="E177" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F177" s="7">
         <v>5</v>
@@ -6963,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="E178" s="7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F178" s="7">
         <v>5</v>
@@ -6987,7 +7005,7 @@
         <v>1</v>
       </c>
       <c r="E179" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F179" s="7">
         <v>5</v>
@@ -7011,7 +7029,7 @@
         <v>1</v>
       </c>
       <c r="E180" s="7" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="F180" s="7">
         <v>5</v>
@@ -7035,7 +7053,7 @@
         <v>1</v>
       </c>
       <c r="E181" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F181" s="7">
         <v>5</v>
@@ -7059,7 +7077,7 @@
         <v>1</v>
       </c>
       <c r="E182" s="7" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="F182" s="7">
         <v>5</v>
@@ -7083,7 +7101,7 @@
         <v>1</v>
       </c>
       <c r="E183" s="7" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F183" s="7">
         <v>5</v>
@@ -7107,7 +7125,7 @@
         <v>1</v>
       </c>
       <c r="E184" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F184" s="7">
         <v>5</v>
@@ -7131,7 +7149,7 @@
         <v>1</v>
       </c>
       <c r="E185" s="7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F185" s="7">
         <v>5</v>
@@ -7141,6 +7159,9 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="E161:E185">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -7163,30 +7184,30 @@
         <v>1</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>2</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>4</v>
       </c>
       <c r="L20" s="4"/>
       <c r="M20" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="Q20" s="4" t="s">
         <v>5</v>
@@ -7195,7 +7216,7 @@
         <v>3</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="5:19">
@@ -7213,29 +7234,29 @@
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L21" s="7"/>
       <c r="M21" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="Q21" s="7" t="s">
         <v>7</v>
       </c>
       <c r="R21" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="S21" s="7"/>
     </row>
@@ -7247,30 +7268,30 @@
         <v>10</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>11</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K22" s="7" t="s">
         <v>13</v>
       </c>
       <c r="L22" s="7"/>
       <c r="M22" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="Q22" s="7" t="s">
         <v>14</v>
@@ -7310,28 +7331,28 @@
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="7" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
       <c r="M24" s="7" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="O24" s="7"/>
       <c r="P24" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="Q24" s="7">
         <v>5</v>
       </c>
       <c r="R24" s="7" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="S24" s="7" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="5:19">
@@ -7349,28 +7370,28 @@
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
       <c r="M25" s="8" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="O25" s="7"/>
       <c r="P25" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="Q25" s="7">
         <v>5</v>
       </c>
       <c r="R25" s="7" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="S25" s="7" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="5:19">
@@ -7438,7 +7459,7 @@
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
       <c r="L28" s="7" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="M28" s="5"/>
       <c r="N28" s="7">
@@ -7446,16 +7467,16 @@
       </c>
       <c r="O28" s="7"/>
       <c r="P28" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="Q28" s="7">
         <v>5</v>
       </c>
       <c r="R28" s="7" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="S28" s="7" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseLine.xlsx
+++ b/slots/resources/sample/BaseLine.xlsx
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="165">
   <si>
     <t>id</t>
   </si>
@@ -654,6 +654,75 @@
   </si>
   <si>
     <t>2_4_7_11_13</t>
+  </si>
+  <si>
+    <t>2_6_8_12_14</t>
+  </si>
+  <si>
+    <t>2_4_8_12_13</t>
+  </si>
+  <si>
+    <t>3_4_8_12_13</t>
+  </si>
+  <si>
+    <t>1_5_9_12_14</t>
+  </si>
+  <si>
+    <t>3_5_9_11_13</t>
+  </si>
+  <si>
+    <t>1_4_7_10_15</t>
+  </si>
+  <si>
+    <t>3_6_9_12_13</t>
+  </si>
+  <si>
+    <t>1_6_8_10_15</t>
+  </si>
+  <si>
+    <t>1_4_9_12_15</t>
+  </si>
+  <si>
+    <t>3_6_7_10_13</t>
+  </si>
+  <si>
+    <t>2_6_9_10_13</t>
+  </si>
+  <si>
+    <t>1_5_9_12_15</t>
+  </si>
+  <si>
+    <t>2_4_9_11_15</t>
+  </si>
+  <si>
+    <t>1_4_8_11_15</t>
+  </si>
+  <si>
+    <t>3_5_7_10_13</t>
+  </si>
+  <si>
+    <t>3_4_8_10_15</t>
+  </si>
+  <si>
+    <t>2_6_7_11_13</t>
+  </si>
+  <si>
+    <t>3_6_8_11_13</t>
+  </si>
+  <si>
+    <t>3_5_7_10_14</t>
+  </si>
+  <si>
+    <t>1_5_7_11_15</t>
+  </si>
+  <si>
+    <t>1_6_9_12_15</t>
+  </si>
+  <si>
+    <t>3_4_7_10_13</t>
+  </si>
+  <si>
+    <t>3_5_8_11_14</t>
   </si>
   <si>
     <t>线路类型</t>
@@ -1533,7 +1602,14 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2366,7 +2442,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z185"/>
+  <dimension ref="A1:Z235"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.375"/>
@@ -7158,9 +7234,1212 @@
         <v>2</v>
       </c>
     </row>
+    <row r="186" spans="1:7">
+      <c r="A186" s="5">
+        <f t="shared" ref="A186:A217" si="6">(B186+500000)*100+C186+G186*1000</f>
+        <v>60250001</v>
+      </c>
+      <c r="B186" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C186" s="7">
+        <v>1</v>
+      </c>
+      <c r="D186" s="9">
+        <v>1</v>
+      </c>
+      <c r="E186" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F186" s="7">
+        <v>5</v>
+      </c>
+      <c r="G186" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7">
+      <c r="A187" s="5">
+        <f t="shared" si="6"/>
+        <v>60250002</v>
+      </c>
+      <c r="B187" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C187" s="7">
+        <v>2</v>
+      </c>
+      <c r="D187" s="9">
+        <v>1</v>
+      </c>
+      <c r="E187" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F187" s="7">
+        <v>5</v>
+      </c>
+      <c r="G187" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7">
+      <c r="A188" s="5">
+        <f t="shared" si="6"/>
+        <v>60250003</v>
+      </c>
+      <c r="B188" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C188" s="7">
+        <v>3</v>
+      </c>
+      <c r="D188" s="9">
+        <v>1</v>
+      </c>
+      <c r="E188" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F188" s="7">
+        <v>5</v>
+      </c>
+      <c r="G188" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7">
+      <c r="A189" s="5">
+        <f t="shared" si="6"/>
+        <v>60250004</v>
+      </c>
+      <c r="B189" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C189" s="7">
+        <v>4</v>
+      </c>
+      <c r="D189" s="9">
+        <v>1</v>
+      </c>
+      <c r="E189" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F189" s="7">
+        <v>5</v>
+      </c>
+      <c r="G189" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7">
+      <c r="A190" s="5">
+        <f t="shared" si="6"/>
+        <v>60250005</v>
+      </c>
+      <c r="B190" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C190" s="7">
+        <v>5</v>
+      </c>
+      <c r="D190" s="9">
+        <v>1</v>
+      </c>
+      <c r="E190" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F190" s="7">
+        <v>5</v>
+      </c>
+      <c r="G190" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7">
+      <c r="A191" s="5">
+        <f t="shared" si="6"/>
+        <v>60250006</v>
+      </c>
+      <c r="B191" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C191" s="7">
+        <v>6</v>
+      </c>
+      <c r="D191" s="9">
+        <v>1</v>
+      </c>
+      <c r="E191" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F191" s="7">
+        <v>5</v>
+      </c>
+      <c r="G191" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7">
+      <c r="A192" s="5">
+        <f t="shared" si="6"/>
+        <v>60250007</v>
+      </c>
+      <c r="B192" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C192" s="7">
+        <v>7</v>
+      </c>
+      <c r="D192" s="9">
+        <v>1</v>
+      </c>
+      <c r="E192" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F192" s="7">
+        <v>5</v>
+      </c>
+      <c r="G192" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7">
+      <c r="A193" s="5">
+        <f t="shared" si="6"/>
+        <v>60250008</v>
+      </c>
+      <c r="B193" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C193" s="7">
+        <v>8</v>
+      </c>
+      <c r="D193" s="9">
+        <v>1</v>
+      </c>
+      <c r="E193" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F193" s="7">
+        <v>5</v>
+      </c>
+      <c r="G193" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7">
+      <c r="A194" s="5">
+        <f t="shared" si="6"/>
+        <v>60250009</v>
+      </c>
+      <c r="B194" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C194" s="7">
+        <v>9</v>
+      </c>
+      <c r="D194" s="9">
+        <v>1</v>
+      </c>
+      <c r="E194" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F194" s="7">
+        <v>5</v>
+      </c>
+      <c r="G194" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7">
+      <c r="A195" s="5">
+        <f t="shared" si="6"/>
+        <v>60250010</v>
+      </c>
+      <c r="B195" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C195" s="7">
+        <v>10</v>
+      </c>
+      <c r="D195" s="9">
+        <v>1</v>
+      </c>
+      <c r="E195" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="F195" s="7">
+        <v>5</v>
+      </c>
+      <c r="G195" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7">
+      <c r="A196" s="5">
+        <f t="shared" si="6"/>
+        <v>60250011</v>
+      </c>
+      <c r="B196" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C196" s="7">
+        <v>11</v>
+      </c>
+      <c r="D196" s="9">
+        <v>1</v>
+      </c>
+      <c r="E196" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F196" s="7">
+        <v>5</v>
+      </c>
+      <c r="G196" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7">
+      <c r="A197" s="5">
+        <f t="shared" si="6"/>
+        <v>60250012</v>
+      </c>
+      <c r="B197" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C197" s="7">
+        <v>12</v>
+      </c>
+      <c r="D197" s="9">
+        <v>1</v>
+      </c>
+      <c r="E197" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F197" s="7">
+        <v>5</v>
+      </c>
+      <c r="G197" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7">
+      <c r="A198" s="5">
+        <f t="shared" si="6"/>
+        <v>60250013</v>
+      </c>
+      <c r="B198" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C198" s="7">
+        <v>13</v>
+      </c>
+      <c r="D198" s="9">
+        <v>1</v>
+      </c>
+      <c r="E198" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F198" s="7">
+        <v>5</v>
+      </c>
+      <c r="G198" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7">
+      <c r="A199" s="5">
+        <f t="shared" si="6"/>
+        <v>60250014</v>
+      </c>
+      <c r="B199" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C199" s="7">
+        <v>14</v>
+      </c>
+      <c r="D199" s="9">
+        <v>1</v>
+      </c>
+      <c r="E199" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F199" s="7">
+        <v>5</v>
+      </c>
+      <c r="G199" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7">
+      <c r="A200" s="5">
+        <f t="shared" si="6"/>
+        <v>60250015</v>
+      </c>
+      <c r="B200" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C200" s="7">
+        <v>15</v>
+      </c>
+      <c r="D200" s="9">
+        <v>1</v>
+      </c>
+      <c r="E200" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="F200" s="7">
+        <v>5</v>
+      </c>
+      <c r="G200" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7">
+      <c r="A201" s="5">
+        <f t="shared" si="6"/>
+        <v>60250016</v>
+      </c>
+      <c r="B201" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C201" s="7">
+        <v>16</v>
+      </c>
+      <c r="D201" s="9">
+        <v>1</v>
+      </c>
+      <c r="E201" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F201" s="7">
+        <v>5</v>
+      </c>
+      <c r="G201" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7">
+      <c r="A202" s="5">
+        <f t="shared" si="6"/>
+        <v>60250017</v>
+      </c>
+      <c r="B202" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C202" s="7">
+        <v>17</v>
+      </c>
+      <c r="D202" s="9">
+        <v>1</v>
+      </c>
+      <c r="E202" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F202" s="7">
+        <v>5</v>
+      </c>
+      <c r="G202" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7">
+      <c r="A203" s="5">
+        <f t="shared" si="6"/>
+        <v>60250018</v>
+      </c>
+      <c r="B203" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C203" s="7">
+        <v>18</v>
+      </c>
+      <c r="D203" s="9">
+        <v>1</v>
+      </c>
+      <c r="E203" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F203" s="7">
+        <v>5</v>
+      </c>
+      <c r="G203" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7">
+      <c r="A204" s="5">
+        <f t="shared" si="6"/>
+        <v>60250019</v>
+      </c>
+      <c r="B204" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C204" s="7">
+        <v>19</v>
+      </c>
+      <c r="D204" s="9">
+        <v>1</v>
+      </c>
+      <c r="E204" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F204" s="7">
+        <v>5</v>
+      </c>
+      <c r="G204" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7">
+      <c r="A205" s="5">
+        <f t="shared" si="6"/>
+        <v>60250020</v>
+      </c>
+      <c r="B205" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C205" s="7">
+        <v>20</v>
+      </c>
+      <c r="D205" s="9">
+        <v>1</v>
+      </c>
+      <c r="E205" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F205" s="7">
+        <v>5</v>
+      </c>
+      <c r="G205" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7">
+      <c r="A206" s="5">
+        <f t="shared" si="6"/>
+        <v>60250021</v>
+      </c>
+      <c r="B206" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C206" s="7">
+        <v>21</v>
+      </c>
+      <c r="D206" s="9">
+        <v>1</v>
+      </c>
+      <c r="E206" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F206" s="7">
+        <v>5</v>
+      </c>
+      <c r="G206" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7">
+      <c r="A207" s="5">
+        <f t="shared" si="6"/>
+        <v>60250022</v>
+      </c>
+      <c r="B207" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C207" s="7">
+        <v>22</v>
+      </c>
+      <c r="D207" s="9">
+        <v>1</v>
+      </c>
+      <c r="E207" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F207" s="7">
+        <v>5</v>
+      </c>
+      <c r="G207" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7">
+      <c r="A208" s="5">
+        <f t="shared" si="6"/>
+        <v>60250023</v>
+      </c>
+      <c r="B208" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C208" s="7">
+        <v>23</v>
+      </c>
+      <c r="D208" s="9">
+        <v>1</v>
+      </c>
+      <c r="E208" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F208" s="7">
+        <v>5</v>
+      </c>
+      <c r="G208" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7">
+      <c r="A209" s="5">
+        <f t="shared" si="6"/>
+        <v>60250024</v>
+      </c>
+      <c r="B209" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C209" s="7">
+        <v>24</v>
+      </c>
+      <c r="D209" s="9">
+        <v>1</v>
+      </c>
+      <c r="E209" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F209" s="7">
+        <v>5</v>
+      </c>
+      <c r="G209" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7">
+      <c r="A210" s="5">
+        <f t="shared" si="6"/>
+        <v>60250025</v>
+      </c>
+      <c r="B210" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C210" s="7">
+        <v>25</v>
+      </c>
+      <c r="D210" s="9">
+        <v>1</v>
+      </c>
+      <c r="E210" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F210" s="7">
+        <v>5</v>
+      </c>
+      <c r="G210" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7">
+      <c r="A211" s="5">
+        <f t="shared" si="6"/>
+        <v>60250026</v>
+      </c>
+      <c r="B211" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C211" s="7">
+        <v>26</v>
+      </c>
+      <c r="D211" s="9">
+        <v>1</v>
+      </c>
+      <c r="E211" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F211" s="7">
+        <v>5</v>
+      </c>
+      <c r="G211" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7">
+      <c r="A212" s="5">
+        <f t="shared" si="6"/>
+        <v>60250027</v>
+      </c>
+      <c r="B212" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C212" s="7">
+        <v>27</v>
+      </c>
+      <c r="D212" s="9">
+        <v>1</v>
+      </c>
+      <c r="E212" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F212" s="7">
+        <v>5</v>
+      </c>
+      <c r="G212" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7">
+      <c r="A213" s="5">
+        <f t="shared" si="6"/>
+        <v>60250028</v>
+      </c>
+      <c r="B213" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C213" s="7">
+        <v>28</v>
+      </c>
+      <c r="D213" s="9">
+        <v>1</v>
+      </c>
+      <c r="E213" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="F213" s="7">
+        <v>5</v>
+      </c>
+      <c r="G213" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7">
+      <c r="A214" s="5">
+        <f t="shared" si="6"/>
+        <v>60250029</v>
+      </c>
+      <c r="B214" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C214" s="7">
+        <v>29</v>
+      </c>
+      <c r="D214" s="9">
+        <v>1</v>
+      </c>
+      <c r="E214" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="F214" s="7">
+        <v>5</v>
+      </c>
+      <c r="G214" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7">
+      <c r="A215" s="5">
+        <f t="shared" si="6"/>
+        <v>60250030</v>
+      </c>
+      <c r="B215" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C215" s="7">
+        <v>30</v>
+      </c>
+      <c r="D215" s="9">
+        <v>1</v>
+      </c>
+      <c r="E215" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="F215" s="7">
+        <v>5</v>
+      </c>
+      <c r="G215" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7">
+      <c r="A216" s="5">
+        <f t="shared" si="6"/>
+        <v>60250031</v>
+      </c>
+      <c r="B216" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C216" s="7">
+        <v>31</v>
+      </c>
+      <c r="D216" s="9">
+        <v>1</v>
+      </c>
+      <c r="E216" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F216" s="7">
+        <v>5</v>
+      </c>
+      <c r="G216" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7">
+      <c r="A217" s="5">
+        <f t="shared" si="6"/>
+        <v>60250032</v>
+      </c>
+      <c r="B217" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C217" s="7">
+        <v>32</v>
+      </c>
+      <c r="D217" s="9">
+        <v>1</v>
+      </c>
+      <c r="E217" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="F217" s="7">
+        <v>5</v>
+      </c>
+      <c r="G217" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7">
+      <c r="A218" s="5">
+        <f t="shared" ref="A218:A235" si="7">(B218+500000)*100+C218+G218*1000</f>
+        <v>60250033</v>
+      </c>
+      <c r="B218" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C218" s="7">
+        <v>33</v>
+      </c>
+      <c r="D218" s="9">
+        <v>1</v>
+      </c>
+      <c r="E218" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="F218" s="7">
+        <v>5</v>
+      </c>
+      <c r="G218" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7">
+      <c r="A219" s="5">
+        <f t="shared" si="7"/>
+        <v>60250034</v>
+      </c>
+      <c r="B219" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C219" s="7">
+        <v>34</v>
+      </c>
+      <c r="D219" s="9">
+        <v>1</v>
+      </c>
+      <c r="E219" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="F219" s="7">
+        <v>5</v>
+      </c>
+      <c r="G219" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7">
+      <c r="A220" s="5">
+        <f t="shared" si="7"/>
+        <v>60250035</v>
+      </c>
+      <c r="B220" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C220" s="7">
+        <v>35</v>
+      </c>
+      <c r="D220" s="9">
+        <v>1</v>
+      </c>
+      <c r="E220" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="F220" s="7">
+        <v>5</v>
+      </c>
+      <c r="G220" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7">
+      <c r="A221" s="5">
+        <f t="shared" si="7"/>
+        <v>60250036</v>
+      </c>
+      <c r="B221" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C221" s="7">
+        <v>36</v>
+      </c>
+      <c r="D221" s="9">
+        <v>1</v>
+      </c>
+      <c r="E221" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="F221" s="7">
+        <v>5</v>
+      </c>
+      <c r="G221" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7">
+      <c r="A222" s="5">
+        <f t="shared" si="7"/>
+        <v>60250037</v>
+      </c>
+      <c r="B222" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C222" s="7">
+        <v>37</v>
+      </c>
+      <c r="D222" s="9">
+        <v>1</v>
+      </c>
+      <c r="E222" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="F222" s="7">
+        <v>5</v>
+      </c>
+      <c r="G222" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7">
+      <c r="A223" s="5">
+        <f t="shared" si="7"/>
+        <v>60250038</v>
+      </c>
+      <c r="B223" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C223" s="7">
+        <v>38</v>
+      </c>
+      <c r="D223" s="9">
+        <v>1</v>
+      </c>
+      <c r="E223" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F223" s="7">
+        <v>5</v>
+      </c>
+      <c r="G223" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7">
+      <c r="A224" s="5">
+        <f t="shared" si="7"/>
+        <v>60250039</v>
+      </c>
+      <c r="B224" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C224" s="7">
+        <v>39</v>
+      </c>
+      <c r="D224" s="9">
+        <v>1</v>
+      </c>
+      <c r="E224" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="F224" s="7">
+        <v>5</v>
+      </c>
+      <c r="G224" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7">
+      <c r="A225" s="5">
+        <f t="shared" si="7"/>
+        <v>60250040</v>
+      </c>
+      <c r="B225" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C225" s="7">
+        <v>40</v>
+      </c>
+      <c r="D225" s="9">
+        <v>1</v>
+      </c>
+      <c r="E225" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F225" s="7">
+        <v>5</v>
+      </c>
+      <c r="G225" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7">
+      <c r="A226" s="5">
+        <f t="shared" si="7"/>
+        <v>60250041</v>
+      </c>
+      <c r="B226" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C226" s="7">
+        <v>41</v>
+      </c>
+      <c r="D226" s="9">
+        <v>1</v>
+      </c>
+      <c r="E226" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="F226" s="7">
+        <v>5</v>
+      </c>
+      <c r="G226" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7">
+      <c r="A227" s="5">
+        <f t="shared" si="7"/>
+        <v>60250042</v>
+      </c>
+      <c r="B227" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C227" s="7">
+        <v>42</v>
+      </c>
+      <c r="D227" s="9">
+        <v>1</v>
+      </c>
+      <c r="E227" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F227" s="7">
+        <v>5</v>
+      </c>
+      <c r="G227" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7">
+      <c r="A228" s="5">
+        <f t="shared" si="7"/>
+        <v>60250043</v>
+      </c>
+      <c r="B228" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C228" s="7">
+        <v>43</v>
+      </c>
+      <c r="D228" s="9">
+        <v>1</v>
+      </c>
+      <c r="E228" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F228" s="7">
+        <v>5</v>
+      </c>
+      <c r="G228" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7">
+      <c r="A229" s="5">
+        <f t="shared" si="7"/>
+        <v>60250044</v>
+      </c>
+      <c r="B229" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C229" s="7">
+        <v>44</v>
+      </c>
+      <c r="D229" s="9">
+        <v>1</v>
+      </c>
+      <c r="E229" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="F229" s="7">
+        <v>5</v>
+      </c>
+      <c r="G229" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7">
+      <c r="A230" s="5">
+        <f t="shared" si="7"/>
+        <v>60250045</v>
+      </c>
+      <c r="B230" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C230" s="7">
+        <v>45</v>
+      </c>
+      <c r="D230" s="9">
+        <v>1</v>
+      </c>
+      <c r="E230" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="F230" s="7">
+        <v>5</v>
+      </c>
+      <c r="G230" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7">
+      <c r="A231" s="5">
+        <f t="shared" si="7"/>
+        <v>60250046</v>
+      </c>
+      <c r="B231" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C231" s="7">
+        <v>46</v>
+      </c>
+      <c r="D231" s="9">
+        <v>1</v>
+      </c>
+      <c r="E231" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="F231" s="7">
+        <v>5</v>
+      </c>
+      <c r="G231" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7">
+      <c r="A232" s="5">
+        <f t="shared" si="7"/>
+        <v>60250047</v>
+      </c>
+      <c r="B232" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C232" s="7">
+        <v>47</v>
+      </c>
+      <c r="D232" s="9">
+        <v>1</v>
+      </c>
+      <c r="E232" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="F232" s="7">
+        <v>5</v>
+      </c>
+      <c r="G232" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7">
+      <c r="A233" s="5">
+        <f t="shared" si="7"/>
+        <v>60250048</v>
+      </c>
+      <c r="B233" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C233" s="7">
+        <v>48</v>
+      </c>
+      <c r="D233" s="9">
+        <v>1</v>
+      </c>
+      <c r="E233" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="F233" s="7">
+        <v>5</v>
+      </c>
+      <c r="G233" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7">
+      <c r="A234" s="5">
+        <f t="shared" si="7"/>
+        <v>60250049</v>
+      </c>
+      <c r="B234" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C234" s="7">
+        <v>49</v>
+      </c>
+      <c r="D234" s="9">
+        <v>1</v>
+      </c>
+      <c r="E234" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="F234" s="7">
+        <v>5</v>
+      </c>
+      <c r="G234" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7">
+      <c r="A235" s="5">
+        <f t="shared" si="7"/>
+        <v>60250050</v>
+      </c>
+      <c r="B235" s="6">
+        <v>102500</v>
+      </c>
+      <c r="C235" s="7">
+        <v>50</v>
+      </c>
+      <c r="D235" s="9">
+        <v>1</v>
+      </c>
+      <c r="E235" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="F235" s="7">
+        <v>5</v>
+      </c>
+      <c r="G235" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="E161:E185">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E186:E235">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -7184,30 +8463,30 @@
         <v>1</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>2</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>4</v>
       </c>
       <c r="L20" s="4"/>
       <c r="M20" s="4" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="Q20" s="4" t="s">
         <v>5</v>
@@ -7216,7 +8495,7 @@
         <v>3</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="5:19">
@@ -7234,29 +8513,29 @@
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="7" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="L21" s="7"/>
       <c r="M21" s="7" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="Q21" s="7" t="s">
         <v>7</v>
       </c>
       <c r="R21" s="7" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="S21" s="7"/>
     </row>
@@ -7268,30 +8547,30 @@
         <v>10</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>11</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="K22" s="7" t="s">
         <v>13</v>
       </c>
       <c r="L22" s="7"/>
       <c r="M22" s="7" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="Q22" s="7" t="s">
         <v>14</v>
@@ -7331,28 +8610,28 @@
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="7" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
       <c r="M24" s="7" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="O24" s="7"/>
       <c r="P24" s="7" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="Q24" s="7">
         <v>5</v>
       </c>
       <c r="R24" s="7" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="S24" s="7" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="5:19">
@@ -7370,28 +8649,28 @@
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
       <c r="M25" s="8" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="O25" s="7"/>
       <c r="P25" s="7" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="Q25" s="7">
         <v>5</v>
       </c>
       <c r="R25" s="7" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="S25" s="7" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="5:19">
@@ -7459,7 +8738,7 @@
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
       <c r="L28" s="7" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="M28" s="5"/>
       <c r="N28" s="7">
@@ -7467,16 +8746,16 @@
       </c>
       <c r="O28" s="7"/>
       <c r="P28" s="7" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="Q28" s="7">
         <v>5</v>
       </c>
       <c r="R28" s="7" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="S28" s="7" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseLine.xlsx
+++ b/slots/resources/sample/BaseLine.xlsx
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="169">
   <si>
     <t>id</t>
   </si>
@@ -723,6 +723,18 @@
   </si>
   <si>
     <t>3_5_8_11_14</t>
+  </si>
+  <si>
+    <t>1_4_7</t>
+  </si>
+  <si>
+    <t>3_6_9</t>
+  </si>
+  <si>
+    <t>1_5_9</t>
+  </si>
+  <si>
+    <t>3_5_7</t>
   </si>
   <si>
     <t>线路类型</t>
@@ -1602,14 +1614,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2442,7 +2447,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z235"/>
+  <dimension ref="A1:Z240"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.375"/>
@@ -8434,12 +8439,147 @@
         <v>0</v>
       </c>
     </row>
+    <row r="236" spans="1:7">
+      <c r="A236" s="5">
+        <f>(B236+500000)*100+C236+G236*1000</f>
+        <v>60340001</v>
+      </c>
+      <c r="B236" s="6">
+        <v>103400</v>
+      </c>
+      <c r="C236" s="7">
+        <v>1</v>
+      </c>
+      <c r="D236" s="9">
+        <v>1</v>
+      </c>
+      <c r="E236" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F236" s="7">
+        <v>5</v>
+      </c>
+      <c r="G236" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7">
+      <c r="A237" s="5">
+        <f>(B237+500000)*100+C237+G237*1000</f>
+        <v>60340002</v>
+      </c>
+      <c r="B237" s="6">
+        <v>103400</v>
+      </c>
+      <c r="C237" s="7">
+        <v>2</v>
+      </c>
+      <c r="D237" s="9">
+        <v>1</v>
+      </c>
+      <c r="E237" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="F237" s="7">
+        <v>5</v>
+      </c>
+      <c r="G237" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7">
+      <c r="A238" s="5">
+        <f>(B238+500000)*100+C238+G238*1000</f>
+        <v>60340003</v>
+      </c>
+      <c r="B238" s="6">
+        <v>103400</v>
+      </c>
+      <c r="C238" s="7">
+        <v>3</v>
+      </c>
+      <c r="D238" s="9">
+        <v>1</v>
+      </c>
+      <c r="E238" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="F238" s="7">
+        <v>5</v>
+      </c>
+      <c r="G238" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7">
+      <c r="A239" s="5">
+        <f>(B239+500000)*100+C239+G239*1000</f>
+        <v>60340004</v>
+      </c>
+      <c r="B239" s="6">
+        <v>103400</v>
+      </c>
+      <c r="C239" s="7">
+        <v>4</v>
+      </c>
+      <c r="D239" s="9">
+        <v>1</v>
+      </c>
+      <c r="E239" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="F239" s="7">
+        <v>5</v>
+      </c>
+      <c r="G239" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7">
+      <c r="A240" s="5">
+        <f>(B240+500000)*100+C240+G240*1000</f>
+        <v>60340005</v>
+      </c>
+      <c r="B240" s="6">
+        <v>103400</v>
+      </c>
+      <c r="C240" s="7">
+        <v>5</v>
+      </c>
+      <c r="D240" s="9">
+        <v>1</v>
+      </c>
+      <c r="E240" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="F240" s="7">
+        <v>5</v>
+      </c>
+      <c r="G240" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E161:E185">
+  <conditionalFormatting sqref="E236">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E237">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E238">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E239">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E240">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E161:E185">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E186:E235">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -8463,30 +8603,30 @@
         <v>1</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>2</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>4</v>
       </c>
       <c r="L20" s="4"/>
       <c r="M20" s="4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="Q20" s="4" t="s">
         <v>5</v>
@@ -8495,7 +8635,7 @@
         <v>3</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="5:19">
@@ -8513,29 +8653,29 @@
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="7" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="L21" s="7"/>
       <c r="M21" s="7" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="Q21" s="7" t="s">
         <v>7</v>
       </c>
       <c r="R21" s="7" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="S21" s="7"/>
     </row>
@@ -8547,30 +8687,30 @@
         <v>10</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>11</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="K22" s="7" t="s">
         <v>13</v>
       </c>
       <c r="L22" s="7"/>
       <c r="M22" s="7" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="Q22" s="7" t="s">
         <v>14</v>
@@ -8610,28 +8750,28 @@
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="7" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
       <c r="M24" s="7" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="O24" s="7"/>
       <c r="P24" s="7" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="Q24" s="7">
         <v>5</v>
       </c>
       <c r="R24" s="7" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="S24" s="7" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="5:19">
@@ -8649,28 +8789,28 @@
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
       <c r="M25" s="8" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="O25" s="7"/>
       <c r="P25" s="7" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="Q25" s="7">
         <v>5</v>
       </c>
       <c r="R25" s="7" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="S25" s="7" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="5:19">
@@ -8738,7 +8878,7 @@
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
       <c r="L28" s="7" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="M28" s="5"/>
       <c r="N28" s="7">
@@ -8746,16 +8886,16 @@
       </c>
       <c r="O28" s="7"/>
       <c r="P28" s="7" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="Q28" s="7">
         <v>5</v>
       </c>
       <c r="R28" s="7" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="S28" s="7" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseLine.xlsx
+++ b/slots/resources/sample/BaseLine.xlsx
@@ -10,6 +10,9 @@
     <sheet name="BaseLine" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseLine!$E$241:$E$250</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -318,7 +321,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="178">
   <si>
     <t>id</t>
   </si>
@@ -735,6 +738,33 @@
   </si>
   <si>
     <t>3_5_7</t>
+  </si>
+  <si>
+    <t>1_6_9</t>
+  </si>
+  <si>
+    <t>1_6_10</t>
+  </si>
+  <si>
+    <t>2_6_9</t>
+  </si>
+  <si>
+    <t>2_6_10</t>
+  </si>
+  <si>
+    <t>2_7_10</t>
+  </si>
+  <si>
+    <t>2_7_11</t>
+  </si>
+  <si>
+    <t>3_7_10</t>
+  </si>
+  <si>
+    <t>3_7_11</t>
+  </si>
+  <si>
+    <t>3_8_11</t>
   </si>
   <si>
     <t>线路类型</t>
@@ -1614,7 +1644,14 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2447,7 +2484,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z240"/>
+  <dimension ref="A1:Z260"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.375"/>
@@ -8009,7 +8046,7 @@
     </row>
     <row r="218" spans="1:7">
       <c r="A218" s="5">
-        <f t="shared" ref="A218:A235" si="7">(B218+500000)*100+C218+G218*1000</f>
+        <f t="shared" ref="A218:A240" si="7">(B218+500000)*100+C218+G218*1000</f>
         <v>60250033</v>
       </c>
       <c r="B218" s="6">
@@ -8441,7 +8478,7 @@
     </row>
     <row r="236" spans="1:7">
       <c r="A236" s="5">
-        <f>(B236+500000)*100+C236+G236*1000</f>
+        <f t="shared" si="7"/>
         <v>60340001</v>
       </c>
       <c r="B236" s="6">
@@ -8465,7 +8502,7 @@
     </row>
     <row r="237" spans="1:7">
       <c r="A237" s="5">
-        <f>(B237+500000)*100+C237+G237*1000</f>
+        <f t="shared" si="7"/>
         <v>60340002</v>
       </c>
       <c r="B237" s="6">
@@ -8489,7 +8526,7 @@
     </row>
     <row r="238" spans="1:7">
       <c r="A238" s="5">
-        <f>(B238+500000)*100+C238+G238*1000</f>
+        <f t="shared" si="7"/>
         <v>60340003</v>
       </c>
       <c r="B238" s="6">
@@ -8513,7 +8550,7 @@
     </row>
     <row r="239" spans="1:7">
       <c r="A239" s="5">
-        <f>(B239+500000)*100+C239+G239*1000</f>
+        <f t="shared" si="7"/>
         <v>60340004</v>
       </c>
       <c r="B239" s="6">
@@ -8537,7 +8574,7 @@
     </row>
     <row r="240" spans="1:7">
       <c r="A240" s="5">
-        <f>(B240+500000)*100+C240+G240*1000</f>
+        <f t="shared" si="7"/>
         <v>60340005</v>
       </c>
       <c r="B240" s="6">
@@ -8559,27 +8596,513 @@
         <v>0</v>
       </c>
     </row>
+    <row r="241" spans="1:7">
+      <c r="A241" s="5">
+        <f t="shared" ref="A241:A250" si="8">(B241+500000)*100+C241+G241*1000</f>
+        <v>60350001</v>
+      </c>
+      <c r="B241" s="6">
+        <v>103500</v>
+      </c>
+      <c r="C241" s="7">
+        <v>1</v>
+      </c>
+      <c r="D241" s="9">
+        <v>1</v>
+      </c>
+      <c r="E241" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="F241" s="7">
+        <v>5</v>
+      </c>
+      <c r="G241" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7">
+      <c r="A242" s="5">
+        <f t="shared" si="8"/>
+        <v>60350002</v>
+      </c>
+      <c r="B242" s="6">
+        <v>103500</v>
+      </c>
+      <c r="C242" s="7">
+        <v>2</v>
+      </c>
+      <c r="D242" s="9">
+        <v>1</v>
+      </c>
+      <c r="E242" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F242" s="7">
+        <v>5</v>
+      </c>
+      <c r="G242" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7">
+      <c r="A243" s="5">
+        <f t="shared" si="8"/>
+        <v>60350003</v>
+      </c>
+      <c r="B243" s="6">
+        <v>103500</v>
+      </c>
+      <c r="C243" s="7">
+        <v>3</v>
+      </c>
+      <c r="D243" s="9">
+        <v>1</v>
+      </c>
+      <c r="E243" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="F243" s="7">
+        <v>5</v>
+      </c>
+      <c r="G243" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7">
+      <c r="A244" s="5">
+        <f t="shared" si="8"/>
+        <v>60350004</v>
+      </c>
+      <c r="B244" s="6">
+        <v>103500</v>
+      </c>
+      <c r="C244" s="7">
+        <v>4</v>
+      </c>
+      <c r="D244" s="9">
+        <v>1</v>
+      </c>
+      <c r="E244" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F244" s="7">
+        <v>5</v>
+      </c>
+      <c r="G244" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7">
+      <c r="A245" s="5">
+        <f t="shared" si="8"/>
+        <v>60350005</v>
+      </c>
+      <c r="B245" s="6">
+        <v>103500</v>
+      </c>
+      <c r="C245" s="7">
+        <v>5</v>
+      </c>
+      <c r="D245" s="9">
+        <v>1</v>
+      </c>
+      <c r="E245" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="F245" s="7">
+        <v>5</v>
+      </c>
+      <c r="G245" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7">
+      <c r="A246" s="5">
+        <f t="shared" si="8"/>
+        <v>60350006</v>
+      </c>
+      <c r="B246" s="6">
+        <v>103500</v>
+      </c>
+      <c r="C246" s="7">
+        <v>6</v>
+      </c>
+      <c r="D246" s="9">
+        <v>1</v>
+      </c>
+      <c r="E246" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="F246" s="7">
+        <v>5</v>
+      </c>
+      <c r="G246" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7">
+      <c r="A247" s="5">
+        <f t="shared" si="8"/>
+        <v>60350007</v>
+      </c>
+      <c r="B247" s="6">
+        <v>103500</v>
+      </c>
+      <c r="C247" s="7">
+        <v>7</v>
+      </c>
+      <c r="D247" s="9">
+        <v>1</v>
+      </c>
+      <c r="E247" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="F247" s="7">
+        <v>5</v>
+      </c>
+      <c r="G247" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7">
+      <c r="A248" s="5">
+        <f t="shared" si="8"/>
+        <v>60350008</v>
+      </c>
+      <c r="B248" s="6">
+        <v>103500</v>
+      </c>
+      <c r="C248" s="7">
+        <v>8</v>
+      </c>
+      <c r="D248" s="9">
+        <v>1</v>
+      </c>
+      <c r="E248" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="F248" s="7">
+        <v>5</v>
+      </c>
+      <c r="G248" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7">
+      <c r="A249" s="5">
+        <f t="shared" si="8"/>
+        <v>60350009</v>
+      </c>
+      <c r="B249" s="6">
+        <v>103500</v>
+      </c>
+      <c r="C249" s="7">
+        <v>9</v>
+      </c>
+      <c r="D249" s="9">
+        <v>1</v>
+      </c>
+      <c r="E249" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F249" s="7">
+        <v>5</v>
+      </c>
+      <c r="G249" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7">
+      <c r="A250" s="5">
+        <f t="shared" si="8"/>
+        <v>60350010</v>
+      </c>
+      <c r="B250" s="6">
+        <v>103500</v>
+      </c>
+      <c r="C250" s="7">
+        <v>10</v>
+      </c>
+      <c r="D250" s="9">
+        <v>1</v>
+      </c>
+      <c r="E250" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="F250" s="7">
+        <v>5</v>
+      </c>
+      <c r="G250" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7">
+      <c r="A251" s="5">
+        <f t="shared" ref="A251:A260" si="9">(B251+500000)*100+C251+G251*1000</f>
+        <v>60350101</v>
+      </c>
+      <c r="B251" s="6">
+        <v>103501</v>
+      </c>
+      <c r="C251" s="7">
+        <v>1</v>
+      </c>
+      <c r="D251" s="9">
+        <v>1</v>
+      </c>
+      <c r="E251" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="F251" s="7">
+        <v>5</v>
+      </c>
+      <c r="G251" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7">
+      <c r="A252" s="5">
+        <f t="shared" si="9"/>
+        <v>60350102</v>
+      </c>
+      <c r="B252" s="6">
+        <v>103501</v>
+      </c>
+      <c r="C252" s="7">
+        <v>2</v>
+      </c>
+      <c r="D252" s="9">
+        <v>1</v>
+      </c>
+      <c r="E252" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F252" s="7">
+        <v>5</v>
+      </c>
+      <c r="G252" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7">
+      <c r="A253" s="5">
+        <f t="shared" si="9"/>
+        <v>60350103</v>
+      </c>
+      <c r="B253" s="6">
+        <v>103501</v>
+      </c>
+      <c r="C253" s="7">
+        <v>3</v>
+      </c>
+      <c r="D253" s="9">
+        <v>1</v>
+      </c>
+      <c r="E253" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="F253" s="7">
+        <v>5</v>
+      </c>
+      <c r="G253" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7">
+      <c r="A254" s="5">
+        <f t="shared" si="9"/>
+        <v>60350104</v>
+      </c>
+      <c r="B254" s="6">
+        <v>103501</v>
+      </c>
+      <c r="C254" s="7">
+        <v>4</v>
+      </c>
+      <c r="D254" s="9">
+        <v>1</v>
+      </c>
+      <c r="E254" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F254" s="7">
+        <v>5</v>
+      </c>
+      <c r="G254" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7">
+      <c r="A255" s="5">
+        <f t="shared" si="9"/>
+        <v>60350105</v>
+      </c>
+      <c r="B255" s="6">
+        <v>103501</v>
+      </c>
+      <c r="C255" s="7">
+        <v>5</v>
+      </c>
+      <c r="D255" s="9">
+        <v>1</v>
+      </c>
+      <c r="E255" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="F255" s="7">
+        <v>5</v>
+      </c>
+      <c r="G255" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7">
+      <c r="A256" s="5">
+        <f t="shared" si="9"/>
+        <v>60350106</v>
+      </c>
+      <c r="B256" s="6">
+        <v>103501</v>
+      </c>
+      <c r="C256" s="7">
+        <v>6</v>
+      </c>
+      <c r="D256" s="9">
+        <v>1</v>
+      </c>
+      <c r="E256" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="F256" s="7">
+        <v>5</v>
+      </c>
+      <c r="G256" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7">
+      <c r="A257" s="5">
+        <f t="shared" si="9"/>
+        <v>60350107</v>
+      </c>
+      <c r="B257" s="6">
+        <v>103501</v>
+      </c>
+      <c r="C257" s="7">
+        <v>7</v>
+      </c>
+      <c r="D257" s="9">
+        <v>1</v>
+      </c>
+      <c r="E257" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="F257" s="7">
+        <v>5</v>
+      </c>
+      <c r="G257" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7">
+      <c r="A258" s="5">
+        <f t="shared" si="9"/>
+        <v>60350108</v>
+      </c>
+      <c r="B258" s="6">
+        <v>103501</v>
+      </c>
+      <c r="C258" s="7">
+        <v>8</v>
+      </c>
+      <c r="D258" s="9">
+        <v>1</v>
+      </c>
+      <c r="E258" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="F258" s="7">
+        <v>5</v>
+      </c>
+      <c r="G258" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7">
+      <c r="A259" s="5">
+        <f t="shared" si="9"/>
+        <v>60350109</v>
+      </c>
+      <c r="B259" s="6">
+        <v>103501</v>
+      </c>
+      <c r="C259" s="7">
+        <v>9</v>
+      </c>
+      <c r="D259" s="9">
+        <v>1</v>
+      </c>
+      <c r="E259" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F259" s="7">
+        <v>5</v>
+      </c>
+      <c r="G259" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7">
+      <c r="A260" s="5">
+        <f t="shared" si="9"/>
+        <v>60350110</v>
+      </c>
+      <c r="B260" s="6">
+        <v>103501</v>
+      </c>
+      <c r="C260" s="7">
+        <v>10</v>
+      </c>
+      <c r="D260" s="9">
+        <v>1</v>
+      </c>
+      <c r="E260" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="F260" s="7">
+        <v>5</v>
+      </c>
+      <c r="G260" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="E236">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E237">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E237">
+  <conditionalFormatting sqref="E238">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E238">
+  <conditionalFormatting sqref="E239">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E239">
+  <conditionalFormatting sqref="E240">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E240">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="E161:E185">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E186:E235">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E241:E250">
+    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E251:E260">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -8603,30 +9126,30 @@
         <v>1</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>2</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>4</v>
       </c>
       <c r="L20" s="4"/>
       <c r="M20" s="4" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="Q20" s="4" t="s">
         <v>5</v>
@@ -8635,7 +9158,7 @@
         <v>3</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="5:19">
@@ -8653,29 +9176,29 @@
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="7" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="L21" s="7"/>
       <c r="M21" s="7" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="Q21" s="7" t="s">
         <v>7</v>
       </c>
       <c r="R21" s="7" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="S21" s="7"/>
     </row>
@@ -8687,30 +9210,30 @@
         <v>10</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>11</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="K22" s="7" t="s">
         <v>13</v>
       </c>
       <c r="L22" s="7"/>
       <c r="M22" s="7" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="Q22" s="7" t="s">
         <v>14</v>
@@ -8750,28 +9273,28 @@
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="7" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
       <c r="M24" s="7" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="O24" s="7"/>
       <c r="P24" s="7" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="Q24" s="7">
         <v>5</v>
       </c>
       <c r="R24" s="7" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="S24" s="7" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="5:19">
@@ -8789,28 +9312,28 @@
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
       <c r="M25" s="8" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="O25" s="7"/>
       <c r="P25" s="7" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="Q25" s="7">
         <v>5</v>
       </c>
       <c r="R25" s="7" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="S25" s="7" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="5:19">
@@ -8878,7 +9401,7 @@
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
       <c r="L28" s="7" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="M28" s="5"/>
       <c r="N28" s="7">
@@ -8886,16 +9409,16 @@
       </c>
       <c r="O28" s="7"/>
       <c r="P28" s="7" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="Q28" s="7">
         <v>5</v>
       </c>
       <c r="R28" s="7" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="S28" s="7" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseLine.xlsx
+++ b/slots/resources/sample/BaseLine.xlsx
@@ -321,7 +321,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="178">
   <si>
     <t>id</t>
   </si>
@@ -1644,14 +1644,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2484,7 +2477,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z260"/>
+  <dimension ref="A1:Z265"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.375"/>
@@ -9076,33 +9069,168 @@
         <v>0</v>
       </c>
     </row>
+    <row r="261" spans="1:7">
+      <c r="A261" s="5">
+        <f>(B261+500000)*100+C261+G261*1000</f>
+        <v>60360001</v>
+      </c>
+      <c r="B261" s="6">
+        <v>103600</v>
+      </c>
+      <c r="C261" s="7">
+        <v>1</v>
+      </c>
+      <c r="D261" s="9">
+        <v>1</v>
+      </c>
+      <c r="E261" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F261" s="7">
+        <v>5</v>
+      </c>
+      <c r="G261" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7">
+      <c r="A262" s="5">
+        <f>(B262+500000)*100+C262+G262*1000</f>
+        <v>60360002</v>
+      </c>
+      <c r="B262" s="6">
+        <v>103600</v>
+      </c>
+      <c r="C262" s="7">
+        <v>2</v>
+      </c>
+      <c r="D262" s="9">
+        <v>1</v>
+      </c>
+      <c r="E262" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="F262" s="7">
+        <v>5</v>
+      </c>
+      <c r="G262" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7">
+      <c r="A263" s="5">
+        <f>(B263+500000)*100+C263+G263*1000</f>
+        <v>60360003</v>
+      </c>
+      <c r="B263" s="6">
+        <v>103600</v>
+      </c>
+      <c r="C263" s="7">
+        <v>3</v>
+      </c>
+      <c r="D263" s="9">
+        <v>1</v>
+      </c>
+      <c r="E263" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="F263" s="7">
+        <v>5</v>
+      </c>
+      <c r="G263" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7">
+      <c r="A264" s="5">
+        <f>(B264+500000)*100+C264+G264*1000</f>
+        <v>60360004</v>
+      </c>
+      <c r="B264" s="6">
+        <v>103600</v>
+      </c>
+      <c r="C264" s="7">
+        <v>4</v>
+      </c>
+      <c r="D264" s="9">
+        <v>1</v>
+      </c>
+      <c r="E264" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="F264" s="7">
+        <v>5</v>
+      </c>
+      <c r="G264" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7">
+      <c r="A265" s="5">
+        <f>(B265+500000)*100+C265+G265*1000</f>
+        <v>60360005</v>
+      </c>
+      <c r="B265" s="6">
+        <v>103600</v>
+      </c>
+      <c r="C265" s="7">
+        <v>5</v>
+      </c>
+      <c r="D265" s="9">
+        <v>1</v>
+      </c>
+      <c r="E265" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="F265" s="7">
+        <v>5</v>
+      </c>
+      <c r="G265" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="E236">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E237">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E238">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E239">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E240">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E261">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E238">
+  <conditionalFormatting sqref="E262">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E239">
+  <conditionalFormatting sqref="E263">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E240">
+  <conditionalFormatting sqref="E264">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E265">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E161:E185">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E186:E235">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E241:E250">
-    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E251:E260">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/slots/resources/sample/BaseLine.xlsx
+++ b/slots/resources/sample/BaseLine.xlsx
@@ -321,7 +321,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="193">
   <si>
     <t>id</t>
   </si>
@@ -765,6 +765,51 @@
   </si>
   <si>
     <t>3_8_11</t>
+  </si>
+  <si>
+    <t>1_6_11_16_21</t>
+  </si>
+  <si>
+    <t>2_7_12_17_22</t>
+  </si>
+  <si>
+    <t>3_8_13_18_23</t>
+  </si>
+  <si>
+    <t>4_9_14_19_24</t>
+  </si>
+  <si>
+    <t>5_10_15_20_25</t>
+  </si>
+  <si>
+    <t>1_7_13_19_25</t>
+  </si>
+  <si>
+    <t>5_9_13_17_21</t>
+  </si>
+  <si>
+    <t>1_7_11_17_21</t>
+  </si>
+  <si>
+    <t>2_6_12_16_22</t>
+  </si>
+  <si>
+    <t>2_8_12_18_22</t>
+  </si>
+  <si>
+    <t>3_7_13_17_23</t>
+  </si>
+  <si>
+    <t>3_9_13_19_23</t>
+  </si>
+  <si>
+    <t>4_8_14_18_24</t>
+  </si>
+  <si>
+    <t>4_10_14_20_24</t>
+  </si>
+  <si>
+    <t>5_9_15_19_25</t>
   </si>
   <si>
     <t>线路类型</t>
@@ -2477,7 +2522,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z265"/>
+  <dimension ref="A1:Z285"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.375"/>
@@ -8831,7 +8876,7 @@
     </row>
     <row r="251" spans="1:7">
       <c r="A251" s="5">
-        <f t="shared" ref="A251:A260" si="9">(B251+500000)*100+C251+G251*1000</f>
+        <f t="shared" ref="A251:A270" si="9">(B251+500000)*100+C251+G251*1000</f>
         <v>60350101</v>
       </c>
       <c r="B251" s="6">
@@ -9071,7 +9116,7 @@
     </row>
     <row r="261" spans="1:7">
       <c r="A261" s="5">
-        <f>(B261+500000)*100+C261+G261*1000</f>
+        <f t="shared" si="9"/>
         <v>60360001</v>
       </c>
       <c r="B261" s="6">
@@ -9095,7 +9140,7 @@
     </row>
     <row r="262" spans="1:7">
       <c r="A262" s="5">
-        <f>(B262+500000)*100+C262+G262*1000</f>
+        <f t="shared" si="9"/>
         <v>60360002</v>
       </c>
       <c r="B262" s="6">
@@ -9119,7 +9164,7 @@
     </row>
     <row r="263" spans="1:7">
       <c r="A263" s="5">
-        <f>(B263+500000)*100+C263+G263*1000</f>
+        <f t="shared" si="9"/>
         <v>60360003</v>
       </c>
       <c r="B263" s="6">
@@ -9143,7 +9188,7 @@
     </row>
     <row r="264" spans="1:7">
       <c r="A264" s="5">
-        <f>(B264+500000)*100+C264+G264*1000</f>
+        <f t="shared" si="9"/>
         <v>60360004</v>
       </c>
       <c r="B264" s="6">
@@ -9167,7 +9212,7 @@
     </row>
     <row r="265" spans="1:7">
       <c r="A265" s="5">
-        <f>(B265+500000)*100+C265+G265*1000</f>
+        <f t="shared" si="9"/>
         <v>60360005</v>
       </c>
       <c r="B265" s="6">
@@ -9189,48 +9234,543 @@
         <v>0</v>
       </c>
     </row>
+    <row r="266" spans="1:7">
+      <c r="A266" s="5">
+        <f t="shared" si="9"/>
+        <v>60340101</v>
+      </c>
+      <c r="B266" s="6">
+        <v>103401</v>
+      </c>
+      <c r="C266" s="7">
+        <v>1</v>
+      </c>
+      <c r="D266" s="9">
+        <v>1</v>
+      </c>
+      <c r="E266" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F266" s="7">
+        <v>5</v>
+      </c>
+      <c r="G266" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7">
+      <c r="A267" s="5">
+        <f t="shared" si="9"/>
+        <v>60340102</v>
+      </c>
+      <c r="B267" s="6">
+        <v>103401</v>
+      </c>
+      <c r="C267" s="7">
+        <v>2</v>
+      </c>
+      <c r="D267" s="9">
+        <v>1</v>
+      </c>
+      <c r="E267" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="F267" s="7">
+        <v>5</v>
+      </c>
+      <c r="G267" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7">
+      <c r="A268" s="5">
+        <f t="shared" si="9"/>
+        <v>60340103</v>
+      </c>
+      <c r="B268" s="6">
+        <v>103401</v>
+      </c>
+      <c r="C268" s="7">
+        <v>3</v>
+      </c>
+      <c r="D268" s="9">
+        <v>1</v>
+      </c>
+      <c r="E268" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="F268" s="7">
+        <v>5</v>
+      </c>
+      <c r="G268" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7">
+      <c r="A269" s="5">
+        <f t="shared" si="9"/>
+        <v>60340104</v>
+      </c>
+      <c r="B269" s="6">
+        <v>103401</v>
+      </c>
+      <c r="C269" s="7">
+        <v>4</v>
+      </c>
+      <c r="D269" s="9">
+        <v>1</v>
+      </c>
+      <c r="E269" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="F269" s="7">
+        <v>5</v>
+      </c>
+      <c r="G269" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7">
+      <c r="A270" s="5">
+        <f t="shared" si="9"/>
+        <v>60340105</v>
+      </c>
+      <c r="B270" s="6">
+        <v>103401</v>
+      </c>
+      <c r="C270" s="7">
+        <v>5</v>
+      </c>
+      <c r="D270" s="9">
+        <v>1</v>
+      </c>
+      <c r="E270" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="F270" s="7">
+        <v>5</v>
+      </c>
+      <c r="G270" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7">
+      <c r="A271" s="5">
+        <f t="shared" ref="A271:A285" si="10">(B271+500000)*100+C271+G271*1000</f>
+        <v>60200001</v>
+      </c>
+      <c r="B271" s="6">
+        <v>102000</v>
+      </c>
+      <c r="C271" s="7">
+        <v>1</v>
+      </c>
+      <c r="D271" s="9">
+        <v>1</v>
+      </c>
+      <c r="E271" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="F271" s="7">
+        <v>5</v>
+      </c>
+      <c r="G271" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7">
+      <c r="A272" s="5">
+        <f t="shared" si="10"/>
+        <v>60200002</v>
+      </c>
+      <c r="B272" s="6">
+        <v>102000</v>
+      </c>
+      <c r="C272" s="7">
+        <v>2</v>
+      </c>
+      <c r="D272" s="9">
+        <v>1</v>
+      </c>
+      <c r="E272" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="F272" s="7">
+        <v>5</v>
+      </c>
+      <c r="G272" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7">
+      <c r="A273" s="5">
+        <f t="shared" si="10"/>
+        <v>60200003</v>
+      </c>
+      <c r="B273" s="6">
+        <v>102000</v>
+      </c>
+      <c r="C273" s="7">
+        <v>3</v>
+      </c>
+      <c r="D273" s="9">
+        <v>1</v>
+      </c>
+      <c r="E273" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="F273" s="7">
+        <v>5</v>
+      </c>
+      <c r="G273" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7">
+      <c r="A274" s="5">
+        <f t="shared" si="10"/>
+        <v>60200004</v>
+      </c>
+      <c r="B274" s="6">
+        <v>102000</v>
+      </c>
+      <c r="C274" s="7">
+        <v>4</v>
+      </c>
+      <c r="D274" s="9">
+        <v>1</v>
+      </c>
+      <c r="E274" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="F274" s="7">
+        <v>5</v>
+      </c>
+      <c r="G274" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7">
+      <c r="A275" s="5">
+        <f t="shared" si="10"/>
+        <v>60200005</v>
+      </c>
+      <c r="B275" s="6">
+        <v>102000</v>
+      </c>
+      <c r="C275" s="7">
+        <v>5</v>
+      </c>
+      <c r="D275" s="9">
+        <v>1</v>
+      </c>
+      <c r="E275" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="F275" s="7">
+        <v>5</v>
+      </c>
+      <c r="G275" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7">
+      <c r="A276" s="5">
+        <f t="shared" si="10"/>
+        <v>60200006</v>
+      </c>
+      <c r="B276" s="6">
+        <v>102000</v>
+      </c>
+      <c r="C276" s="7">
+        <v>6</v>
+      </c>
+      <c r="D276" s="9">
+        <v>1</v>
+      </c>
+      <c r="E276" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="F276" s="7">
+        <v>5</v>
+      </c>
+      <c r="G276" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7">
+      <c r="A277" s="5">
+        <f t="shared" si="10"/>
+        <v>60201007</v>
+      </c>
+      <c r="B277" s="6">
+        <v>102000</v>
+      </c>
+      <c r="C277" s="7">
+        <v>7</v>
+      </c>
+      <c r="D277" s="9">
+        <v>1</v>
+      </c>
+      <c r="E277" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="F277" s="7">
+        <v>5</v>
+      </c>
+      <c r="G277" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7">
+      <c r="A278" s="5">
+        <f t="shared" si="10"/>
+        <v>60202008</v>
+      </c>
+      <c r="B278" s="6">
+        <v>102000</v>
+      </c>
+      <c r="C278" s="7">
+        <v>8</v>
+      </c>
+      <c r="D278" s="9">
+        <v>1</v>
+      </c>
+      <c r="E278" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="F278" s="7">
+        <v>5</v>
+      </c>
+      <c r="G278" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7">
+      <c r="A279" s="5">
+        <f t="shared" si="10"/>
+        <v>60203009</v>
+      </c>
+      <c r="B279" s="6">
+        <v>102000</v>
+      </c>
+      <c r="C279" s="7">
+        <v>9</v>
+      </c>
+      <c r="D279" s="9">
+        <v>1</v>
+      </c>
+      <c r="E279" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F279" s="7">
+        <v>5</v>
+      </c>
+      <c r="G279" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7">
+      <c r="A280" s="5">
+        <f t="shared" si="10"/>
+        <v>60204010</v>
+      </c>
+      <c r="B280" s="6">
+        <v>102000</v>
+      </c>
+      <c r="C280" s="7">
+        <v>10</v>
+      </c>
+      <c r="D280" s="9">
+        <v>1</v>
+      </c>
+      <c r="E280" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="F280" s="7">
+        <v>5</v>
+      </c>
+      <c r="G280" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7">
+      <c r="A281" s="5">
+        <f t="shared" si="10"/>
+        <v>60205011</v>
+      </c>
+      <c r="B281" s="6">
+        <v>102000</v>
+      </c>
+      <c r="C281" s="7">
+        <v>11</v>
+      </c>
+      <c r="D281" s="9">
+        <v>1</v>
+      </c>
+      <c r="E281" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F281" s="7">
+        <v>5</v>
+      </c>
+      <c r="G281" s="9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7">
+      <c r="A282" s="5">
+        <f t="shared" si="10"/>
+        <v>60206012</v>
+      </c>
+      <c r="B282" s="6">
+        <v>102000</v>
+      </c>
+      <c r="C282" s="7">
+        <v>12</v>
+      </c>
+      <c r="D282" s="9">
+        <v>1</v>
+      </c>
+      <c r="E282" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="F282" s="7">
+        <v>5</v>
+      </c>
+      <c r="G282" s="9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7">
+      <c r="A283" s="5">
+        <f t="shared" si="10"/>
+        <v>60207013</v>
+      </c>
+      <c r="B283" s="6">
+        <v>102000</v>
+      </c>
+      <c r="C283" s="7">
+        <v>13</v>
+      </c>
+      <c r="D283" s="9">
+        <v>1</v>
+      </c>
+      <c r="E283" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="F283" s="7">
+        <v>5</v>
+      </c>
+      <c r="G283" s="9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
+      <c r="A284" s="5">
+        <f t="shared" si="10"/>
+        <v>60208014</v>
+      </c>
+      <c r="B284" s="6">
+        <v>102000</v>
+      </c>
+      <c r="C284" s="7">
+        <v>14</v>
+      </c>
+      <c r="D284" s="9">
+        <v>1</v>
+      </c>
+      <c r="E284" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="F284" s="7">
+        <v>5</v>
+      </c>
+      <c r="G284" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7">
+      <c r="A285" s="5">
+        <f t="shared" si="10"/>
+        <v>60209015</v>
+      </c>
+      <c r="B285" s="6">
+        <v>102000</v>
+      </c>
+      <c r="C285" s="7">
+        <v>15</v>
+      </c>
+      <c r="D285" s="9">
+        <v>1</v>
+      </c>
+      <c r="E285" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F285" s="7">
+        <v>5</v>
+      </c>
+      <c r="G285" s="9">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="E236">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E237">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E238">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E239">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E240">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E261">
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E238">
+  <conditionalFormatting sqref="E262">
     <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E239">
+  <conditionalFormatting sqref="E263">
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E240">
+  <conditionalFormatting sqref="E264">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E261">
+  <conditionalFormatting sqref="E265">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E266">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E262">
+  <conditionalFormatting sqref="E267">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E263">
+  <conditionalFormatting sqref="E268">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E264">
+  <conditionalFormatting sqref="E269">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E265">
+  <conditionalFormatting sqref="E270">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E161:E185">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E186:E235">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E241:E250">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E251:E260">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -9254,30 +9794,30 @@
         <v>1</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>2</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>4</v>
       </c>
       <c r="L20" s="4"/>
       <c r="M20" s="4" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="Q20" s="4" t="s">
         <v>5</v>
@@ -9286,7 +9826,7 @@
         <v>3</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="5:19">
@@ -9304,29 +9844,29 @@
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="7" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="L21" s="7"/>
       <c r="M21" s="7" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="Q21" s="7" t="s">
         <v>7</v>
       </c>
       <c r="R21" s="7" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="S21" s="7"/>
     </row>
@@ -9338,30 +9878,30 @@
         <v>10</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>11</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="K22" s="7" t="s">
         <v>13</v>
       </c>
       <c r="L22" s="7"/>
       <c r="M22" s="7" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="Q22" s="7" t="s">
         <v>14</v>
@@ -9401,28 +9941,28 @@
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="7" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
       <c r="M24" s="7" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="O24" s="7"/>
       <c r="P24" s="7" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="Q24" s="7">
         <v>5</v>
       </c>
       <c r="R24" s="7" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="S24" s="7" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="5:19">
@@ -9440,28 +9980,28 @@
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
       <c r="M25" s="8" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="O25" s="7"/>
       <c r="P25" s="7" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="Q25" s="7">
         <v>5</v>
       </c>
       <c r="R25" s="7" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="S25" s="7" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="5:19">
@@ -9529,7 +10069,7 @@
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
       <c r="L28" s="7" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="M28" s="5"/>
       <c r="N28" s="7">
@@ -9537,16 +10077,16 @@
       </c>
       <c r="O28" s="7"/>
       <c r="P28" s="7" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="Q28" s="7">
         <v>5</v>
       </c>
       <c r="R28" s="7" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="S28" s="7" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseLine.xlsx
+++ b/slots/resources/sample/BaseLine.xlsx
@@ -321,7 +321,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="201">
   <si>
     <t>id</t>
   </si>
@@ -810,6 +810,30 @@
   </si>
   <si>
     <t>5_9_15_19_25</t>
+  </si>
+  <si>
+    <t>3_6_9_11_13</t>
+  </si>
+  <si>
+    <t>1_4_7_11_15</t>
+  </si>
+  <si>
+    <t>2_5_8_10_14</t>
+  </si>
+  <si>
+    <t>2_5_8_12_14</t>
+  </si>
+  <si>
+    <t>2_4_8_11_14</t>
+  </si>
+  <si>
+    <t>2_6_8_11_14</t>
+  </si>
+  <si>
+    <t>1_5_8_11_15</t>
+  </si>
+  <si>
+    <t>2_6_9_11_13</t>
   </si>
   <si>
     <t>线路类型</t>
@@ -1689,7 +1713,14 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2522,7 +2553,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z285"/>
+  <dimension ref="A1:Z325"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.375"/>
@@ -9501,7 +9532,7 @@
     <row r="277" spans="1:7">
       <c r="A277" s="5">
         <f t="shared" si="10"/>
-        <v>60201007</v>
+        <v>60200007</v>
       </c>
       <c r="B277" s="6">
         <v>102000</v>
@@ -9519,13 +9550,13 @@
         <v>5</v>
       </c>
       <c r="G277" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278" spans="1:7">
       <c r="A278" s="5">
         <f t="shared" si="10"/>
-        <v>60202008</v>
+        <v>60200008</v>
       </c>
       <c r="B278" s="6">
         <v>102000</v>
@@ -9543,13 +9574,13 @@
         <v>5</v>
       </c>
       <c r="G278" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279" spans="1:7">
       <c r="A279" s="5">
         <f t="shared" si="10"/>
-        <v>60203009</v>
+        <v>60200009</v>
       </c>
       <c r="B279" s="6">
         <v>102000</v>
@@ -9567,13 +9598,13 @@
         <v>5</v>
       </c>
       <c r="G279" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="280" spans="1:7">
       <c r="A280" s="5">
         <f t="shared" si="10"/>
-        <v>60204010</v>
+        <v>60200010</v>
       </c>
       <c r="B280" s="6">
         <v>102000</v>
@@ -9591,13 +9622,13 @@
         <v>5</v>
       </c>
       <c r="G280" s="9">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="281" spans="1:7">
       <c r="A281" s="5">
         <f t="shared" si="10"/>
-        <v>60205011</v>
+        <v>60200011</v>
       </c>
       <c r="B281" s="6">
         <v>102000</v>
@@ -9615,13 +9646,13 @@
         <v>5</v>
       </c>
       <c r="G281" s="9">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="282" spans="1:7">
       <c r="A282" s="5">
         <f t="shared" si="10"/>
-        <v>60206012</v>
+        <v>60200012</v>
       </c>
       <c r="B282" s="6">
         <v>102000</v>
@@ -9639,13 +9670,13 @@
         <v>5</v>
       </c>
       <c r="G282" s="9">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="283" spans="1:7">
       <c r="A283" s="5">
         <f t="shared" si="10"/>
-        <v>60207013</v>
+        <v>60200013</v>
       </c>
       <c r="B283" s="6">
         <v>102000</v>
@@ -9663,13 +9694,13 @@
         <v>5</v>
       </c>
       <c r="G283" s="9">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="284" spans="1:7">
       <c r="A284" s="5">
         <f t="shared" si="10"/>
-        <v>60208014</v>
+        <v>60200014</v>
       </c>
       <c r="B284" s="6">
         <v>102000</v>
@@ -9687,13 +9718,13 @@
         <v>5</v>
       </c>
       <c r="G284" s="9">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285" spans="1:7">
       <c r="A285" s="5">
         <f t="shared" si="10"/>
-        <v>60209015</v>
+        <v>60200015</v>
       </c>
       <c r="B285" s="6">
         <v>102000</v>
@@ -9711,7 +9742,1012 @@
         <v>5</v>
       </c>
       <c r="G285" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7">
+      <c r="A286" s="5">
+        <f t="shared" ref="A286:A325" si="11">(B286+500000)*100+C286+G286*1000</f>
+        <v>60380001</v>
+      </c>
+      <c r="B286" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C286" s="7">
+        <v>1</v>
+      </c>
+      <c r="D286" s="9">
+        <v>1</v>
+      </c>
+      <c r="E286" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F286" s="7">
+        <v>5</v>
+      </c>
+      <c r="G286" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7">
+      <c r="A287" s="5">
+        <f t="shared" si="11"/>
+        <v>60380002</v>
+      </c>
+      <c r="B287" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C287" s="7">
+        <v>2</v>
+      </c>
+      <c r="D287" s="9">
+        <v>1</v>
+      </c>
+      <c r="E287" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F287" s="7">
+        <v>5</v>
+      </c>
+      <c r="G287" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7">
+      <c r="A288" s="5">
+        <f t="shared" si="11"/>
+        <v>60380003</v>
+      </c>
+      <c r="B288" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C288" s="7">
+        <v>3</v>
+      </c>
+      <c r="D288" s="9">
+        <v>1</v>
+      </c>
+      <c r="E288" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F288" s="7">
+        <v>5</v>
+      </c>
+      <c r="G288" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:19">
+      <c r="A289" s="5">
+        <f t="shared" si="11"/>
+        <v>60380004</v>
+      </c>
+      <c r="B289" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C289" s="7">
+        <v>4</v>
+      </c>
+      <c r="D289" s="9">
+        <v>1</v>
+      </c>
+      <c r="E289" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F289" s="7">
+        <v>5</v>
+      </c>
+      <c r="G289" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:19">
+      <c r="A290" s="5">
+        <f t="shared" si="11"/>
+        <v>60380005</v>
+      </c>
+      <c r="B290" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C290" s="7">
+        <v>5</v>
+      </c>
+      <c r="D290" s="9">
+        <v>1</v>
+      </c>
+      <c r="E290" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F290" s="7">
+        <v>5</v>
+      </c>
+      <c r="G290" s="9">
+        <v>0</v>
+      </c>
+      <c r="O290" s="9">
+        <v>1</v>
+      </c>
+      <c r="P290" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q290" s="9">
+        <v>7</v>
+      </c>
+      <c r="R290" s="9">
+        <v>10</v>
+      </c>
+      <c r="S290" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="291" spans="1:19">
+      <c r="A291" s="5">
+        <f t="shared" si="11"/>
+        <v>60380006</v>
+      </c>
+      <c r="B291" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C291" s="7">
+        <v>6</v>
+      </c>
+      <c r="D291" s="9">
+        <v>1</v>
+      </c>
+      <c r="E291" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F291" s="7">
+        <v>5</v>
+      </c>
+      <c r="G291" s="9">
+        <v>0</v>
+      </c>
+      <c r="O291" s="9">
+        <v>2</v>
+      </c>
+      <c r="P291" s="9">
+        <v>5</v>
+      </c>
+      <c r="Q291" s="9">
+        <v>8</v>
+      </c>
+      <c r="R291" s="9">
+        <v>11</v>
+      </c>
+      <c r="S291" s="9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="292" spans="1:19">
+      <c r="A292" s="5">
+        <f t="shared" si="11"/>
+        <v>60380007</v>
+      </c>
+      <c r="B292" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C292" s="7">
+        <v>7</v>
+      </c>
+      <c r="D292" s="9">
+        <v>1</v>
+      </c>
+      <c r="E292" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F292" s="7">
+        <v>5</v>
+      </c>
+      <c r="G292" s="9">
+        <v>0</v>
+      </c>
+      <c r="O292" s="9">
+        <v>3</v>
+      </c>
+      <c r="P292" s="9">
+        <v>6</v>
+      </c>
+      <c r="Q292" s="9">
         <v>9</v>
+      </c>
+      <c r="R292" s="9">
+        <v>12</v>
+      </c>
+      <c r="S292" s="9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="293" spans="1:19">
+      <c r="A293" s="5">
+        <f t="shared" si="11"/>
+        <v>60380008</v>
+      </c>
+      <c r="B293" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C293" s="7">
+        <v>8</v>
+      </c>
+      <c r="D293" s="9">
+        <v>1</v>
+      </c>
+      <c r="E293" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F293" s="7">
+        <v>5</v>
+      </c>
+      <c r="G293" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:19">
+      <c r="A294" s="5">
+        <f t="shared" si="11"/>
+        <v>60380009</v>
+      </c>
+      <c r="B294" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C294" s="7">
+        <v>9</v>
+      </c>
+      <c r="D294" s="9">
+        <v>1</v>
+      </c>
+      <c r="E294" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F294" s="7">
+        <v>5</v>
+      </c>
+      <c r="G294" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:19">
+      <c r="A295" s="5">
+        <f t="shared" si="11"/>
+        <v>60380010</v>
+      </c>
+      <c r="B295" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C295" s="7">
+        <v>10</v>
+      </c>
+      <c r="D295" s="9">
+        <v>1</v>
+      </c>
+      <c r="E295" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F295" s="7">
+        <v>5</v>
+      </c>
+      <c r="G295" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:19">
+      <c r="A296" s="5">
+        <f t="shared" si="11"/>
+        <v>60380011</v>
+      </c>
+      <c r="B296" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C296" s="7">
+        <v>11</v>
+      </c>
+      <c r="D296" s="9">
+        <v>1</v>
+      </c>
+      <c r="E296" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="F296" s="7">
+        <v>5</v>
+      </c>
+      <c r="G296" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:19">
+      <c r="A297" s="5">
+        <f t="shared" si="11"/>
+        <v>60380012</v>
+      </c>
+      <c r="B297" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C297" s="7">
+        <v>12</v>
+      </c>
+      <c r="D297" s="9">
+        <v>1</v>
+      </c>
+      <c r="E297" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F297" s="7">
+        <v>5</v>
+      </c>
+      <c r="G297" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:19">
+      <c r="A298" s="5">
+        <f t="shared" si="11"/>
+        <v>60380013</v>
+      </c>
+      <c r="B298" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C298" s="7">
+        <v>13</v>
+      </c>
+      <c r="D298" s="9">
+        <v>1</v>
+      </c>
+      <c r="E298" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F298" s="7">
+        <v>5</v>
+      </c>
+      <c r="G298" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:19">
+      <c r="A299" s="5">
+        <f t="shared" si="11"/>
+        <v>60380014</v>
+      </c>
+      <c r="B299" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C299" s="7">
+        <v>14</v>
+      </c>
+      <c r="D299" s="9">
+        <v>1</v>
+      </c>
+      <c r="E299" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F299" s="7">
+        <v>5</v>
+      </c>
+      <c r="G299" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:19">
+      <c r="A300" s="5">
+        <f t="shared" si="11"/>
+        <v>60380015</v>
+      </c>
+      <c r="B300" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C300" s="7">
+        <v>15</v>
+      </c>
+      <c r="D300" s="9">
+        <v>1</v>
+      </c>
+      <c r="E300" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F300" s="7">
+        <v>5</v>
+      </c>
+      <c r="G300" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:19">
+      <c r="A301" s="5">
+        <f t="shared" si="11"/>
+        <v>60380016</v>
+      </c>
+      <c r="B301" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C301" s="7">
+        <v>16</v>
+      </c>
+      <c r="D301" s="9">
+        <v>1</v>
+      </c>
+      <c r="E301" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F301" s="7">
+        <v>5</v>
+      </c>
+      <c r="G301" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:19">
+      <c r="A302" s="5">
+        <f t="shared" si="11"/>
+        <v>60380017</v>
+      </c>
+      <c r="B302" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C302" s="7">
+        <v>17</v>
+      </c>
+      <c r="D302" s="9">
+        <v>1</v>
+      </c>
+      <c r="E302" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F302" s="7">
+        <v>5</v>
+      </c>
+      <c r="G302" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:19">
+      <c r="A303" s="5">
+        <f t="shared" si="11"/>
+        <v>60380018</v>
+      </c>
+      <c r="B303" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C303" s="7">
+        <v>18</v>
+      </c>
+      <c r="D303" s="9">
+        <v>1</v>
+      </c>
+      <c r="E303" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F303" s="7">
+        <v>5</v>
+      </c>
+      <c r="G303" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:19">
+      <c r="A304" s="5">
+        <f t="shared" si="11"/>
+        <v>60380019</v>
+      </c>
+      <c r="B304" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C304" s="7">
+        <v>19</v>
+      </c>
+      <c r="D304" s="9">
+        <v>1</v>
+      </c>
+      <c r="E304" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F304" s="7">
+        <v>5</v>
+      </c>
+      <c r="G304" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7">
+      <c r="A305" s="5">
+        <f t="shared" si="11"/>
+        <v>60380020</v>
+      </c>
+      <c r="B305" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C305" s="7">
+        <v>20</v>
+      </c>
+      <c r="D305" s="9">
+        <v>1</v>
+      </c>
+      <c r="E305" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F305" s="7">
+        <v>5</v>
+      </c>
+      <c r="G305" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7">
+      <c r="A306" s="5">
+        <f t="shared" si="11"/>
+        <v>60380021</v>
+      </c>
+      <c r="B306" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C306" s="7">
+        <v>21</v>
+      </c>
+      <c r="D306" s="9">
+        <v>1</v>
+      </c>
+      <c r="E306" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F306" s="7">
+        <v>5</v>
+      </c>
+      <c r="G306" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7">
+      <c r="A307" s="5">
+        <f t="shared" si="11"/>
+        <v>60380022</v>
+      </c>
+      <c r="B307" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C307" s="7">
+        <v>22</v>
+      </c>
+      <c r="D307" s="9">
+        <v>1</v>
+      </c>
+      <c r="E307" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F307" s="7">
+        <v>5</v>
+      </c>
+      <c r="G307" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7">
+      <c r="A308" s="5">
+        <f t="shared" si="11"/>
+        <v>60380023</v>
+      </c>
+      <c r="B308" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C308" s="7">
+        <v>23</v>
+      </c>
+      <c r="D308" s="9">
+        <v>1</v>
+      </c>
+      <c r="E308" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F308" s="7">
+        <v>5</v>
+      </c>
+      <c r="G308" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7">
+      <c r="A309" s="5">
+        <f t="shared" si="11"/>
+        <v>60380024</v>
+      </c>
+      <c r="B309" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C309" s="7">
+        <v>24</v>
+      </c>
+      <c r="D309" s="9">
+        <v>1</v>
+      </c>
+      <c r="E309" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F309" s="7">
+        <v>5</v>
+      </c>
+      <c r="G309" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7">
+      <c r="A310" s="5">
+        <f t="shared" si="11"/>
+        <v>60380025</v>
+      </c>
+      <c r="B310" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C310" s="7">
+        <v>25</v>
+      </c>
+      <c r="D310" s="9">
+        <v>1</v>
+      </c>
+      <c r="E310" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F310" s="7">
+        <v>5</v>
+      </c>
+      <c r="G310" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7">
+      <c r="A311" s="5">
+        <f t="shared" si="11"/>
+        <v>60380026</v>
+      </c>
+      <c r="B311" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C311" s="7">
+        <v>26</v>
+      </c>
+      <c r="D311" s="9">
+        <v>1</v>
+      </c>
+      <c r="E311" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F311" s="7">
+        <v>5</v>
+      </c>
+      <c r="G311" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7">
+      <c r="A312" s="5">
+        <f t="shared" si="11"/>
+        <v>60380027</v>
+      </c>
+      <c r="B312" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C312" s="7">
+        <v>27</v>
+      </c>
+      <c r="D312" s="9">
+        <v>1</v>
+      </c>
+      <c r="E312" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F312" s="7">
+        <v>5</v>
+      </c>
+      <c r="G312" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7">
+      <c r="A313" s="5">
+        <f t="shared" si="11"/>
+        <v>60380028</v>
+      </c>
+      <c r="B313" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C313" s="7">
+        <v>28</v>
+      </c>
+      <c r="D313" s="9">
+        <v>1</v>
+      </c>
+      <c r="E313" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="F313" s="7">
+        <v>5</v>
+      </c>
+      <c r="G313" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7">
+      <c r="A314" s="5">
+        <f t="shared" si="11"/>
+        <v>60380029</v>
+      </c>
+      <c r="B314" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C314" s="7">
+        <v>29</v>
+      </c>
+      <c r="D314" s="9">
+        <v>1</v>
+      </c>
+      <c r="E314" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F314" s="7">
+        <v>5</v>
+      </c>
+      <c r="G314" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7">
+      <c r="A315" s="5">
+        <f t="shared" si="11"/>
+        <v>60380030</v>
+      </c>
+      <c r="B315" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C315" s="7">
+        <v>30</v>
+      </c>
+      <c r="D315" s="9">
+        <v>1</v>
+      </c>
+      <c r="E315" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="F315" s="7">
+        <v>5</v>
+      </c>
+      <c r="G315" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7">
+      <c r="A316" s="5">
+        <f t="shared" si="11"/>
+        <v>60380031</v>
+      </c>
+      <c r="B316" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C316" s="7">
+        <v>31</v>
+      </c>
+      <c r="D316" s="9">
+        <v>1</v>
+      </c>
+      <c r="E316" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="F316" s="7">
+        <v>5</v>
+      </c>
+      <c r="G316" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7">
+      <c r="A317" s="5">
+        <f t="shared" si="11"/>
+        <v>60380032</v>
+      </c>
+      <c r="B317" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C317" s="7">
+        <v>32</v>
+      </c>
+      <c r="D317" s="9">
+        <v>1</v>
+      </c>
+      <c r="E317" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="F317" s="7">
+        <v>5</v>
+      </c>
+      <c r="G317" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7">
+      <c r="A318" s="5">
+        <f t="shared" si="11"/>
+        <v>60380033</v>
+      </c>
+      <c r="B318" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C318" s="7">
+        <v>33</v>
+      </c>
+      <c r="D318" s="9">
+        <v>1</v>
+      </c>
+      <c r="E318" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="F318" s="7">
+        <v>5</v>
+      </c>
+      <c r="G318" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7">
+      <c r="A319" s="5">
+        <f t="shared" si="11"/>
+        <v>60380034</v>
+      </c>
+      <c r="B319" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C319" s="7">
+        <v>34</v>
+      </c>
+      <c r="D319" s="9">
+        <v>1</v>
+      </c>
+      <c r="E319" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="F319" s="7">
+        <v>5</v>
+      </c>
+      <c r="G319" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7">
+      <c r="A320" s="5">
+        <f t="shared" si="11"/>
+        <v>60380035</v>
+      </c>
+      <c r="B320" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C320" s="7">
+        <v>35</v>
+      </c>
+      <c r="D320" s="9">
+        <v>1</v>
+      </c>
+      <c r="E320" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="F320" s="7">
+        <v>5</v>
+      </c>
+      <c r="G320" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7">
+      <c r="A321" s="5">
+        <f t="shared" si="11"/>
+        <v>60380036</v>
+      </c>
+      <c r="B321" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C321" s="7">
+        <v>36</v>
+      </c>
+      <c r="D321" s="9">
+        <v>1</v>
+      </c>
+      <c r="E321" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="F321" s="7">
+        <v>5</v>
+      </c>
+      <c r="G321" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7">
+      <c r="A322" s="5">
+        <f t="shared" si="11"/>
+        <v>60380037</v>
+      </c>
+      <c r="B322" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C322" s="7">
+        <v>37</v>
+      </c>
+      <c r="D322" s="9">
+        <v>1</v>
+      </c>
+      <c r="E322" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="F322" s="7">
+        <v>5</v>
+      </c>
+      <c r="G322" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7">
+      <c r="A323" s="5">
+        <f t="shared" si="11"/>
+        <v>60380038</v>
+      </c>
+      <c r="B323" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C323" s="7">
+        <v>38</v>
+      </c>
+      <c r="D323" s="9">
+        <v>1</v>
+      </c>
+      <c r="E323" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F323" s="7">
+        <v>5</v>
+      </c>
+      <c r="G323" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7">
+      <c r="A324" s="5">
+        <f t="shared" si="11"/>
+        <v>60380039</v>
+      </c>
+      <c r="B324" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C324" s="7">
+        <v>39</v>
+      </c>
+      <c r="D324" s="9">
+        <v>1</v>
+      </c>
+      <c r="E324" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="F324" s="7">
+        <v>5</v>
+      </c>
+      <c r="G324" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7">
+      <c r="A325" s="5">
+        <f t="shared" si="11"/>
+        <v>60380040</v>
+      </c>
+      <c r="B325" s="6">
+        <v>103800</v>
+      </c>
+      <c r="C325" s="7">
+        <v>40</v>
+      </c>
+      <c r="D325" s="9">
+        <v>1</v>
+      </c>
+      <c r="E325" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="F325" s="7">
+        <v>5</v>
+      </c>
+      <c r="G325" s="9">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -9772,6 +10808,12 @@
   <conditionalFormatting sqref="E251:E260">
     <cfRule type="duplicateValues" dxfId="0" priority="11"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E271:E285">
+    <cfRule type="duplicateValues" dxfId="1" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E286:E325">
+    <cfRule type="duplicateValues" dxfId="1" priority="20"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -9794,30 +10836,30 @@
         <v>1</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>2</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>4</v>
       </c>
       <c r="L20" s="4"/>
       <c r="M20" s="4" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="Q20" s="4" t="s">
         <v>5</v>
@@ -9826,7 +10868,7 @@
         <v>3</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="5:19">
@@ -9844,29 +10886,29 @@
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="7" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L21" s="7"/>
       <c r="M21" s="7" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="Q21" s="7" t="s">
         <v>7</v>
       </c>
       <c r="R21" s="7" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="S21" s="7"/>
     </row>
@@ -9878,30 +10920,30 @@
         <v>10</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>11</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="K22" s="7" t="s">
         <v>13</v>
       </c>
       <c r="L22" s="7"/>
       <c r="M22" s="7" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="Q22" s="7" t="s">
         <v>14</v>
@@ -9941,28 +10983,28 @@
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="7" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
       <c r="M24" s="7" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="O24" s="7"/>
       <c r="P24" s="7" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="Q24" s="7">
         <v>5</v>
       </c>
       <c r="R24" s="7" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="S24" s="7" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="5:19">
@@ -9980,28 +11022,28 @@
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
       <c r="M25" s="8" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="O25" s="7"/>
       <c r="P25" s="7" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="Q25" s="7">
         <v>5</v>
       </c>
       <c r="R25" s="7" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="S25" s="7" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="5:19">
@@ -10069,7 +11111,7 @@
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
       <c r="L28" s="7" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="M28" s="5"/>
       <c r="N28" s="7">
@@ -10077,16 +11119,16 @@
       </c>
       <c r="O28" s="7"/>
       <c r="P28" s="7" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="Q28" s="7">
         <v>5</v>
       </c>
       <c r="R28" s="7" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="S28" s="7" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseLine.xlsx
+++ b/slots/resources/sample/BaseLine.xlsx
@@ -321,7 +321,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="201">
   <si>
     <t>id</t>
   </si>
@@ -1713,14 +1713,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2553,7 +2546,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z325"/>
+  <dimension ref="A1:Z335"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.375"/>
@@ -9817,7 +9810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:19">
+    <row r="289" spans="1:7">
       <c r="A289" s="5">
         <f t="shared" si="11"/>
         <v>60380004</v>
@@ -9841,7 +9834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:19">
+    <row r="290" spans="1:7">
       <c r="A290" s="5">
         <f t="shared" si="11"/>
         <v>60380005</v>
@@ -9864,23 +9857,8 @@
       <c r="G290" s="9">
         <v>0</v>
       </c>
-      <c r="O290" s="9">
-        <v>1</v>
-      </c>
-      <c r="P290" s="9">
-        <v>4</v>
-      </c>
-      <c r="Q290" s="9">
-        <v>7</v>
-      </c>
-      <c r="R290" s="9">
-        <v>10</v>
-      </c>
-      <c r="S290" s="9">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="291" spans="1:19">
+    </row>
+    <row r="291" spans="1:7">
       <c r="A291" s="5">
         <f t="shared" si="11"/>
         <v>60380006</v>
@@ -9903,23 +9881,8 @@
       <c r="G291" s="9">
         <v>0</v>
       </c>
-      <c r="O291" s="9">
-        <v>2</v>
-      </c>
-      <c r="P291" s="9">
-        <v>5</v>
-      </c>
-      <c r="Q291" s="9">
-        <v>8</v>
-      </c>
-      <c r="R291" s="9">
-        <v>11</v>
-      </c>
-      <c r="S291" s="9">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="292" spans="1:19">
+    </row>
+    <row r="292" spans="1:7">
       <c r="A292" s="5">
         <f t="shared" si="11"/>
         <v>60380007</v>
@@ -9942,23 +9905,8 @@
       <c r="G292" s="9">
         <v>0</v>
       </c>
-      <c r="O292" s="9">
-        <v>3</v>
-      </c>
-      <c r="P292" s="9">
-        <v>6</v>
-      </c>
-      <c r="Q292" s="9">
-        <v>9</v>
-      </c>
-      <c r="R292" s="9">
-        <v>12</v>
-      </c>
-      <c r="S292" s="9">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="293" spans="1:19">
+    </row>
+    <row r="293" spans="1:7">
       <c r="A293" s="5">
         <f t="shared" si="11"/>
         <v>60380008</v>
@@ -9982,7 +9930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:19">
+    <row r="294" spans="1:7">
       <c r="A294" s="5">
         <f t="shared" si="11"/>
         <v>60380009</v>
@@ -10006,7 +9954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:19">
+    <row r="295" spans="1:7">
       <c r="A295" s="5">
         <f t="shared" si="11"/>
         <v>60380010</v>
@@ -10030,7 +9978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:19">
+    <row r="296" spans="1:7">
       <c r="A296" s="5">
         <f t="shared" si="11"/>
         <v>60380011</v>
@@ -10054,7 +10002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:19">
+    <row r="297" spans="1:7">
       <c r="A297" s="5">
         <f t="shared" si="11"/>
         <v>60380012</v>
@@ -10078,7 +10026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:19">
+    <row r="298" spans="1:7">
       <c r="A298" s="5">
         <f t="shared" si="11"/>
         <v>60380013</v>
@@ -10102,7 +10050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:19">
+    <row r="299" spans="1:7">
       <c r="A299" s="5">
         <f t="shared" si="11"/>
         <v>60380014</v>
@@ -10126,7 +10074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:19">
+    <row r="300" spans="1:7">
       <c r="A300" s="5">
         <f t="shared" si="11"/>
         <v>60380015</v>
@@ -10150,7 +10098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:19">
+    <row r="301" spans="1:7">
       <c r="A301" s="5">
         <f t="shared" si="11"/>
         <v>60380016</v>
@@ -10174,7 +10122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:19">
+    <row r="302" spans="1:7">
       <c r="A302" s="5">
         <f t="shared" si="11"/>
         <v>60380017</v>
@@ -10198,7 +10146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:19">
+    <row r="303" spans="1:7">
       <c r="A303" s="5">
         <f t="shared" si="11"/>
         <v>60380018</v>
@@ -10222,7 +10170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:19">
+    <row r="304" spans="1:7">
       <c r="A304" s="5">
         <f t="shared" si="11"/>
         <v>60380019</v>
@@ -10750,69 +10698,312 @@
         <v>0</v>
       </c>
     </row>
+    <row r="326" spans="1:7">
+      <c r="A326" s="5">
+        <f t="shared" ref="A326:A335" si="12">(B326+500000)*100+C326+G326*1000</f>
+        <v>60370001</v>
+      </c>
+      <c r="B326" s="6">
+        <v>103700</v>
+      </c>
+      <c r="C326" s="7">
+        <v>1</v>
+      </c>
+      <c r="D326" s="9">
+        <v>1</v>
+      </c>
+      <c r="E326" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="F326" s="7">
+        <v>5</v>
+      </c>
+      <c r="G326" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7">
+      <c r="A327" s="5">
+        <f t="shared" si="12"/>
+        <v>60370102</v>
+      </c>
+      <c r="B327" s="6">
+        <v>103701</v>
+      </c>
+      <c r="C327" s="7">
+        <v>2</v>
+      </c>
+      <c r="D327" s="9">
+        <v>1</v>
+      </c>
+      <c r="E327" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F327" s="7">
+        <v>5</v>
+      </c>
+      <c r="G327" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7">
+      <c r="A328" s="5">
+        <f t="shared" si="12"/>
+        <v>60370203</v>
+      </c>
+      <c r="B328" s="6">
+        <v>103702</v>
+      </c>
+      <c r="C328" s="7">
+        <v>3</v>
+      </c>
+      <c r="D328" s="9">
+        <v>1</v>
+      </c>
+      <c r="E328" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="F328" s="7">
+        <v>5</v>
+      </c>
+      <c r="G328" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7">
+      <c r="A329" s="5">
+        <f t="shared" si="12"/>
+        <v>60370304</v>
+      </c>
+      <c r="B329" s="6">
+        <v>103703</v>
+      </c>
+      <c r="C329" s="7">
+        <v>4</v>
+      </c>
+      <c r="D329" s="9">
+        <v>1</v>
+      </c>
+      <c r="E329" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F329" s="7">
+        <v>5</v>
+      </c>
+      <c r="G329" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7">
+      <c r="A330" s="5">
+        <f t="shared" si="12"/>
+        <v>60370405</v>
+      </c>
+      <c r="B330" s="6">
+        <v>103704</v>
+      </c>
+      <c r="C330" s="7">
+        <v>5</v>
+      </c>
+      <c r="D330" s="9">
+        <v>1</v>
+      </c>
+      <c r="E330" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="F330" s="7">
+        <v>5</v>
+      </c>
+      <c r="G330" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7">
+      <c r="A331" s="5">
+        <f t="shared" si="12"/>
+        <v>60370506</v>
+      </c>
+      <c r="B331" s="6">
+        <v>103705</v>
+      </c>
+      <c r="C331" s="7">
+        <v>6</v>
+      </c>
+      <c r="D331" s="9">
+        <v>1</v>
+      </c>
+      <c r="E331" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="F331" s="7">
+        <v>5</v>
+      </c>
+      <c r="G331" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7">
+      <c r="A332" s="5">
+        <f t="shared" si="12"/>
+        <v>60370607</v>
+      </c>
+      <c r="B332" s="6">
+        <v>103706</v>
+      </c>
+      <c r="C332" s="7">
+        <v>7</v>
+      </c>
+      <c r="D332" s="9">
+        <v>1</v>
+      </c>
+      <c r="E332" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="F332" s="7">
+        <v>5</v>
+      </c>
+      <c r="G332" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:7">
+      <c r="A333" s="5">
+        <f t="shared" si="12"/>
+        <v>60370708</v>
+      </c>
+      <c r="B333" s="6">
+        <v>103707</v>
+      </c>
+      <c r="C333" s="7">
+        <v>8</v>
+      </c>
+      <c r="D333" s="9">
+        <v>1</v>
+      </c>
+      <c r="E333" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="F333" s="7">
+        <v>5</v>
+      </c>
+      <c r="G333" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7">
+      <c r="A334" s="5">
+        <f t="shared" si="12"/>
+        <v>60370809</v>
+      </c>
+      <c r="B334" s="6">
+        <v>103708</v>
+      </c>
+      <c r="C334" s="7">
+        <v>9</v>
+      </c>
+      <c r="D334" s="9">
+        <v>1</v>
+      </c>
+      <c r="E334" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F334" s="7">
+        <v>5</v>
+      </c>
+      <c r="G334" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="1:7">
+      <c r="A335" s="5">
+        <f t="shared" si="12"/>
+        <v>60370910</v>
+      </c>
+      <c r="B335" s="6">
+        <v>103709</v>
+      </c>
+      <c r="C335" s="7">
+        <v>10</v>
+      </c>
+      <c r="D335" s="9">
+        <v>1</v>
+      </c>
+      <c r="E335" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="F335" s="7">
+        <v>5</v>
+      </c>
+      <c r="G335" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="E236">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E237">
     <cfRule type="duplicateValues" dxfId="0" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E237">
+  <conditionalFormatting sqref="E238">
     <cfRule type="duplicateValues" dxfId="0" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E238">
+  <conditionalFormatting sqref="E239">
     <cfRule type="duplicateValues" dxfId="0" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E239">
+  <conditionalFormatting sqref="E240">
     <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E240">
+  <conditionalFormatting sqref="E261">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E262">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E263">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E264">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E265">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E266">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E267">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E268">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E269">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E270">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E161:E185">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E186:E235">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E241:E250">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E251:E260">
     <cfRule type="duplicateValues" dxfId="0" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E261">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E262">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E263">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E264">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E265">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E266">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E267">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E268">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E269">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E270">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E161:E185">
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E186:E235">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E241:E250">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E251:E260">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="E271:E285">
-    <cfRule type="duplicateValues" dxfId="1" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E286:E325">
-    <cfRule type="duplicateValues" dxfId="1" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E326:E335">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/slots/resources/sample/BaseLine.xlsx
+++ b/slots/resources/sample/BaseLine.xlsx
@@ -321,7 +321,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="201">
   <si>
     <t>id</t>
   </si>
@@ -2546,7 +2546,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z335"/>
+  <dimension ref="A1:Z360"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.375"/>
@@ -10725,10 +10725,10 @@
     <row r="327" spans="1:7">
       <c r="A327" s="5">
         <f t="shared" si="12"/>
-        <v>60370102</v>
+        <v>60370002</v>
       </c>
       <c r="B327" s="6">
-        <v>103701</v>
+        <v>103700</v>
       </c>
       <c r="C327" s="7">
         <v>2</v>
@@ -10749,10 +10749,10 @@
     <row r="328" spans="1:7">
       <c r="A328" s="5">
         <f t="shared" si="12"/>
-        <v>60370203</v>
+        <v>60370003</v>
       </c>
       <c r="B328" s="6">
-        <v>103702</v>
+        <v>103700</v>
       </c>
       <c r="C328" s="7">
         <v>3</v>
@@ -10773,10 +10773,10 @@
     <row r="329" spans="1:7">
       <c r="A329" s="5">
         <f t="shared" si="12"/>
-        <v>60370304</v>
+        <v>60370004</v>
       </c>
       <c r="B329" s="6">
-        <v>103703</v>
+        <v>103700</v>
       </c>
       <c r="C329" s="7">
         <v>4</v>
@@ -10797,10 +10797,10 @@
     <row r="330" spans="1:7">
       <c r="A330" s="5">
         <f t="shared" si="12"/>
-        <v>60370405</v>
+        <v>60370005</v>
       </c>
       <c r="B330" s="6">
-        <v>103704</v>
+        <v>103700</v>
       </c>
       <c r="C330" s="7">
         <v>5</v>
@@ -10821,10 +10821,10 @@
     <row r="331" spans="1:7">
       <c r="A331" s="5">
         <f t="shared" si="12"/>
-        <v>60370506</v>
+        <v>60370006</v>
       </c>
       <c r="B331" s="6">
-        <v>103705</v>
+        <v>103700</v>
       </c>
       <c r="C331" s="7">
         <v>6</v>
@@ -10845,10 +10845,10 @@
     <row r="332" spans="1:7">
       <c r="A332" s="5">
         <f t="shared" si="12"/>
-        <v>60370607</v>
+        <v>60370007</v>
       </c>
       <c r="B332" s="6">
-        <v>103706</v>
+        <v>103700</v>
       </c>
       <c r="C332" s="7">
         <v>7</v>
@@ -10869,10 +10869,10 @@
     <row r="333" spans="1:7">
       <c r="A333" s="5">
         <f t="shared" si="12"/>
-        <v>60370708</v>
+        <v>60370008</v>
       </c>
       <c r="B333" s="6">
-        <v>103707</v>
+        <v>103700</v>
       </c>
       <c r="C333" s="7">
         <v>8</v>
@@ -10893,10 +10893,10 @@
     <row r="334" spans="1:7">
       <c r="A334" s="5">
         <f t="shared" si="12"/>
-        <v>60370809</v>
+        <v>60370009</v>
       </c>
       <c r="B334" s="6">
-        <v>103708</v>
+        <v>103700</v>
       </c>
       <c r="C334" s="7">
         <v>9</v>
@@ -10917,10 +10917,10 @@
     <row r="335" spans="1:7">
       <c r="A335" s="5">
         <f t="shared" si="12"/>
-        <v>60370910</v>
+        <v>60370010</v>
       </c>
       <c r="B335" s="6">
-        <v>103709</v>
+        <v>103700</v>
       </c>
       <c r="C335" s="7">
         <v>10</v>
@@ -10935,6 +10935,606 @@
         <v>5</v>
       </c>
       <c r="G335" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7">
+      <c r="A336" s="5">
+        <f t="shared" ref="A336:A360" si="13">(B336+500000)*100+C336+G336*1000</f>
+        <v>60310001</v>
+      </c>
+      <c r="B336" s="6">
+        <v>103100</v>
+      </c>
+      <c r="C336" s="7">
+        <v>1</v>
+      </c>
+      <c r="D336" s="9">
+        <v>1</v>
+      </c>
+      <c r="E336" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="F336" s="7">
+        <v>5</v>
+      </c>
+      <c r="G336" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7">
+      <c r="A337" s="5">
+        <f t="shared" si="13"/>
+        <v>60310002</v>
+      </c>
+      <c r="B337" s="6">
+        <v>103100</v>
+      </c>
+      <c r="C337" s="7">
+        <v>2</v>
+      </c>
+      <c r="D337" s="9">
+        <v>1</v>
+      </c>
+      <c r="E337" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F337" s="7">
+        <v>5</v>
+      </c>
+      <c r="G337" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:7">
+      <c r="A338" s="5">
+        <f t="shared" si="13"/>
+        <v>60310003</v>
+      </c>
+      <c r="B338" s="6">
+        <v>103100</v>
+      </c>
+      <c r="C338" s="7">
+        <v>3</v>
+      </c>
+      <c r="D338" s="9">
+        <v>1</v>
+      </c>
+      <c r="E338" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F338" s="7">
+        <v>5</v>
+      </c>
+      <c r="G338" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7">
+      <c r="A339" s="5">
+        <f t="shared" si="13"/>
+        <v>60310004</v>
+      </c>
+      <c r="B339" s="6">
+        <v>103100</v>
+      </c>
+      <c r="C339" s="7">
+        <v>4</v>
+      </c>
+      <c r="D339" s="9">
+        <v>1</v>
+      </c>
+      <c r="E339" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F339" s="7">
+        <v>5</v>
+      </c>
+      <c r="G339" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7">
+      <c r="A340" s="5">
+        <f t="shared" si="13"/>
+        <v>60310005</v>
+      </c>
+      <c r="B340" s="6">
+        <v>103100</v>
+      </c>
+      <c r="C340" s="7">
+        <v>5</v>
+      </c>
+      <c r="D340" s="9">
+        <v>1</v>
+      </c>
+      <c r="E340" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F340" s="7">
+        <v>5</v>
+      </c>
+      <c r="G340" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7">
+      <c r="A341" s="5">
+        <f t="shared" si="13"/>
+        <v>60310006</v>
+      </c>
+      <c r="B341" s="6">
+        <v>103100</v>
+      </c>
+      <c r="C341" s="7">
+        <v>6</v>
+      </c>
+      <c r="D341" s="9">
+        <v>1</v>
+      </c>
+      <c r="E341" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F341" s="7">
+        <v>5</v>
+      </c>
+      <c r="G341" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7">
+      <c r="A342" s="5">
+        <f t="shared" si="13"/>
+        <v>60310007</v>
+      </c>
+      <c r="B342" s="6">
+        <v>103100</v>
+      </c>
+      <c r="C342" s="7">
+        <v>7</v>
+      </c>
+      <c r="D342" s="9">
+        <v>1</v>
+      </c>
+      <c r="E342" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F342" s="7">
+        <v>5</v>
+      </c>
+      <c r="G342" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7">
+      <c r="A343" s="5">
+        <f t="shared" si="13"/>
+        <v>60310008</v>
+      </c>
+      <c r="B343" s="6">
+        <v>103100</v>
+      </c>
+      <c r="C343" s="7">
+        <v>8</v>
+      </c>
+      <c r="D343" s="9">
+        <v>1</v>
+      </c>
+      <c r="E343" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F343" s="7">
+        <v>5</v>
+      </c>
+      <c r="G343" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="1:7">
+      <c r="A344" s="5">
+        <f t="shared" si="13"/>
+        <v>60310009</v>
+      </c>
+      <c r="B344" s="6">
+        <v>103100</v>
+      </c>
+      <c r="C344" s="7">
+        <v>9</v>
+      </c>
+      <c r="D344" s="9">
+        <v>1</v>
+      </c>
+      <c r="E344" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F344" s="7">
+        <v>5</v>
+      </c>
+      <c r="G344" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="1:7">
+      <c r="A345" s="5">
+        <f t="shared" si="13"/>
+        <v>60310010</v>
+      </c>
+      <c r="B345" s="6">
+        <v>103100</v>
+      </c>
+      <c r="C345" s="7">
+        <v>10</v>
+      </c>
+      <c r="D345" s="9">
+        <v>1</v>
+      </c>
+      <c r="E345" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F345" s="7">
+        <v>5</v>
+      </c>
+      <c r="G345" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7">
+      <c r="A346" s="5">
+        <f t="shared" si="13"/>
+        <v>60310011</v>
+      </c>
+      <c r="B346" s="6">
+        <v>103100</v>
+      </c>
+      <c r="C346" s="7">
+        <v>11</v>
+      </c>
+      <c r="D346" s="9">
+        <v>1</v>
+      </c>
+      <c r="E346" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F346" s="7">
+        <v>5</v>
+      </c>
+      <c r="G346" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="1:7">
+      <c r="A347" s="5">
+        <f t="shared" si="13"/>
+        <v>60310012</v>
+      </c>
+      <c r="B347" s="6">
+        <v>103100</v>
+      </c>
+      <c r="C347" s="7">
+        <v>12</v>
+      </c>
+      <c r="D347" s="9">
+        <v>1</v>
+      </c>
+      <c r="E347" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F347" s="7">
+        <v>5</v>
+      </c>
+      <c r="G347" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:7">
+      <c r="A348" s="5">
+        <f t="shared" si="13"/>
+        <v>60310013</v>
+      </c>
+      <c r="B348" s="6">
+        <v>103100</v>
+      </c>
+      <c r="C348" s="7">
+        <v>13</v>
+      </c>
+      <c r="D348" s="9">
+        <v>1</v>
+      </c>
+      <c r="E348" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F348" s="7">
+        <v>5</v>
+      </c>
+      <c r="G348" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7">
+      <c r="A349" s="5">
+        <f t="shared" si="13"/>
+        <v>60310014</v>
+      </c>
+      <c r="B349" s="6">
+        <v>103100</v>
+      </c>
+      <c r="C349" s="7">
+        <v>14</v>
+      </c>
+      <c r="D349" s="9">
+        <v>1</v>
+      </c>
+      <c r="E349" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F349" s="7">
+        <v>5</v>
+      </c>
+      <c r="G349" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:7">
+      <c r="A350" s="5">
+        <f t="shared" si="13"/>
+        <v>60310015</v>
+      </c>
+      <c r="B350" s="6">
+        <v>103100</v>
+      </c>
+      <c r="C350" s="7">
+        <v>15</v>
+      </c>
+      <c r="D350" s="9">
+        <v>1</v>
+      </c>
+      <c r="E350" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="F350" s="7">
+        <v>5</v>
+      </c>
+      <c r="G350" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="1:7">
+      <c r="A351" s="5">
+        <f t="shared" si="13"/>
+        <v>60310016</v>
+      </c>
+      <c r="B351" s="6">
+        <v>103100</v>
+      </c>
+      <c r="C351" s="7">
+        <v>16</v>
+      </c>
+      <c r="D351" s="9">
+        <v>1</v>
+      </c>
+      <c r="E351" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F351" s="7">
+        <v>5</v>
+      </c>
+      <c r="G351" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:7">
+      <c r="A352" s="5">
+        <f t="shared" si="13"/>
+        <v>60310017</v>
+      </c>
+      <c r="B352" s="6">
+        <v>103100</v>
+      </c>
+      <c r="C352" s="7">
+        <v>17</v>
+      </c>
+      <c r="D352" s="9">
+        <v>1</v>
+      </c>
+      <c r="E352" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F352" s="7">
+        <v>5</v>
+      </c>
+      <c r="G352" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7">
+      <c r="A353" s="5">
+        <f t="shared" si="13"/>
+        <v>60310018</v>
+      </c>
+      <c r="B353" s="6">
+        <v>103100</v>
+      </c>
+      <c r="C353" s="7">
+        <v>18</v>
+      </c>
+      <c r="D353" s="9">
+        <v>1</v>
+      </c>
+      <c r="E353" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F353" s="7">
+        <v>5</v>
+      </c>
+      <c r="G353" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7">
+      <c r="A354" s="5">
+        <f t="shared" si="13"/>
+        <v>60310019</v>
+      </c>
+      <c r="B354" s="6">
+        <v>103100</v>
+      </c>
+      <c r="C354" s="7">
+        <v>19</v>
+      </c>
+      <c r="D354" s="9">
+        <v>1</v>
+      </c>
+      <c r="E354" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F354" s="7">
+        <v>5</v>
+      </c>
+      <c r="G354" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="1:7">
+      <c r="A355" s="5">
+        <f t="shared" si="13"/>
+        <v>60310020</v>
+      </c>
+      <c r="B355" s="6">
+        <v>103100</v>
+      </c>
+      <c r="C355" s="7">
+        <v>20</v>
+      </c>
+      <c r="D355" s="9">
+        <v>1</v>
+      </c>
+      <c r="E355" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F355" s="7">
+        <v>5</v>
+      </c>
+      <c r="G355" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7">
+      <c r="A356" s="5">
+        <f t="shared" si="13"/>
+        <v>60310021</v>
+      </c>
+      <c r="B356" s="6">
+        <v>103100</v>
+      </c>
+      <c r="C356" s="7">
+        <v>21</v>
+      </c>
+      <c r="D356" s="9">
+        <v>1</v>
+      </c>
+      <c r="E356" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F356" s="7">
+        <v>5</v>
+      </c>
+      <c r="G356" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7">
+      <c r="A357" s="5">
+        <f t="shared" si="13"/>
+        <v>60310022</v>
+      </c>
+      <c r="B357" s="6">
+        <v>103100</v>
+      </c>
+      <c r="C357" s="7">
+        <v>22</v>
+      </c>
+      <c r="D357" s="9">
+        <v>1</v>
+      </c>
+      <c r="E357" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F357" s="7">
+        <v>5</v>
+      </c>
+      <c r="G357" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="1:7">
+      <c r="A358" s="5">
+        <f t="shared" si="13"/>
+        <v>60310023</v>
+      </c>
+      <c r="B358" s="6">
+        <v>103100</v>
+      </c>
+      <c r="C358" s="7">
+        <v>23</v>
+      </c>
+      <c r="D358" s="9">
+        <v>1</v>
+      </c>
+      <c r="E358" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F358" s="7">
+        <v>5</v>
+      </c>
+      <c r="G358" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7">
+      <c r="A359" s="5">
+        <f t="shared" si="13"/>
+        <v>60310024</v>
+      </c>
+      <c r="B359" s="6">
+        <v>103100</v>
+      </c>
+      <c r="C359" s="7">
+        <v>24</v>
+      </c>
+      <c r="D359" s="9">
+        <v>1</v>
+      </c>
+      <c r="E359" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F359" s="7">
+        <v>5</v>
+      </c>
+      <c r="G359" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7">
+      <c r="A360" s="5">
+        <f t="shared" si="13"/>
+        <v>60310025</v>
+      </c>
+      <c r="B360" s="6">
+        <v>103100</v>
+      </c>
+      <c r="C360" s="7">
+        <v>25</v>
+      </c>
+      <c r="D360" s="9">
+        <v>1</v>
+      </c>
+      <c r="E360" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F360" s="7">
+        <v>5</v>
+      </c>
+      <c r="G360" s="9">
         <v>0</v>
       </c>
     </row>

--- a/slots/resources/sample/BaseLine.xlsx
+++ b/slots/resources/sample/BaseLine.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseLine" sheetId="1" r:id="rId1"/>
@@ -321,7 +321,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="204">
   <si>
     <t>id</t>
   </si>
@@ -834,6 +834,15 @@
   </si>
   <si>
     <t>2_6_9_11_13</t>
+  </si>
+  <si>
+    <t>3_5_9_10_13</t>
+  </si>
+  <si>
+    <t>3_4_7_11_15</t>
+  </si>
+  <si>
+    <t>3_6_7_11_13</t>
   </si>
   <si>
     <t>线路类型</t>
@@ -2546,7 +2555,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z360"/>
+  <dimension ref="A1:Z425"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.375"/>
@@ -11538,71 +11547,1637 @@
         <v>0</v>
       </c>
     </row>
+    <row r="361" spans="1:7">
+      <c r="A361" s="5">
+        <f t="shared" ref="A361:A400" si="14">(B361+500000)*100+C361+G361*1000</f>
+        <v>60400001</v>
+      </c>
+      <c r="B361" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C361" s="7">
+        <v>1</v>
+      </c>
+      <c r="D361" s="9">
+        <v>1</v>
+      </c>
+      <c r="E361" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F361" s="7">
+        <v>5</v>
+      </c>
+      <c r="G361" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7">
+      <c r="A362" s="5">
+        <f t="shared" si="14"/>
+        <v>60400002</v>
+      </c>
+      <c r="B362" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C362" s="7">
+        <v>2</v>
+      </c>
+      <c r="D362" s="9">
+        <v>1</v>
+      </c>
+      <c r="E362" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F362" s="7">
+        <v>5</v>
+      </c>
+      <c r="G362" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7">
+      <c r="A363" s="5">
+        <f t="shared" si="14"/>
+        <v>60400003</v>
+      </c>
+      <c r="B363" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C363" s="7">
+        <v>3</v>
+      </c>
+      <c r="D363" s="9">
+        <v>1</v>
+      </c>
+      <c r="E363" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F363" s="7">
+        <v>5</v>
+      </c>
+      <c r="G363" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7">
+      <c r="A364" s="5">
+        <f t="shared" si="14"/>
+        <v>60400004</v>
+      </c>
+      <c r="B364" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C364" s="7">
+        <v>4</v>
+      </c>
+      <c r="D364" s="9">
+        <v>1</v>
+      </c>
+      <c r="E364" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F364" s="7">
+        <v>5</v>
+      </c>
+      <c r="G364" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7">
+      <c r="A365" s="5">
+        <f t="shared" si="14"/>
+        <v>60400005</v>
+      </c>
+      <c r="B365" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C365" s="7">
+        <v>5</v>
+      </c>
+      <c r="D365" s="9">
+        <v>1</v>
+      </c>
+      <c r="E365" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F365" s="7">
+        <v>5</v>
+      </c>
+      <c r="G365" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7">
+      <c r="A366" s="5">
+        <f t="shared" si="14"/>
+        <v>60400006</v>
+      </c>
+      <c r="B366" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C366" s="7">
+        <v>6</v>
+      </c>
+      <c r="D366" s="9">
+        <v>1</v>
+      </c>
+      <c r="E366" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F366" s="7">
+        <v>5</v>
+      </c>
+      <c r="G366" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7">
+      <c r="A367" s="5">
+        <f t="shared" si="14"/>
+        <v>60400007</v>
+      </c>
+      <c r="B367" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C367" s="7">
+        <v>7</v>
+      </c>
+      <c r="D367" s="9">
+        <v>1</v>
+      </c>
+      <c r="E367" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F367" s="7">
+        <v>5</v>
+      </c>
+      <c r="G367" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7">
+      <c r="A368" s="5">
+        <f t="shared" si="14"/>
+        <v>60400008</v>
+      </c>
+      <c r="B368" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C368" s="7">
+        <v>8</v>
+      </c>
+      <c r="D368" s="9">
+        <v>1</v>
+      </c>
+      <c r="E368" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F368" s="7">
+        <v>5</v>
+      </c>
+      <c r="G368" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7">
+      <c r="A369" s="5">
+        <f t="shared" si="14"/>
+        <v>60400009</v>
+      </c>
+      <c r="B369" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C369" s="7">
+        <v>9</v>
+      </c>
+      <c r="D369" s="9">
+        <v>1</v>
+      </c>
+      <c r="E369" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F369" s="7">
+        <v>5</v>
+      </c>
+      <c r="G369" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7">
+      <c r="A370" s="5">
+        <f t="shared" si="14"/>
+        <v>60400010</v>
+      </c>
+      <c r="B370" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C370" s="7">
+        <v>10</v>
+      </c>
+      <c r="D370" s="9">
+        <v>1</v>
+      </c>
+      <c r="E370" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F370" s="7">
+        <v>5</v>
+      </c>
+      <c r="G370" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7">
+      <c r="A371" s="5">
+        <f t="shared" si="14"/>
+        <v>60400011</v>
+      </c>
+      <c r="B371" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C371" s="7">
+        <v>11</v>
+      </c>
+      <c r="D371" s="9">
+        <v>1</v>
+      </c>
+      <c r="E371" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F371" s="7">
+        <v>5</v>
+      </c>
+      <c r="G371" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7">
+      <c r="A372" s="5">
+        <f t="shared" si="14"/>
+        <v>60400012</v>
+      </c>
+      <c r="B372" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C372" s="7">
+        <v>12</v>
+      </c>
+      <c r="D372" s="9">
+        <v>1</v>
+      </c>
+      <c r="E372" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F372" s="7">
+        <v>5</v>
+      </c>
+      <c r="G372" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7">
+      <c r="A373" s="5">
+        <f t="shared" si="14"/>
+        <v>60400013</v>
+      </c>
+      <c r="B373" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C373" s="7">
+        <v>13</v>
+      </c>
+      <c r="D373" s="9">
+        <v>1</v>
+      </c>
+      <c r="E373" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F373" s="7">
+        <v>5</v>
+      </c>
+      <c r="G373" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:7">
+      <c r="A374" s="5">
+        <f t="shared" si="14"/>
+        <v>60400014</v>
+      </c>
+      <c r="B374" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C374" s="7">
+        <v>14</v>
+      </c>
+      <c r="D374" s="9">
+        <v>1</v>
+      </c>
+      <c r="E374" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F374" s="7">
+        <v>5</v>
+      </c>
+      <c r="G374" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:7">
+      <c r="A375" s="5">
+        <f t="shared" si="14"/>
+        <v>60400015</v>
+      </c>
+      <c r="B375" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C375" s="7">
+        <v>15</v>
+      </c>
+      <c r="D375" s="9">
+        <v>1</v>
+      </c>
+      <c r="E375" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="F375" s="7">
+        <v>5</v>
+      </c>
+      <c r="G375" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:7">
+      <c r="A376" s="5">
+        <f t="shared" si="14"/>
+        <v>60400016</v>
+      </c>
+      <c r="B376" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C376" s="7">
+        <v>16</v>
+      </c>
+      <c r="D376" s="9">
+        <v>1</v>
+      </c>
+      <c r="E376" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F376" s="7">
+        <v>5</v>
+      </c>
+      <c r="G376" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:7">
+      <c r="A377" s="5">
+        <f t="shared" si="14"/>
+        <v>60400017</v>
+      </c>
+      <c r="B377" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C377" s="7">
+        <v>17</v>
+      </c>
+      <c r="D377" s="9">
+        <v>1</v>
+      </c>
+      <c r="E377" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F377" s="7">
+        <v>5</v>
+      </c>
+      <c r="G377" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:7">
+      <c r="A378" s="5">
+        <f t="shared" si="14"/>
+        <v>60400018</v>
+      </c>
+      <c r="B378" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C378" s="7">
+        <v>18</v>
+      </c>
+      <c r="D378" s="9">
+        <v>1</v>
+      </c>
+      <c r="E378" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F378" s="7">
+        <v>5</v>
+      </c>
+      <c r="G378" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7">
+      <c r="A379" s="5">
+        <f t="shared" si="14"/>
+        <v>60400019</v>
+      </c>
+      <c r="B379" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C379" s="7">
+        <v>19</v>
+      </c>
+      <c r="D379" s="9">
+        <v>1</v>
+      </c>
+      <c r="E379" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F379" s="7">
+        <v>5</v>
+      </c>
+      <c r="G379" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7">
+      <c r="A380" s="5">
+        <f t="shared" si="14"/>
+        <v>60400020</v>
+      </c>
+      <c r="B380" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C380" s="7">
+        <v>20</v>
+      </c>
+      <c r="D380" s="9">
+        <v>1</v>
+      </c>
+      <c r="E380" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F380" s="7">
+        <v>5</v>
+      </c>
+      <c r="G380" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:7">
+      <c r="A381" s="5">
+        <f t="shared" si="14"/>
+        <v>60400021</v>
+      </c>
+      <c r="B381" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C381" s="7">
+        <v>21</v>
+      </c>
+      <c r="D381" s="9">
+        <v>1</v>
+      </c>
+      <c r="E381" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F381" s="7">
+        <v>5</v>
+      </c>
+      <c r="G381" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:7">
+      <c r="A382" s="5">
+        <f t="shared" si="14"/>
+        <v>60400022</v>
+      </c>
+      <c r="B382" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C382" s="7">
+        <v>22</v>
+      </c>
+      <c r="D382" s="9">
+        <v>1</v>
+      </c>
+      <c r="E382" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F382" s="7">
+        <v>5</v>
+      </c>
+      <c r="G382" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7">
+      <c r="A383" s="5">
+        <f t="shared" si="14"/>
+        <v>60400023</v>
+      </c>
+      <c r="B383" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C383" s="7">
+        <v>23</v>
+      </c>
+      <c r="D383" s="9">
+        <v>1</v>
+      </c>
+      <c r="E383" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F383" s="7">
+        <v>5</v>
+      </c>
+      <c r="G383" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:7">
+      <c r="A384" s="5">
+        <f t="shared" si="14"/>
+        <v>60400024</v>
+      </c>
+      <c r="B384" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C384" s="7">
+        <v>24</v>
+      </c>
+      <c r="D384" s="9">
+        <v>1</v>
+      </c>
+      <c r="E384" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F384" s="7">
+        <v>5</v>
+      </c>
+      <c r="G384" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:7">
+      <c r="A385" s="5">
+        <f t="shared" si="14"/>
+        <v>60400025</v>
+      </c>
+      <c r="B385" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C385" s="7">
+        <v>25</v>
+      </c>
+      <c r="D385" s="9">
+        <v>1</v>
+      </c>
+      <c r="E385" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F385" s="7">
+        <v>5</v>
+      </c>
+      <c r="G385" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:7">
+      <c r="A386" s="5">
+        <f t="shared" si="14"/>
+        <v>60400026</v>
+      </c>
+      <c r="B386" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C386" s="7">
+        <v>26</v>
+      </c>
+      <c r="D386" s="9">
+        <v>1</v>
+      </c>
+      <c r="E386" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="F386" s="7">
+        <v>5</v>
+      </c>
+      <c r="G386" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:7">
+      <c r="A387" s="5">
+        <f t="shared" si="14"/>
+        <v>60400027</v>
+      </c>
+      <c r="B387" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C387" s="7">
+        <v>27</v>
+      </c>
+      <c r="D387" s="9">
+        <v>1</v>
+      </c>
+      <c r="E387" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="F387" s="7">
+        <v>5</v>
+      </c>
+      <c r="G387" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:7">
+      <c r="A388" s="5">
+        <f t="shared" si="14"/>
+        <v>60400028</v>
+      </c>
+      <c r="B388" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C388" s="7">
+        <v>28</v>
+      </c>
+      <c r="D388" s="9">
+        <v>1</v>
+      </c>
+      <c r="E388" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="F388" s="7">
+        <v>5</v>
+      </c>
+      <c r="G388" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:7">
+      <c r="A389" s="5">
+        <f t="shared" si="14"/>
+        <v>60400029</v>
+      </c>
+      <c r="B389" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C389" s="7">
+        <v>29</v>
+      </c>
+      <c r="D389" s="9">
+        <v>1</v>
+      </c>
+      <c r="E389" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F389" s="7">
+        <v>5</v>
+      </c>
+      <c r="G389" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:7">
+      <c r="A390" s="5">
+        <f t="shared" si="14"/>
+        <v>60400030</v>
+      </c>
+      <c r="B390" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C390" s="7">
+        <v>30</v>
+      </c>
+      <c r="D390" s="9">
+        <v>1</v>
+      </c>
+      <c r="E390" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="F390" s="7">
+        <v>5</v>
+      </c>
+      <c r="G390" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:7">
+      <c r="A391" s="5">
+        <f t="shared" si="14"/>
+        <v>60400031</v>
+      </c>
+      <c r="B391" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C391" s="7">
+        <v>31</v>
+      </c>
+      <c r="D391" s="9">
+        <v>1</v>
+      </c>
+      <c r="E391" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="F391" s="7">
+        <v>5</v>
+      </c>
+      <c r="G391" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:7">
+      <c r="A392" s="5">
+        <f t="shared" si="14"/>
+        <v>60400032</v>
+      </c>
+      <c r="B392" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C392" s="7">
+        <v>32</v>
+      </c>
+      <c r="D392" s="9">
+        <v>1</v>
+      </c>
+      <c r="E392" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="F392" s="7">
+        <v>5</v>
+      </c>
+      <c r="G392" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:7">
+      <c r="A393" s="5">
+        <f t="shared" si="14"/>
+        <v>60400033</v>
+      </c>
+      <c r="B393" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C393" s="7">
+        <v>33</v>
+      </c>
+      <c r="D393" s="9">
+        <v>1</v>
+      </c>
+      <c r="E393" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F393" s="7">
+        <v>5</v>
+      </c>
+      <c r="G393" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="1:7">
+      <c r="A394" s="5">
+        <f t="shared" si="14"/>
+        <v>60400034</v>
+      </c>
+      <c r="B394" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C394" s="7">
+        <v>34</v>
+      </c>
+      <c r="D394" s="9">
+        <v>1</v>
+      </c>
+      <c r="E394" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="F394" s="7">
+        <v>5</v>
+      </c>
+      <c r="G394" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="1:7">
+      <c r="A395" s="5">
+        <f t="shared" si="14"/>
+        <v>60400035</v>
+      </c>
+      <c r="B395" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C395" s="7">
+        <v>35</v>
+      </c>
+      <c r="D395" s="9">
+        <v>1</v>
+      </c>
+      <c r="E395" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="F395" s="7">
+        <v>5</v>
+      </c>
+      <c r="G395" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="1:7">
+      <c r="A396" s="5">
+        <f t="shared" si="14"/>
+        <v>60400036</v>
+      </c>
+      <c r="B396" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C396" s="7">
+        <v>36</v>
+      </c>
+      <c r="D396" s="9">
+        <v>1</v>
+      </c>
+      <c r="E396" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="F396" s="7">
+        <v>5</v>
+      </c>
+      <c r="G396" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:7">
+      <c r="A397" s="5">
+        <f t="shared" si="14"/>
+        <v>60400037</v>
+      </c>
+      <c r="B397" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C397" s="7">
+        <v>37</v>
+      </c>
+      <c r="D397" s="9">
+        <v>1</v>
+      </c>
+      <c r="E397" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="F397" s="7">
+        <v>5</v>
+      </c>
+      <c r="G397" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:7">
+      <c r="A398" s="5">
+        <f t="shared" si="14"/>
+        <v>60400038</v>
+      </c>
+      <c r="B398" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C398" s="7">
+        <v>38</v>
+      </c>
+      <c r="D398" s="9">
+        <v>1</v>
+      </c>
+      <c r="E398" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F398" s="7">
+        <v>5</v>
+      </c>
+      <c r="G398" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:7">
+      <c r="A399" s="5">
+        <f t="shared" si="14"/>
+        <v>60400039</v>
+      </c>
+      <c r="B399" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C399" s="7">
+        <v>39</v>
+      </c>
+      <c r="D399" s="9">
+        <v>1</v>
+      </c>
+      <c r="E399" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F399" s="7">
+        <v>5</v>
+      </c>
+      <c r="G399" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:7">
+      <c r="A400" s="5">
+        <f t="shared" si="14"/>
+        <v>60400040</v>
+      </c>
+      <c r="B400" s="6">
+        <v>104000</v>
+      </c>
+      <c r="C400" s="7">
+        <v>40</v>
+      </c>
+      <c r="D400" s="9">
+        <v>1</v>
+      </c>
+      <c r="E400" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="F400" s="7">
+        <v>5</v>
+      </c>
+      <c r="G400" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:7">
+      <c r="A401" s="5">
+        <f t="shared" ref="A401:A425" si="15">(B401+500000)*100+C401+G401*1000</f>
+        <v>60390001</v>
+      </c>
+      <c r="B401" s="6">
+        <v>103900</v>
+      </c>
+      <c r="C401" s="7">
+        <v>1</v>
+      </c>
+      <c r="D401" s="9">
+        <v>1</v>
+      </c>
+      <c r="E401" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F401" s="7">
+        <v>5</v>
+      </c>
+      <c r="G401" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="1:7">
+      <c r="A402" s="5">
+        <f t="shared" si="15"/>
+        <v>60390002</v>
+      </c>
+      <c r="B402" s="6">
+        <v>103900</v>
+      </c>
+      <c r="C402" s="7">
+        <v>2</v>
+      </c>
+      <c r="D402" s="9">
+        <v>1</v>
+      </c>
+      <c r="E402" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F402" s="7">
+        <v>5</v>
+      </c>
+      <c r="G402" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:7">
+      <c r="A403" s="5">
+        <f t="shared" si="15"/>
+        <v>60390003</v>
+      </c>
+      <c r="B403" s="6">
+        <v>103900</v>
+      </c>
+      <c r="C403" s="7">
+        <v>3</v>
+      </c>
+      <c r="D403" s="9">
+        <v>1</v>
+      </c>
+      <c r="E403" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F403" s="7">
+        <v>5</v>
+      </c>
+      <c r="G403" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:7">
+      <c r="A404" s="5">
+        <f t="shared" si="15"/>
+        <v>60390004</v>
+      </c>
+      <c r="B404" s="6">
+        <v>103900</v>
+      </c>
+      <c r="C404" s="7">
+        <v>4</v>
+      </c>
+      <c r="D404" s="9">
+        <v>1</v>
+      </c>
+      <c r="E404" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F404" s="7">
+        <v>5</v>
+      </c>
+      <c r="G404" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:7">
+      <c r="A405" s="5">
+        <f t="shared" si="15"/>
+        <v>60390005</v>
+      </c>
+      <c r="B405" s="6">
+        <v>103900</v>
+      </c>
+      <c r="C405" s="7">
+        <v>5</v>
+      </c>
+      <c r="D405" s="9">
+        <v>1</v>
+      </c>
+      <c r="E405" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F405" s="7">
+        <v>5</v>
+      </c>
+      <c r="G405" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="1:7">
+      <c r="A406" s="5">
+        <f t="shared" si="15"/>
+        <v>60390006</v>
+      </c>
+      <c r="B406" s="6">
+        <v>103900</v>
+      </c>
+      <c r="C406" s="7">
+        <v>6</v>
+      </c>
+      <c r="D406" s="9">
+        <v>1</v>
+      </c>
+      <c r="E406" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F406" s="7">
+        <v>5</v>
+      </c>
+      <c r="G406" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="1:7">
+      <c r="A407" s="5">
+        <f t="shared" si="15"/>
+        <v>60390007</v>
+      </c>
+      <c r="B407" s="6">
+        <v>103900</v>
+      </c>
+      <c r="C407" s="7">
+        <v>7</v>
+      </c>
+      <c r="D407" s="9">
+        <v>1</v>
+      </c>
+      <c r="E407" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F407" s="7">
+        <v>5</v>
+      </c>
+      <c r="G407" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="1:7">
+      <c r="A408" s="5">
+        <f t="shared" si="15"/>
+        <v>60390008</v>
+      </c>
+      <c r="B408" s="6">
+        <v>103900</v>
+      </c>
+      <c r="C408" s="7">
+        <v>8</v>
+      </c>
+      <c r="D408" s="9">
+        <v>1</v>
+      </c>
+      <c r="E408" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F408" s="7">
+        <v>5</v>
+      </c>
+      <c r="G408" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="1:7">
+      <c r="A409" s="5">
+        <f t="shared" si="15"/>
+        <v>60390009</v>
+      </c>
+      <c r="B409" s="6">
+        <v>103900</v>
+      </c>
+      <c r="C409" s="7">
+        <v>9</v>
+      </c>
+      <c r="D409" s="9">
+        <v>1</v>
+      </c>
+      <c r="E409" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F409" s="7">
+        <v>5</v>
+      </c>
+      <c r="G409" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" spans="1:7">
+      <c r="A410" s="5">
+        <f t="shared" si="15"/>
+        <v>60390010</v>
+      </c>
+      <c r="B410" s="6">
+        <v>103900</v>
+      </c>
+      <c r="C410" s="7">
+        <v>10</v>
+      </c>
+      <c r="D410" s="9">
+        <v>1</v>
+      </c>
+      <c r="E410" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F410" s="7">
+        <v>5</v>
+      </c>
+      <c r="G410" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:7">
+      <c r="A411" s="5">
+        <f t="shared" si="15"/>
+        <v>60390011</v>
+      </c>
+      <c r="B411" s="6">
+        <v>103900</v>
+      </c>
+      <c r="C411" s="7">
+        <v>11</v>
+      </c>
+      <c r="D411" s="9">
+        <v>1</v>
+      </c>
+      <c r="E411" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F411" s="7">
+        <v>5</v>
+      </c>
+      <c r="G411" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="1:7">
+      <c r="A412" s="5">
+        <f t="shared" si="15"/>
+        <v>60390012</v>
+      </c>
+      <c r="B412" s="6">
+        <v>103900</v>
+      </c>
+      <c r="C412" s="7">
+        <v>12</v>
+      </c>
+      <c r="D412" s="9">
+        <v>1</v>
+      </c>
+      <c r="E412" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F412" s="7">
+        <v>5</v>
+      </c>
+      <c r="G412" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" spans="1:7">
+      <c r="A413" s="5">
+        <f t="shared" si="15"/>
+        <v>60390013</v>
+      </c>
+      <c r="B413" s="6">
+        <v>103900</v>
+      </c>
+      <c r="C413" s="7">
+        <v>13</v>
+      </c>
+      <c r="D413" s="9">
+        <v>1</v>
+      </c>
+      <c r="E413" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F413" s="7">
+        <v>5</v>
+      </c>
+      <c r="G413" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414" spans="1:7">
+      <c r="A414" s="5">
+        <f t="shared" si="15"/>
+        <v>60390014</v>
+      </c>
+      <c r="B414" s="6">
+        <v>103900</v>
+      </c>
+      <c r="C414" s="7">
+        <v>14</v>
+      </c>
+      <c r="D414" s="9">
+        <v>1</v>
+      </c>
+      <c r="E414" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F414" s="7">
+        <v>5</v>
+      </c>
+      <c r="G414" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="1:7">
+      <c r="A415" s="5">
+        <f t="shared" si="15"/>
+        <v>60390015</v>
+      </c>
+      <c r="B415" s="6">
+        <v>103900</v>
+      </c>
+      <c r="C415" s="7">
+        <v>15</v>
+      </c>
+      <c r="D415" s="9">
+        <v>1</v>
+      </c>
+      <c r="E415" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="F415" s="7">
+        <v>5</v>
+      </c>
+      <c r="G415" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" spans="1:7">
+      <c r="A416" s="5">
+        <f t="shared" si="15"/>
+        <v>60390016</v>
+      </c>
+      <c r="B416" s="6">
+        <v>103900</v>
+      </c>
+      <c r="C416" s="7">
+        <v>16</v>
+      </c>
+      <c r="D416" s="9">
+        <v>1</v>
+      </c>
+      <c r="E416" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F416" s="7">
+        <v>5</v>
+      </c>
+      <c r="G416" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417" spans="1:7">
+      <c r="A417" s="5">
+        <f t="shared" si="15"/>
+        <v>60390017</v>
+      </c>
+      <c r="B417" s="6">
+        <v>103900</v>
+      </c>
+      <c r="C417" s="7">
+        <v>17</v>
+      </c>
+      <c r="D417" s="9">
+        <v>1</v>
+      </c>
+      <c r="E417" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F417" s="7">
+        <v>5</v>
+      </c>
+      <c r="G417" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418" spans="1:7">
+      <c r="A418" s="5">
+        <f t="shared" si="15"/>
+        <v>60390018</v>
+      </c>
+      <c r="B418" s="6">
+        <v>103900</v>
+      </c>
+      <c r="C418" s="7">
+        <v>18</v>
+      </c>
+      <c r="D418" s="9">
+        <v>1</v>
+      </c>
+      <c r="E418" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F418" s="7">
+        <v>5</v>
+      </c>
+      <c r="G418" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" spans="1:7">
+      <c r="A419" s="5">
+        <f t="shared" si="15"/>
+        <v>60390019</v>
+      </c>
+      <c r="B419" s="6">
+        <v>103900</v>
+      </c>
+      <c r="C419" s="7">
+        <v>19</v>
+      </c>
+      <c r="D419" s="9">
+        <v>1</v>
+      </c>
+      <c r="E419" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F419" s="7">
+        <v>5</v>
+      </c>
+      <c r="G419" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420" spans="1:7">
+      <c r="A420" s="5">
+        <f t="shared" si="15"/>
+        <v>60390020</v>
+      </c>
+      <c r="B420" s="6">
+        <v>103900</v>
+      </c>
+      <c r="C420" s="7">
+        <v>20</v>
+      </c>
+      <c r="D420" s="9">
+        <v>1</v>
+      </c>
+      <c r="E420" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F420" s="7">
+        <v>5</v>
+      </c>
+      <c r="G420" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="1:7">
+      <c r="A421" s="5">
+        <f t="shared" si="15"/>
+        <v>60390021</v>
+      </c>
+      <c r="B421" s="6">
+        <v>103900</v>
+      </c>
+      <c r="C421" s="7">
+        <v>21</v>
+      </c>
+      <c r="D421" s="9">
+        <v>1</v>
+      </c>
+      <c r="E421" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F421" s="7">
+        <v>5</v>
+      </c>
+      <c r="G421" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" spans="1:7">
+      <c r="A422" s="5">
+        <f t="shared" si="15"/>
+        <v>60390022</v>
+      </c>
+      <c r="B422" s="6">
+        <v>103900</v>
+      </c>
+      <c r="C422" s="7">
+        <v>22</v>
+      </c>
+      <c r="D422" s="9">
+        <v>1</v>
+      </c>
+      <c r="E422" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F422" s="7">
+        <v>5</v>
+      </c>
+      <c r="G422" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423" spans="1:7">
+      <c r="A423" s="5">
+        <f t="shared" si="15"/>
+        <v>60390023</v>
+      </c>
+      <c r="B423" s="6">
+        <v>103900</v>
+      </c>
+      <c r="C423" s="7">
+        <v>23</v>
+      </c>
+      <c r="D423" s="9">
+        <v>1</v>
+      </c>
+      <c r="E423" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F423" s="7">
+        <v>5</v>
+      </c>
+      <c r="G423" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424" spans="1:7">
+      <c r="A424" s="5">
+        <f t="shared" si="15"/>
+        <v>60390024</v>
+      </c>
+      <c r="B424" s="6">
+        <v>103900</v>
+      </c>
+      <c r="C424" s="7">
+        <v>24</v>
+      </c>
+      <c r="D424" s="9">
+        <v>1</v>
+      </c>
+      <c r="E424" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F424" s="7">
+        <v>5</v>
+      </c>
+      <c r="G424" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425" spans="1:7">
+      <c r="A425" s="5">
+        <f t="shared" si="15"/>
+        <v>60390025</v>
+      </c>
+      <c r="B425" s="6">
+        <v>103900</v>
+      </c>
+      <c r="C425" s="7">
+        <v>25</v>
+      </c>
+      <c r="D425" s="9">
+        <v>1</v>
+      </c>
+      <c r="E425" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F425" s="7">
+        <v>5</v>
+      </c>
+      <c r="G425" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="E236">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E237">
     <cfRule type="duplicateValues" dxfId="0" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E237">
+  <conditionalFormatting sqref="E238">
     <cfRule type="duplicateValues" dxfId="0" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E238">
+  <conditionalFormatting sqref="E239">
     <cfRule type="duplicateValues" dxfId="0" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E239">
+  <conditionalFormatting sqref="E240">
     <cfRule type="duplicateValues" dxfId="0" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E240">
+  <conditionalFormatting sqref="E261">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E262">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E263">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E264">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E265">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E266">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E267">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E268">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E269">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E270">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E161:E185">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E186:E235">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E241:E250">
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E251:E260">
     <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E261">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  <conditionalFormatting sqref="E271:E285">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E262">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  <conditionalFormatting sqref="E286:E325">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E263">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E264">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E265">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E266">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E267">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E268">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E269">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E270">
+  <conditionalFormatting sqref="E326:E335">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E161:E185">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  <conditionalFormatting sqref="E361:E400">
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E186:E235">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E241:E250">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E251:E260">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E271:E285">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E286:E325">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E326:E335">
+  <conditionalFormatting sqref="E401:E403">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11627,30 +13202,30 @@
         <v>1</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>2</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>4</v>
       </c>
       <c r="L20" s="4"/>
       <c r="M20" s="4" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q20" s="4" t="s">
         <v>5</v>
@@ -11659,7 +13234,7 @@
         <v>3</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="5:19">
@@ -11677,29 +13252,29 @@
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="7" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="L21" s="7"/>
       <c r="M21" s="7" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q21" s="7" t="s">
         <v>7</v>
       </c>
       <c r="R21" s="7" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="S21" s="7"/>
     </row>
@@ -11711,30 +13286,30 @@
         <v>10</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>11</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K22" s="7" t="s">
         <v>13</v>
       </c>
       <c r="L22" s="7"/>
       <c r="M22" s="7" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q22" s="7" t="s">
         <v>14</v>
@@ -11774,28 +13349,28 @@
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="7" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
       <c r="M24" s="7" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="O24" s="7"/>
       <c r="P24" s="7" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q24" s="7">
         <v>5</v>
       </c>
       <c r="R24" s="7" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="S24" s="7" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="5:19">
@@ -11813,28 +13388,28 @@
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
       <c r="M25" s="8" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="O25" s="7"/>
       <c r="P25" s="7" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q25" s="7">
         <v>5</v>
       </c>
       <c r="R25" s="7" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="S25" s="7" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="5:19">
@@ -11902,7 +13477,7 @@
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
       <c r="L28" s="7" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="M28" s="5"/>
       <c r="N28" s="7">
@@ -11910,16 +13485,16 @@
       </c>
       <c r="O28" s="7"/>
       <c r="P28" s="7" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q28" s="7">
         <v>5</v>
       </c>
       <c r="R28" s="7" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="S28" s="7" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseLine.xlsx
+++ b/slots/resources/sample/BaseLine.xlsx
@@ -321,7 +321,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="205">
   <si>
     <t>id</t>
   </si>
@@ -828,6 +828,9 @@
   </si>
   <si>
     <t>2_6_8_11_14</t>
+  </si>
+  <si>
+    <t>3_5_8_11_13</t>
   </si>
   <si>
     <t>1_5_8_11_15</t>
@@ -10650,7 +10653,7 @@
         <v>1</v>
       </c>
       <c r="E323" s="7" t="s">
-        <v>98</v>
+        <v>169</v>
       </c>
       <c r="F323" s="7">
         <v>5</v>
@@ -10674,7 +10677,7 @@
         <v>1</v>
       </c>
       <c r="E324" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F324" s="7">
         <v>5</v>
@@ -10698,7 +10701,7 @@
         <v>1</v>
       </c>
       <c r="E325" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F325" s="7">
         <v>5</v>
@@ -12378,7 +12381,7 @@
         <v>1</v>
       </c>
       <c r="E395" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F395" s="7">
         <v>5</v>
@@ -12402,7 +12405,7 @@
         <v>1</v>
       </c>
       <c r="E396" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F396" s="7">
         <v>5</v>
@@ -12474,7 +12477,7 @@
         <v>1</v>
       </c>
       <c r="E399" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F399" s="7">
         <v>5</v>
@@ -13202,30 +13205,30 @@
         <v>1</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>2</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>4</v>
       </c>
       <c r="L20" s="4"/>
       <c r="M20" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q20" s="4" t="s">
         <v>5</v>
@@ -13234,7 +13237,7 @@
         <v>3</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="5:19">
@@ -13252,29 +13255,29 @@
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L21" s="7"/>
       <c r="M21" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N21" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="O21" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="O21" s="7" t="s">
-        <v>183</v>
-      </c>
       <c r="P21" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q21" s="7" t="s">
         <v>7</v>
       </c>
       <c r="R21" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="S21" s="7"/>
     </row>
@@ -13286,30 +13289,30 @@
         <v>10</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>11</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K22" s="7" t="s">
         <v>13</v>
       </c>
       <c r="L22" s="7"/>
       <c r="M22" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q22" s="7" t="s">
         <v>14</v>
@@ -13349,28 +13352,28 @@
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
       <c r="M24" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="N24" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="N24" s="7" t="s">
-        <v>192</v>
       </c>
       <c r="O24" s="7"/>
       <c r="P24" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q24" s="7">
         <v>5</v>
       </c>
       <c r="R24" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="S24" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="5:19">
@@ -13388,28 +13391,28 @@
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
       <c r="M25" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O25" s="7"/>
       <c r="P25" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q25" s="7">
         <v>5</v>
       </c>
       <c r="R25" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="S25" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="5:19">
@@ -13477,7 +13480,7 @@
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
       <c r="L28" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M28" s="5"/>
       <c r="N28" s="7">
@@ -13485,16 +13488,16 @@
       </c>
       <c r="O28" s="7"/>
       <c r="P28" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q28" s="7">
         <v>5</v>
       </c>
       <c r="R28" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="S28" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseLine.xlsx
+++ b/slots/resources/sample/BaseLine.xlsx
@@ -321,7 +321,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="204">
   <si>
     <t>id</t>
   </si>
@@ -828,9 +828,6 @@
   </si>
   <si>
     <t>2_6_8_11_14</t>
-  </si>
-  <si>
-    <t>3_5_8_11_13</t>
   </si>
   <si>
     <t>1_5_8_11_15</t>
@@ -10653,7 +10650,7 @@
         <v>1</v>
       </c>
       <c r="E323" s="7" t="s">
-        <v>169</v>
+        <v>98</v>
       </c>
       <c r="F323" s="7">
         <v>5</v>
@@ -10677,7 +10674,7 @@
         <v>1</v>
       </c>
       <c r="E324" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F324" s="7">
         <v>5</v>
@@ -10701,7 +10698,7 @@
         <v>1</v>
       </c>
       <c r="E325" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F325" s="7">
         <v>5</v>
@@ -12381,7 +12378,7 @@
         <v>1</v>
       </c>
       <c r="E395" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F395" s="7">
         <v>5</v>
@@ -12405,7 +12402,7 @@
         <v>1</v>
       </c>
       <c r="E396" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F396" s="7">
         <v>5</v>
@@ -12477,7 +12474,7 @@
         <v>1</v>
       </c>
       <c r="E399" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F399" s="7">
         <v>5</v>
@@ -13205,30 +13202,30 @@
         <v>1</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>2</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>4</v>
       </c>
       <c r="L20" s="4"/>
       <c r="M20" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="N20" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="N20" s="4" t="s">
+      <c r="O20" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="O20" s="4" t="s">
+      <c r="P20" s="4" t="s">
         <v>179</v>
-      </c>
-      <c r="P20" s="4" t="s">
-        <v>180</v>
       </c>
       <c r="Q20" s="4" t="s">
         <v>5</v>
@@ -13237,7 +13234,7 @@
         <v>3</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="5:19">
@@ -13255,29 +13252,29 @@
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="K21" s="7" t="s">
         <v>182</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>183</v>
       </c>
       <c r="L21" s="7"/>
       <c r="M21" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="N21" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="N21" s="7" t="s">
+      <c r="O21" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="P21" s="7" t="s">
         <v>185</v>
-      </c>
-      <c r="O21" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="P21" s="7" t="s">
-        <v>186</v>
       </c>
       <c r="Q21" s="7" t="s">
         <v>7</v>
       </c>
       <c r="R21" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="S21" s="7"/>
     </row>
@@ -13289,30 +13286,30 @@
         <v>10</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>11</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K22" s="7" t="s">
         <v>13</v>
       </c>
       <c r="L22" s="7"/>
       <c r="M22" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="N22" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="N22" s="7" t="s">
+      <c r="O22" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="O22" s="7" t="s">
+      <c r="P22" s="7" t="s">
         <v>191</v>
-      </c>
-      <c r="P22" s="7" t="s">
-        <v>192</v>
       </c>
       <c r="Q22" s="7" t="s">
         <v>14</v>
@@ -13352,28 +13349,28 @@
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
       <c r="M24" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O24" s="7"/>
       <c r="P24" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q24" s="7">
+        <v>5</v>
+      </c>
+      <c r="R24" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="Q24" s="7">
-        <v>5</v>
-      </c>
-      <c r="R24" s="7" t="s">
+      <c r="S24" s="7" t="s">
         <v>196</v>
-      </c>
-      <c r="S24" s="7" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="5:19">
@@ -13391,28 +13388,28 @@
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
       <c r="M25" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="N25" s="7" t="s">
         <v>199</v>
-      </c>
-      <c r="N25" s="7" t="s">
-        <v>200</v>
       </c>
       <c r="O25" s="7"/>
       <c r="P25" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q25" s="7">
         <v>5</v>
       </c>
       <c r="R25" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="S25" s="7" t="s">
         <v>201</v>
-      </c>
-      <c r="S25" s="7" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="5:19">
@@ -13480,7 +13477,7 @@
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
       <c r="L28" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M28" s="5"/>
       <c r="N28" s="7">
@@ -13488,16 +13485,16 @@
       </c>
       <c r="O28" s="7"/>
       <c r="P28" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q28" s="7">
+        <v>5</v>
+      </c>
+      <c r="R28" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="Q28" s="7">
-        <v>5</v>
-      </c>
-      <c r="R28" s="7" t="s">
-        <v>196</v>
-      </c>
       <c r="S28" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
